--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_ACF12A4F8F533250C750CDEB4C3C9E6128049166" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77C087A-42ED-4314-BA05-5794F1884A2D}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16542C7B-15B1-4E99-BCCE-B1C26AEC06AC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="1296" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="360">
   <si>
     <t>Template Test Case</t>
   </si>
@@ -1118,7 +1118,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,6 +1309,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1715,7 +1721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1998,6 +2004,27 @@
     <xf numFmtId="0" fontId="28" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2010,25 +2037,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2366,89 +2375,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DB19"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.08984375" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.08984375" customWidth="1"/>
-    <col min="4" max="4" width="9.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
-    <col min="6" max="6" width="32.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8.08984375" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
-    <col min="14" max="14" width="21.36328125" customWidth="1"/>
-    <col min="15" max="15" width="19.7265625" customWidth="1"/>
-    <col min="16" max="16" width="27.453125" customWidth="1"/>
-    <col min="17" max="17" width="25.08984375" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
+    <col min="16" max="16" width="27.42578125" customWidth="1"/>
+    <col min="17" max="17" width="25.140625" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="21.7265625" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="31.08984375" customWidth="1"/>
-    <col min="22" max="22" width="16.453125" customWidth="1"/>
-    <col min="23" max="23" width="25.36328125" customWidth="1"/>
-    <col min="24" max="24" width="8.453125" customWidth="1"/>
-    <col min="25" max="25" width="15.36328125" customWidth="1"/>
-    <col min="26" max="26" width="14.81640625" customWidth="1"/>
-    <col min="27" max="27" width="15.36328125" customWidth="1"/>
-    <col min="28" max="28" width="16.81640625" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" customWidth="1"/>
-    <col min="30" max="30" width="24.54296875" customWidth="1"/>
+    <col min="19" max="19" width="21.7109375" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="21" max="21" width="31.140625" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" customWidth="1"/>
+    <col min="23" max="23" width="25.42578125" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.42578125" customWidth="1"/>
+    <col min="28" max="28" width="16.85546875" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" customWidth="1"/>
+    <col min="30" max="30" width="24.5703125" customWidth="1"/>
     <col min="31" max="31" width="24" customWidth="1"/>
-    <col min="32" max="32" width="27.7265625" customWidth="1"/>
-    <col min="33" max="33" width="17.36328125" customWidth="1"/>
-    <col min="34" max="34" width="18.26953125" customWidth="1"/>
+    <col min="32" max="32" width="27.7109375" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" customWidth="1"/>
+    <col min="34" max="34" width="18.28515625" customWidth="1"/>
     <col min="35" max="35" width="24" customWidth="1"/>
-    <col min="36" max="36" width="16.26953125" customWidth="1"/>
+    <col min="36" max="36" width="16.28515625" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="27.453125" customWidth="1"/>
-    <col min="39" max="39" width="21.36328125" customWidth="1"/>
-    <col min="40" max="40" width="15.26953125" customWidth="1"/>
+    <col min="38" max="38" width="27.42578125" customWidth="1"/>
+    <col min="39" max="39" width="21.42578125" customWidth="1"/>
+    <col min="40" max="40" width="15.28515625" customWidth="1"/>
     <col min="41" max="41" width="29" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="8.08984375" customWidth="1"/>
+    <col min="43" max="43" width="8.140625" customWidth="1"/>
     <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="45" max="45" width="14.36328125" customWidth="1"/>
-    <col min="46" max="46" width="23.36328125" customWidth="1"/>
-    <col min="47" max="47" width="23.08984375" customWidth="1"/>
-    <col min="48" max="48" width="17.453125" customWidth="1"/>
-    <col min="49" max="49" width="14.08984375" customWidth="1"/>
-    <col min="50" max="50" width="18.7265625" customWidth="1"/>
-    <col min="51" max="51" width="23.36328125" customWidth="1"/>
-    <col min="52" max="52" width="24.7265625" customWidth="1"/>
-    <col min="53" max="55" width="12.54296875" customWidth="1"/>
-    <col min="56" max="56" width="25.36328125" customWidth="1"/>
-    <col min="57" max="57" width="22.36328125" customWidth="1"/>
-    <col min="58" max="58" width="13.453125" customWidth="1"/>
-    <col min="59" max="59" width="15.08984375" customWidth="1"/>
-    <col min="60" max="60" width="13.36328125" customWidth="1"/>
-    <col min="61" max="61" width="14.36328125" customWidth="1"/>
-    <col min="62" max="62" width="15.36328125" customWidth="1"/>
-    <col min="63" max="63" width="17.81640625" customWidth="1"/>
-    <col min="64" max="64" width="12.54296875" customWidth="1"/>
-    <col min="65" max="65" width="27.36328125" customWidth="1"/>
-    <col min="66" max="66" width="24.36328125" customWidth="1"/>
-    <col min="67" max="73" width="12.54296875" customWidth="1"/>
-    <col min="74" max="74" width="27.36328125" customWidth="1"/>
-    <col min="75" max="75" width="24.36328125" customWidth="1"/>
-    <col min="76" max="87" width="12.54296875" customWidth="1"/>
-    <col min="88" max="88" width="15.7265625" customWidth="1"/>
-    <col min="89" max="95" width="12.54296875" customWidth="1"/>
-    <col min="96" max="96" width="15.7265625" customWidth="1"/>
-    <col min="97" max="97" width="17.7265625" customWidth="1"/>
-    <col min="98" max="98" width="19.54296875" customWidth="1"/>
+    <col min="45" max="45" width="14.42578125" customWidth="1"/>
+    <col min="46" max="46" width="23.42578125" customWidth="1"/>
+    <col min="47" max="47" width="23.140625" customWidth="1"/>
+    <col min="48" max="48" width="17.42578125" customWidth="1"/>
+    <col min="49" max="49" width="14.140625" customWidth="1"/>
+    <col min="50" max="50" width="18.7109375" customWidth="1"/>
+    <col min="51" max="51" width="23.42578125" customWidth="1"/>
+    <col min="52" max="52" width="24.7109375" customWidth="1"/>
+    <col min="53" max="55" width="12.5703125" customWidth="1"/>
+    <col min="56" max="56" width="25.42578125" customWidth="1"/>
+    <col min="57" max="57" width="22.42578125" customWidth="1"/>
+    <col min="58" max="58" width="13.42578125" customWidth="1"/>
+    <col min="59" max="59" width="15.140625" customWidth="1"/>
+    <col min="60" max="60" width="13.42578125" customWidth="1"/>
+    <col min="61" max="61" width="14.42578125" customWidth="1"/>
+    <col min="62" max="62" width="15.42578125" customWidth="1"/>
+    <col min="63" max="63" width="17.85546875" customWidth="1"/>
+    <col min="64" max="64" width="12.5703125" customWidth="1"/>
+    <col min="65" max="65" width="27.42578125" customWidth="1"/>
+    <col min="66" max="66" width="24.42578125" customWidth="1"/>
+    <col min="67" max="73" width="12.5703125" customWidth="1"/>
+    <col min="74" max="74" width="27.42578125" customWidth="1"/>
+    <col min="75" max="75" width="24.42578125" customWidth="1"/>
+    <col min="76" max="87" width="12.5703125" customWidth="1"/>
+    <col min="88" max="88" width="15.7109375" customWidth="1"/>
+    <col min="89" max="95" width="12.5703125" customWidth="1"/>
+    <col min="96" max="96" width="15.7109375" customWidth="1"/>
+    <col min="97" max="97" width="17.7109375" customWidth="1"/>
+    <col min="98" max="98" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2747,29 +2756,29 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="N4" s="106" t="s">
+    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="107"/>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="107"/>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
-      <c r="AB4" s="107"/>
-      <c r="AC4" s="107"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="108"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="114"/>
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="115"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2842,16 +2851,16 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="109" t="s">
+      <c r="CW4" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="109"/>
-      <c r="CY4" s="109"/>
-      <c r="CZ4" s="109"/>
-      <c r="DA4" s="109"/>
-      <c r="DB4" s="109"/>
-    </row>
-    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CX4" s="116"/>
+      <c r="CY4" s="116"/>
+      <c r="CZ4" s="116"/>
+      <c r="DA4" s="116"/>
+      <c r="DB4" s="116"/>
+    </row>
+    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>7</v>
@@ -3166,7 +3175,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35"/>
       <c r="B6" s="36" t="s">
         <v>111</v>
@@ -3281,9 +3290,7 @@
       <c r="AO6" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="AP6" s="113" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP6" s="109"/>
       <c r="AQ6" s="38"/>
       <c r="AR6" s="38"/>
       <c r="AS6" s="38"/>
@@ -3291,7 +3298,7 @@
         <v>145</v>
       </c>
       <c r="AU6" s="38"/>
-      <c r="AV6" s="113"/>
+      <c r="AV6" s="109"/>
       <c r="AW6" s="38" t="s">
         <v>134</v>
       </c>
@@ -3382,7 +3389,7 @@
       <c r="DA6" s="46"/>
       <c r="DB6" s="46"/>
     </row>
-    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35"/>
       <c r="B7" s="36" t="s">
         <v>150</v>
@@ -3497,9 +3504,7 @@
       <c r="AO7" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="AP7" s="113" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP7" s="109"/>
       <c r="AQ7" s="38"/>
       <c r="AR7" s="38"/>
       <c r="AS7" s="38"/>
@@ -3507,7 +3512,7 @@
         <v>145</v>
       </c>
       <c r="AU7" s="38"/>
-      <c r="AV7" s="113"/>
+      <c r="AV7" s="109"/>
       <c r="AW7" s="38" t="s">
         <v>174</v>
       </c>
@@ -3542,7 +3547,7 @@
       <c r="BJ7" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="BK7" s="113"/>
+      <c r="BK7" s="109"/>
       <c r="BL7" s="38" t="s">
         <v>147</v>
       </c>
@@ -3555,7 +3560,7 @@
       <c r="BO7" s="50"/>
       <c r="BP7" s="50"/>
       <c r="BQ7" s="50"/>
-      <c r="BR7" s="113"/>
+      <c r="BR7" s="109"/>
       <c r="BS7" s="38"/>
       <c r="BT7" s="50"/>
       <c r="BU7" s="50"/>
@@ -3592,7 +3597,7 @@
       <c r="DA7" s="42"/>
       <c r="DB7" s="42"/>
     </row>
-    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="B8" s="36" t="s">
         <v>177</v>
@@ -3704,9 +3709,7 @@
       <c r="AO8" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="AP8" s="113" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP8" s="109"/>
       <c r="AQ8" s="38"/>
       <c r="AR8" s="38"/>
       <c r="AS8" s="38"/>
@@ -3714,7 +3717,7 @@
         <v>145</v>
       </c>
       <c r="AU8" s="38"/>
-      <c r="AV8" s="113"/>
+      <c r="AV8" s="109"/>
       <c r="AW8" s="38" t="s">
         <v>165</v>
       </c>
@@ -3749,7 +3752,7 @@
       <c r="BJ8" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="BK8" s="113"/>
+      <c r="BK8" s="109"/>
       <c r="BL8" s="38" t="s">
         <v>147</v>
       </c>
@@ -3762,7 +3765,7 @@
       <c r="BO8" s="50"/>
       <c r="BP8" s="50"/>
       <c r="BQ8" s="50"/>
-      <c r="BR8" s="113"/>
+      <c r="BR8" s="109"/>
       <c r="BS8" s="38"/>
       <c r="BT8" s="50"/>
       <c r="BU8" s="50"/>
@@ -3799,7 +3802,7 @@
       <c r="DA8" s="42"/>
       <c r="DB8" s="42"/>
     </row>
-    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="B9" s="36" t="s">
         <v>198</v>
@@ -3916,9 +3919,7 @@
       <c r="AO9" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="AP9" s="113" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP9" s="109"/>
       <c r="AQ9" s="38"/>
       <c r="AR9" s="38"/>
       <c r="AS9" s="38"/>
@@ -3926,7 +3927,7 @@
         <v>145</v>
       </c>
       <c r="AU9" s="38"/>
-      <c r="AV9" s="113"/>
+      <c r="AV9" s="109"/>
       <c r="AW9" s="38" t="s">
         <v>174</v>
       </c>
@@ -4017,7 +4018,7 @@
       <c r="DA9" s="42"/>
       <c r="DB9" s="42"/>
     </row>
-    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
       <c r="B10" s="36" t="s">
         <v>217</v>
@@ -4042,36 +4043,32 @@
       <c r="J10" s="59"/>
       <c r="K10" s="59"/>
       <c r="L10" s="59"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
-      <c r="R10" s="110"/>
+      <c r="R10" s="106"/>
       <c r="S10" s="60" t="s">
         <v>220</v>
       </c>
       <c r="T10" s="59"/>
-      <c r="U10" s="110"/>
+      <c r="U10" s="106"/>
       <c r="V10" s="59"/>
       <c r="W10" s="59"/>
       <c r="X10" s="59"/>
-      <c r="Y10" s="110"/>
+      <c r="Y10" s="106"/>
       <c r="Z10" s="59"/>
       <c r="AA10" s="61" t="s">
         <v>139</v>
       </c>
       <c r="AB10" s="59"/>
-      <c r="AC10" s="112" t="s">
-        <v>144</v>
-      </c>
+      <c r="AC10" s="108"/>
       <c r="AD10" s="56">
         <v>0</v>
       </c>
       <c r="AE10" s="59"/>
-      <c r="AF10" s="110" t="s">
-        <v>144</v>
-      </c>
+      <c r="AF10" s="106"/>
       <c r="AG10" s="59"/>
       <c r="AH10" s="62">
         <v>0.32</v>
@@ -4081,33 +4078,29 @@
       </c>
       <c r="AJ10" s="59"/>
       <c r="AK10" s="59"/>
-      <c r="AL10" s="110" t="s">
-        <v>144</v>
-      </c>
+      <c r="AL10" s="106"/>
       <c r="AM10" s="59"/>
       <c r="AN10" s="59"/>
       <c r="AO10" s="63">
         <v>7775014694</v>
       </c>
-      <c r="AP10" s="110" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP10" s="106"/>
       <c r="AQ10" s="59"/>
       <c r="AR10" s="59"/>
       <c r="AS10" s="59"/>
       <c r="AT10" s="59"/>
       <c r="AU10" s="59"/>
-      <c r="AV10" s="110"/>
+      <c r="AV10" s="106"/>
       <c r="AW10" s="59" t="s">
         <v>139</v>
       </c>
       <c r="AX10" s="59"/>
-      <c r="AY10" s="110"/>
-      <c r="AZ10" s="110"/>
+      <c r="AY10" s="106"/>
+      <c r="AZ10" s="106"/>
       <c r="BA10" s="42"/>
-      <c r="BB10" s="116"/>
+      <c r="BB10" s="112"/>
       <c r="BC10" s="59"/>
-      <c r="BD10" s="116"/>
+      <c r="BD10" s="112"/>
       <c r="BE10" s="50"/>
       <c r="BF10" s="49"/>
       <c r="BG10" s="49"/>
@@ -4118,14 +4111,14 @@
       <c r="BJ10" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="BK10" s="110"/>
+      <c r="BK10" s="106"/>
       <c r="BL10" s="59"/>
-      <c r="BM10" s="110"/>
+      <c r="BM10" s="106"/>
       <c r="BN10" s="50"/>
       <c r="BO10" s="50"/>
       <c r="BP10" s="50"/>
       <c r="BQ10" s="50"/>
-      <c r="BR10" s="110"/>
+      <c r="BR10" s="106"/>
       <c r="BS10" s="59"/>
       <c r="BT10" s="50"/>
       <c r="BU10" s="50"/>
@@ -4162,7 +4155,7 @@
       <c r="DA10" s="42"/>
       <c r="DB10" s="42"/>
     </row>
-    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="66"/>
       <c r="B11" s="67" t="s">
         <v>222</v>
@@ -4285,9 +4278,7 @@
       <c r="AO11" s="68">
         <v>1233321</v>
       </c>
-      <c r="AP11" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP11" s="107"/>
       <c r="AQ11" s="68"/>
       <c r="AR11" s="68" t="s">
         <v>228</v>
@@ -4297,7 +4288,7 @@
         <v>145</v>
       </c>
       <c r="AU11" s="68"/>
-      <c r="AV11" s="111"/>
+      <c r="AV11" s="107"/>
       <c r="AW11" s="68" t="s">
         <v>174</v>
       </c>
@@ -4332,7 +4323,7 @@
       <c r="BJ11" s="68" t="s">
         <v>231</v>
       </c>
-      <c r="BK11" s="111"/>
+      <c r="BK11" s="107"/>
       <c r="BL11" s="68" t="s">
         <v>147</v>
       </c>
@@ -4345,7 +4336,7 @@
       <c r="BO11" s="50"/>
       <c r="BP11" s="50"/>
       <c r="BQ11" s="50"/>
-      <c r="BR11" s="111"/>
+      <c r="BR11" s="107"/>
       <c r="BS11" s="68"/>
       <c r="BT11" s="50"/>
       <c r="BU11" s="50"/>
@@ -4376,7 +4367,7 @@
       <c r="CT11" s="50"/>
       <c r="CU11" s="51"/>
     </row>
-    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="71"/>
       <c r="B12" s="72" t="s">
         <v>234</v>
@@ -4499,9 +4490,7 @@
       <c r="AO12" s="68">
         <v>1234567</v>
       </c>
-      <c r="AP12" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP12" s="107"/>
       <c r="AQ12" s="68"/>
       <c r="AR12" s="68" t="s">
         <v>228</v>
@@ -4511,7 +4500,7 @@
         <v>145</v>
       </c>
       <c r="AU12" s="68"/>
-      <c r="AV12" s="111"/>
+      <c r="AV12" s="107"/>
       <c r="AW12" s="68" t="s">
         <v>174</v>
       </c>
@@ -4546,7 +4535,7 @@
       <c r="BJ12" s="74" t="s">
         <v>231</v>
       </c>
-      <c r="BK12" s="111"/>
+      <c r="BK12" s="107"/>
       <c r="BL12" s="68" t="s">
         <v>147</v>
       </c>
@@ -4559,7 +4548,7 @@
       <c r="BO12" s="50"/>
       <c r="BP12" s="50"/>
       <c r="BQ12" s="50"/>
-      <c r="BR12" s="111"/>
+      <c r="BR12" s="107"/>
       <c r="BS12" s="68" t="s">
         <v>228</v>
       </c>
@@ -4592,7 +4581,7 @@
       <c r="CT12" s="50"/>
       <c r="CU12" s="51"/>
     </row>
-    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="71"/>
       <c r="B13" s="72" t="s">
         <v>243</v>
@@ -4715,9 +4704,7 @@
       <c r="AO13" s="75">
         <v>5643234</v>
       </c>
-      <c r="AP13" s="114" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP13" s="110"/>
       <c r="AQ13" s="75"/>
       <c r="AR13" s="75" t="s">
         <v>228</v>
@@ -4727,7 +4714,7 @@
         <v>145</v>
       </c>
       <c r="AU13" s="75"/>
-      <c r="AV13" s="114"/>
+      <c r="AV13" s="110"/>
       <c r="AW13" s="75" t="s">
         <v>134</v>
       </c>
@@ -4762,7 +4749,7 @@
       <c r="BJ13" s="75" t="s">
         <v>231</v>
       </c>
-      <c r="BK13" s="114"/>
+      <c r="BK13" s="110"/>
       <c r="BL13" s="75" t="s">
         <v>147</v>
       </c>
@@ -4775,7 +4762,7 @@
       <c r="BO13" s="50"/>
       <c r="BP13" s="50"/>
       <c r="BQ13" s="50"/>
-      <c r="BR13" s="111"/>
+      <c r="BR13" s="107"/>
       <c r="BS13" s="68" t="s">
         <v>228</v>
       </c>
@@ -4808,7 +4795,7 @@
       <c r="CT13" s="50"/>
       <c r="CU13" s="51"/>
     </row>
-    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="71"/>
       <c r="B14" s="72" t="s">
         <v>250</v>
@@ -4931,9 +4918,7 @@
       <c r="AO14" s="68">
         <v>1234567</v>
       </c>
-      <c r="AP14" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP14" s="107"/>
       <c r="AQ14" s="68"/>
       <c r="AR14" s="68" t="s">
         <v>228</v>
@@ -4943,7 +4928,7 @@
         <v>145</v>
       </c>
       <c r="AU14" s="68"/>
-      <c r="AV14" s="111"/>
+      <c r="AV14" s="107"/>
       <c r="AW14" s="68" t="s">
         <v>174</v>
       </c>
@@ -4978,7 +4963,7 @@
       <c r="BJ14" s="68" t="s">
         <v>231</v>
       </c>
-      <c r="BK14" s="111"/>
+      <c r="BK14" s="107"/>
       <c r="BL14" s="68" t="s">
         <v>147</v>
       </c>
@@ -4991,7 +4976,7 @@
       <c r="BO14" s="50"/>
       <c r="BP14" s="50"/>
       <c r="BQ14" s="50"/>
-      <c r="BR14" s="111"/>
+      <c r="BR14" s="107"/>
       <c r="BS14" s="68"/>
       <c r="BT14" s="50"/>
       <c r="BU14" s="50"/>
@@ -5022,7 +5007,7 @@
       <c r="CT14" s="50"/>
       <c r="CU14" s="51"/>
     </row>
-    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="71"/>
       <c r="B15" s="72" t="s">
         <v>256</v>
@@ -5145,9 +5130,7 @@
       <c r="AO15" s="75">
         <v>1234567</v>
       </c>
-      <c r="AP15" s="114" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP15" s="110"/>
       <c r="AQ15" s="75"/>
       <c r="AR15" s="75" t="s">
         <v>228</v>
@@ -5157,7 +5140,7 @@
         <v>145</v>
       </c>
       <c r="AU15" s="75"/>
-      <c r="AV15" s="114"/>
+      <c r="AV15" s="110"/>
       <c r="AW15" s="75" t="s">
         <v>139</v>
       </c>
@@ -5242,7 +5225,7 @@
       <c r="CT15" s="50"/>
       <c r="CU15" s="51"/>
     </row>
-    <row r="16" spans="1:106" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:106" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="77"/>
       <c r="B16" s="72" t="s">
         <v>265</v>
@@ -5356,9 +5339,7 @@
       <c r="AO16" s="78">
         <v>7776665</v>
       </c>
-      <c r="AP16" s="114" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP16" s="110"/>
       <c r="AQ16" s="81"/>
       <c r="AR16" s="81"/>
       <c r="AS16" s="81"/>
@@ -5401,14 +5382,14 @@
       <c r="BJ16" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="BK16" s="111"/>
+      <c r="BK16" s="107"/>
       <c r="BL16" s="83"/>
-      <c r="BM16" s="111"/>
+      <c r="BM16" s="107"/>
       <c r="BN16" s="83"/>
       <c r="BO16" s="83"/>
       <c r="BP16" s="78"/>
       <c r="BQ16" s="78"/>
-      <c r="BR16" s="114"/>
+      <c r="BR16" s="110"/>
       <c r="BS16" s="78"/>
       <c r="BT16" s="82"/>
       <c r="BU16" s="78"/>
@@ -5439,7 +5420,7 @@
       <c r="CT16" s="81"/>
       <c r="CU16" s="81"/>
     </row>
-    <row r="17" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:99" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="82"/>
       <c r="B17" s="36" t="s">
         <v>273</v>
@@ -5551,9 +5532,7 @@
       <c r="AO17" s="86">
         <v>6767679</v>
       </c>
-      <c r="AP17" s="115" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP17" s="111"/>
       <c r="AQ17" s="81"/>
       <c r="AR17" s="81"/>
       <c r="AS17" s="81"/>
@@ -5596,14 +5575,14 @@
       <c r="BJ17" s="86" t="s">
         <v>187</v>
       </c>
-      <c r="BK17" s="115"/>
+      <c r="BK17" s="111"/>
       <c r="BL17" s="86"/>
-      <c r="BM17" s="115"/>
+      <c r="BM17" s="111"/>
       <c r="BN17" s="86"/>
       <c r="BO17" s="86"/>
       <c r="BP17" s="86"/>
       <c r="BQ17" s="86"/>
-      <c r="BR17" s="115"/>
+      <c r="BR17" s="111"/>
       <c r="BS17" s="86"/>
       <c r="BT17" s="82"/>
       <c r="BU17" s="86"/>
@@ -5634,7 +5613,7 @@
       <c r="CT17" s="81"/>
       <c r="CU17" s="81"/>
     </row>
-    <row r="18" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:99" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="89"/>
       <c r="B18" s="72" t="s">
         <v>281</v>
@@ -5746,9 +5725,7 @@
       <c r="AO18" s="90">
         <v>5656578</v>
       </c>
-      <c r="AP18" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP18" s="107"/>
       <c r="AQ18" s="92"/>
       <c r="AR18" s="92"/>
       <c r="AS18" s="92"/>
@@ -5791,14 +5768,14 @@
       <c r="BJ18" s="90" t="s">
         <v>187</v>
       </c>
-      <c r="BK18" s="111"/>
+      <c r="BK18" s="107"/>
       <c r="BL18" s="90"/>
-      <c r="BM18" s="111"/>
+      <c r="BM18" s="107"/>
       <c r="BN18" s="90"/>
       <c r="BO18" s="90"/>
       <c r="BP18" s="90"/>
       <c r="BQ18" s="90"/>
-      <c r="BR18" s="111"/>
+      <c r="BR18" s="107"/>
       <c r="BS18" s="90"/>
       <c r="BT18" s="93"/>
       <c r="BU18" s="90"/>
@@ -5829,7 +5806,7 @@
       <c r="CT18" s="92"/>
       <c r="CU18" s="92"/>
     </row>
-    <row r="19" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:99" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="89"/>
       <c r="B19" s="96" t="s">
         <v>287</v>
@@ -5852,34 +5829,28 @@
       <c r="J19" s="90"/>
       <c r="K19" s="90"/>
       <c r="L19" s="90"/>
-      <c r="M19" s="111" t="s">
-        <v>144</v>
-      </c>
-      <c r="N19" s="111"/>
-      <c r="O19" s="111"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="107"/>
       <c r="P19" s="90"/>
       <c r="Q19" s="90"/>
-      <c r="R19" s="111"/>
-      <c r="S19" s="111"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="107"/>
       <c r="T19" s="90"/>
-      <c r="U19" s="111"/>
+      <c r="U19" s="107"/>
       <c r="V19" s="90"/>
       <c r="W19" s="90"/>
       <c r="X19" s="90"/>
-      <c r="Y19" s="111"/>
+      <c r="Y19" s="107"/>
       <c r="Z19" s="90"/>
-      <c r="AA19" s="111"/>
+      <c r="AA19" s="107"/>
       <c r="AB19" s="90"/>
       <c r="AC19" s="47">
         <v>769.16</v>
       </c>
-      <c r="AD19" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AD19" s="107"/>
       <c r="AE19" s="90"/>
-      <c r="AF19" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AF19" s="107"/>
       <c r="AG19" s="90"/>
       <c r="AH19" s="98">
         <v>65.09</v>
@@ -5889,31 +5860,27 @@
       </c>
       <c r="AJ19" s="90"/>
       <c r="AK19" s="90"/>
-      <c r="AL19" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AL19" s="107"/>
       <c r="AM19" s="90"/>
       <c r="AN19" s="90"/>
       <c r="AO19" s="90"/>
-      <c r="AP19" s="111" t="s">
-        <v>144</v>
-      </c>
+      <c r="AP19" s="107"/>
       <c r="AQ19" s="99"/>
       <c r="AR19" s="99"/>
       <c r="AS19" s="99"/>
       <c r="AT19" s="90"/>
       <c r="AU19" s="90"/>
-      <c r="AV19" s="111"/>
+      <c r="AV19" s="107"/>
       <c r="AW19" s="90"/>
       <c r="AX19" s="90"/>
-      <c r="AY19" s="111"/>
-      <c r="AZ19" s="111"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="90"/>
       <c r="BB19" s="87" t="s">
         <v>146</v>
       </c>
       <c r="BC19" s="90"/>
-      <c r="BD19" s="111"/>
+      <c r="BD19" s="107"/>
       <c r="BE19" s="99"/>
       <c r="BF19" s="99"/>
       <c r="BG19" s="99"/>
@@ -5924,14 +5891,14 @@
       <c r="BJ19" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="BK19" s="111"/>
+      <c r="BK19" s="107"/>
       <c r="BL19" s="90"/>
-      <c r="BM19" s="111"/>
+      <c r="BM19" s="107"/>
       <c r="BN19" s="90"/>
       <c r="BO19" s="90"/>
       <c r="BP19" s="90"/>
       <c r="BQ19" s="90"/>
-      <c r="BR19" s="111"/>
+      <c r="BR19" s="107"/>
       <c r="BS19" s="90"/>
       <c r="BT19" s="101"/>
       <c r="BU19" s="90"/>
@@ -5979,7 +5946,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5988,7 +5955,7 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="102" t="s">
         <v>289</v>
       </c>
@@ -6005,7 +5972,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>6</v>
       </c>
@@ -6022,7 +5989,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>6</v>
       </c>
@@ -6039,7 +6006,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -6056,7 +6023,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>6</v>
       </c>
@@ -6073,7 +6040,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -6090,7 +6057,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6107,7 +6074,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6124,7 +6091,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -6141,7 +6108,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6158,7 +6125,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -6175,7 +6142,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6</v>
       </c>
@@ -6192,7 +6159,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
@@ -6209,7 +6176,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>6</v>
       </c>
@@ -6226,7 +6193,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>6</v>
       </c>
@@ -6243,7 +6210,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>6</v>
       </c>
@@ -6260,7 +6227,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>6</v>
       </c>
@@ -6277,7 +6244,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>6</v>
       </c>
@@ -6294,7 +6261,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6</v>
       </c>
@@ -6311,7 +6278,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6</v>
       </c>
@@ -6328,7 +6295,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6</v>
       </c>
@@ -6345,7 +6312,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -6362,7 +6329,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>6</v>
       </c>
@@ -6379,7 +6346,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6396,7 +6363,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>6</v>
       </c>
@@ -6413,7 +6380,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>6</v>
       </c>
@@ -6430,7 +6397,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>7</v>
       </c>
@@ -6447,7 +6414,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
@@ -6464,7 +6431,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>7</v>
       </c>
@@ -6481,7 +6448,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>7</v>
       </c>
@@ -6498,7 +6465,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>7</v>
       </c>
@@ -6515,7 +6482,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>7</v>
       </c>
@@ -6532,7 +6499,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>7</v>
       </c>
@@ -6549,7 +6516,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>7</v>
       </c>
@@ -6566,7 +6533,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>7</v>
       </c>
@@ -6583,7 +6550,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>7</v>
       </c>
@@ -6600,7 +6567,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>7</v>
       </c>
@@ -6617,7 +6584,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>7</v>
       </c>
@@ -6634,7 +6601,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6651,7 +6618,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>7</v>
       </c>
@@ -6668,7 +6635,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -6685,7 +6652,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -6702,7 +6669,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -6719,7 +6686,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
@@ -6736,7 +6703,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>7</v>
       </c>
@@ -6753,7 +6720,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>7</v>
       </c>
@@ -6770,7 +6737,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>7</v>
       </c>
@@ -6787,7 +6754,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>7</v>
       </c>
@@ -6804,7 +6771,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>7</v>
       </c>
@@ -6821,7 +6788,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>7</v>
       </c>
@@ -6838,7 +6805,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>7</v>
       </c>
@@ -6855,7 +6822,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>8</v>
       </c>
@@ -6872,7 +6839,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>8</v>
       </c>
@@ -6889,7 +6856,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>8</v>
       </c>
@@ -6906,7 +6873,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>8</v>
       </c>
@@ -6923,7 +6890,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>8</v>
       </c>
@@ -6940,7 +6907,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8</v>
       </c>
@@ -6957,7 +6924,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>8</v>
       </c>
@@ -6974,7 +6941,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>8</v>
       </c>
@@ -6991,7 +6958,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>8</v>
       </c>
@@ -7008,7 +6975,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>8</v>
       </c>
@@ -7025,7 +6992,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>8</v>
       </c>
@@ -7042,7 +7009,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>8</v>
       </c>
@@ -7059,7 +7026,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>8</v>
       </c>
@@ -7076,7 +7043,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>8</v>
       </c>
@@ -7093,7 +7060,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>8</v>
       </c>
@@ -7110,7 +7077,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>8</v>
       </c>
@@ -7127,7 +7094,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>8</v>
       </c>
@@ -7144,7 +7111,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8</v>
       </c>
@@ -7161,7 +7128,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>8</v>
       </c>
@@ -7178,7 +7145,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>8</v>
       </c>
@@ -7195,7 +7162,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>8</v>
       </c>
@@ -7212,7 +7179,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7229,7 +7196,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>8</v>
       </c>
@@ -7246,7 +7213,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>8</v>
       </c>
@@ -7263,7 +7230,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>8</v>
       </c>
@@ -7280,7 +7247,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>9</v>
       </c>
@@ -7297,7 +7264,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>9</v>
       </c>
@@ -7314,7 +7281,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>9</v>
       </c>
@@ -7331,7 +7298,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>9</v>
       </c>
@@ -7348,7 +7315,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>9</v>
       </c>
@@ -7365,7 +7332,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9</v>
       </c>
@@ -7382,7 +7349,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>9</v>
       </c>
@@ -7399,7 +7366,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>9</v>
       </c>
@@ -7416,7 +7383,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>9</v>
       </c>
@@ -7433,7 +7400,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>9</v>
       </c>
@@ -7450,7 +7417,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>9</v>
       </c>
@@ -7467,7 +7434,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7484,7 +7451,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7501,7 +7468,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7518,7 +7485,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7535,7 +7502,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7552,7 +7519,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7569,7 +7536,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7586,7 +7553,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7603,7 +7570,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7620,7 +7587,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7637,7 +7604,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7654,7 +7621,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7671,7 +7638,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7688,7 +7655,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7705,7 +7672,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>10</v>
       </c>
@@ -7722,7 +7689,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>10</v>
       </c>
@@ -7739,7 +7706,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>10</v>
       </c>
@@ -7756,7 +7723,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>10</v>
       </c>
@@ -7773,7 +7740,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>10</v>
       </c>
@@ -7790,7 +7757,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10</v>
       </c>
@@ -7807,7 +7774,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>10</v>
       </c>
@@ -7824,7 +7791,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>10</v>
       </c>
@@ -7841,7 +7808,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>10</v>
       </c>
@@ -7858,7 +7825,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>10</v>
       </c>
@@ -7875,7 +7842,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>10</v>
       </c>
@@ -7892,7 +7859,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>10</v>
       </c>
@@ -7909,7 +7876,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>10</v>
       </c>
@@ -7926,7 +7893,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>10</v>
       </c>
@@ -7943,7 +7910,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>10</v>
       </c>
@@ -7960,7 +7927,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>10</v>
       </c>
@@ -7977,7 +7944,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>10</v>
       </c>
@@ -7994,7 +7961,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>10</v>
       </c>
@@ -8011,7 +7978,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>10</v>
       </c>
@@ -8028,7 +7995,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>10</v>
       </c>
@@ -8045,7 +8012,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>10</v>
       </c>
@@ -8062,7 +8029,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>10</v>
       </c>
@@ -8079,7 +8046,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>10</v>
       </c>
@@ -8096,7 +8063,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>10</v>
       </c>
@@ -8113,7 +8080,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>10</v>
       </c>
@@ -8130,7 +8097,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>11</v>
       </c>
@@ -8147,7 +8114,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>11</v>
       </c>
@@ -8164,7 +8131,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>11</v>
       </c>
@@ -8181,7 +8148,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>11</v>
       </c>
@@ -8198,7 +8165,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>11</v>
       </c>
@@ -8215,7 +8182,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>11</v>
       </c>
@@ -8232,7 +8199,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>11</v>
       </c>
@@ -8249,7 +8216,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>11</v>
       </c>
@@ -8266,7 +8233,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>11</v>
       </c>
@@ -8283,7 +8250,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>11</v>
       </c>
@@ -8300,7 +8267,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>11</v>
       </c>
@@ -8317,7 +8284,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>11</v>
       </c>
@@ -8334,7 +8301,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>11</v>
       </c>
@@ -8351,7 +8318,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>11</v>
       </c>
@@ -8368,7 +8335,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>11</v>
       </c>
@@ -8385,7 +8352,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>11</v>
       </c>
@@ -8402,7 +8369,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>11</v>
       </c>
@@ -8419,7 +8386,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>11</v>
       </c>
@@ -8436,7 +8403,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>11</v>
       </c>
@@ -8453,7 +8420,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>11</v>
       </c>
@@ -8470,7 +8437,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>11</v>
       </c>
@@ -8487,7 +8454,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>11</v>
       </c>
@@ -8504,7 +8471,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>11</v>
       </c>
@@ -8521,7 +8488,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>11</v>
       </c>
@@ -8538,7 +8505,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>11</v>
       </c>
@@ -8555,7 +8522,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>12</v>
       </c>
@@ -8572,7 +8539,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>12</v>
       </c>
@@ -8589,7 +8556,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>12</v>
       </c>
@@ -8606,7 +8573,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>12</v>
       </c>
@@ -8623,7 +8590,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>12</v>
       </c>
@@ -8640,7 +8607,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>12</v>
       </c>
@@ -8657,7 +8624,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>12</v>
       </c>
@@ -8674,7 +8641,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>12</v>
       </c>
@@ -8691,7 +8658,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>12</v>
       </c>
@@ -8708,7 +8675,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>12</v>
       </c>
@@ -8725,7 +8692,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>12</v>
       </c>
@@ -8742,7 +8709,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>12</v>
       </c>
@@ -8759,7 +8726,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>12</v>
       </c>
@@ -8776,7 +8743,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>12</v>
       </c>
@@ -8793,7 +8760,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>12</v>
       </c>
@@ -8810,7 +8777,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>12</v>
       </c>
@@ -8827,7 +8794,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>12</v>
       </c>
@@ -8844,7 +8811,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>12</v>
       </c>
@@ -8861,7 +8828,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>12</v>
       </c>
@@ -8878,7 +8845,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>12</v>
       </c>
@@ -8895,7 +8862,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>12</v>
       </c>
@@ -8912,7 +8879,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>12</v>
       </c>
@@ -8929,7 +8896,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>12</v>
       </c>
@@ -8946,7 +8913,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>12</v>
       </c>
@@ -8963,7 +8930,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>12</v>
       </c>
@@ -8980,7 +8947,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>13</v>
       </c>
@@ -8997,7 +8964,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>13</v>
       </c>
@@ -9014,7 +8981,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>13</v>
       </c>
@@ -9031,7 +8998,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>13</v>
       </c>
@@ -9048,7 +9015,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>13</v>
       </c>
@@ -9065,7 +9032,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>13</v>
       </c>
@@ -9082,7 +9049,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>13</v>
       </c>
@@ -9099,7 +9066,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>13</v>
       </c>
@@ -9116,7 +9083,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>13</v>
       </c>
@@ -9133,7 +9100,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>13</v>
       </c>
@@ -9150,7 +9117,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>13</v>
       </c>
@@ -9167,7 +9134,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>13</v>
       </c>
@@ -9184,7 +9151,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>13</v>
       </c>
@@ -9201,7 +9168,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>13</v>
       </c>
@@ -9218,7 +9185,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>13</v>
       </c>
@@ -9235,7 +9202,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>13</v>
       </c>
@@ -9252,7 +9219,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>13</v>
       </c>
@@ -9269,7 +9236,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>13</v>
       </c>
@@ -9286,7 +9253,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>13</v>
       </c>
@@ -9303,7 +9270,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>13</v>
       </c>
@@ -9320,7 +9287,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>13</v>
       </c>
@@ -9337,7 +9304,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>13</v>
       </c>
@@ -9354,7 +9321,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>13</v>
       </c>
@@ -9371,7 +9338,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>13</v>
       </c>
@@ -9388,7 +9355,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>13</v>
       </c>
@@ -9405,7 +9372,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>14</v>
       </c>
@@ -9422,7 +9389,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>14</v>
       </c>
@@ -9439,7 +9406,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>14</v>
       </c>
@@ -9456,7 +9423,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>14</v>
       </c>
@@ -9473,7 +9440,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>14</v>
       </c>
@@ -9490,7 +9457,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>14</v>
       </c>
@@ -9507,7 +9474,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>14</v>
       </c>
@@ -9524,7 +9491,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>14</v>
       </c>
@@ -9541,7 +9508,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>14</v>
       </c>
@@ -9558,7 +9525,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>14</v>
       </c>
@@ -9575,7 +9542,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>14</v>
       </c>
@@ -9592,7 +9559,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>14</v>
       </c>
@@ -9609,7 +9576,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>14</v>
       </c>
@@ -9626,7 +9593,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>14</v>
       </c>
@@ -9643,7 +9610,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>14</v>
       </c>
@@ -9660,7 +9627,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>14</v>
       </c>
@@ -9677,7 +9644,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>14</v>
       </c>
@@ -9694,7 +9661,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>14</v>
       </c>
@@ -9711,7 +9678,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>14</v>
       </c>
@@ -9728,7 +9695,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>14</v>
       </c>
@@ -9745,7 +9712,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>14</v>
       </c>
@@ -9762,7 +9729,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>14</v>
       </c>
@@ -9779,7 +9746,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>14</v>
       </c>
@@ -9796,7 +9763,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>14</v>
       </c>
@@ -9813,7 +9780,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>14</v>
       </c>
@@ -9830,7 +9797,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>15</v>
       </c>
@@ -9847,7 +9814,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>15</v>
       </c>
@@ -9864,7 +9831,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>15</v>
       </c>
@@ -9881,7 +9848,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>15</v>
       </c>
@@ -9898,7 +9865,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>15</v>
       </c>
@@ -9915,7 +9882,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>15</v>
       </c>
@@ -9932,7 +9899,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>15</v>
       </c>
@@ -9949,7 +9916,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>15</v>
       </c>
@@ -9966,7 +9933,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>15</v>
       </c>
@@ -9983,7 +9950,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>15</v>
       </c>
@@ -10000,7 +9967,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>15</v>
       </c>
@@ -10017,7 +9984,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>15</v>
       </c>
@@ -10034,7 +10001,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>15</v>
       </c>
@@ -10051,7 +10018,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>15</v>
       </c>
@@ -10068,7 +10035,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>15</v>
       </c>
@@ -10085,7 +10052,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>15</v>
       </c>
@@ -10102,7 +10069,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>15</v>
       </c>
@@ -10119,7 +10086,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>15</v>
       </c>
@@ -10136,7 +10103,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>15</v>
       </c>
@@ -10153,7 +10120,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>15</v>
       </c>
@@ -10170,7 +10137,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>15</v>
       </c>
@@ -10187,7 +10154,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>15</v>
       </c>
@@ -10204,7 +10171,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>15</v>
       </c>
@@ -10221,7 +10188,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>15</v>
       </c>
@@ -10238,7 +10205,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>15</v>
       </c>
@@ -10255,7 +10222,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>16</v>
       </c>
@@ -10272,7 +10239,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>16</v>
       </c>
@@ -10289,7 +10256,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>16</v>
       </c>
@@ -10306,7 +10273,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>16</v>
       </c>
@@ -10323,7 +10290,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>16</v>
       </c>
@@ -10340,7 +10307,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>16</v>
       </c>
@@ -10357,7 +10324,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>16</v>
       </c>
@@ -10374,7 +10341,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>16</v>
       </c>
@@ -10391,7 +10358,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>16</v>
       </c>
@@ -10408,7 +10375,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>16</v>
       </c>
@@ -10425,7 +10392,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>16</v>
       </c>
@@ -10442,7 +10409,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>16</v>
       </c>
@@ -10459,7 +10426,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>16</v>
       </c>
@@ -10476,7 +10443,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>16</v>
       </c>
@@ -10493,7 +10460,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>16</v>
       </c>
@@ -10510,7 +10477,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>16</v>
       </c>
@@ -10527,7 +10494,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>16</v>
       </c>
@@ -10544,7 +10511,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>16</v>
       </c>
@@ -10561,7 +10528,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>16</v>
       </c>
@@ -10578,7 +10545,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>16</v>
       </c>
@@ -10595,7 +10562,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>16</v>
       </c>
@@ -10612,7 +10579,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>16</v>
       </c>
@@ -10629,7 +10596,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>16</v>
       </c>
@@ -10646,7 +10613,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>16</v>
       </c>
@@ -10663,7 +10630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>16</v>
       </c>
@@ -10680,7 +10647,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10697,7 +10664,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>17</v>
       </c>
@@ -10714,7 +10681,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>17</v>
       </c>
@@ -10731,7 +10698,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>17</v>
       </c>
@@ -10748,7 +10715,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>17</v>
       </c>
@@ -10765,7 +10732,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>17</v>
       </c>
@@ -10782,7 +10749,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>17</v>
       </c>
@@ -10799,7 +10766,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>17</v>
       </c>
@@ -10816,7 +10783,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>17</v>
       </c>
@@ -10833,7 +10800,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>17</v>
       </c>
@@ -10850,7 +10817,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10867,7 +10834,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>17</v>
       </c>
@@ -10884,7 +10851,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>17</v>
       </c>
@@ -10901,7 +10868,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>17</v>
       </c>
@@ -10918,7 +10885,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>17</v>
       </c>
@@ -10935,7 +10902,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>17</v>
       </c>
@@ -10952,7 +10919,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>17</v>
       </c>
@@ -10969,7 +10936,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>17</v>
       </c>
@@ -10986,7 +10953,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>17</v>
       </c>
@@ -11003,7 +10970,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>17</v>
       </c>
@@ -11020,7 +10987,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>17</v>
       </c>
@@ -11037,7 +11004,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>17</v>
       </c>
@@ -11054,7 +11021,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>17</v>
       </c>
@@ -11071,7 +11038,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>17</v>
       </c>
@@ -11088,7 +11055,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>17</v>
       </c>
@@ -11105,7 +11072,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>18</v>
       </c>
@@ -11122,7 +11089,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>18</v>
       </c>
@@ -11139,7 +11106,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>18</v>
       </c>
@@ -11156,7 +11123,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>18</v>
       </c>
@@ -11173,7 +11140,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>18</v>
       </c>
@@ -11190,7 +11157,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>18</v>
       </c>
@@ -11207,7 +11174,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>18</v>
       </c>
@@ -11224,7 +11191,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>18</v>
       </c>
@@ -11241,7 +11208,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>18</v>
       </c>
@@ -11258,7 +11225,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>18</v>
       </c>
@@ -11275,7 +11242,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>18</v>
       </c>
@@ -11292,7 +11259,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>18</v>
       </c>
@@ -11309,7 +11276,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>18</v>
       </c>
@@ -11326,7 +11293,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>18</v>
       </c>
@@ -11343,7 +11310,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>18</v>
       </c>
@@ -11360,7 +11327,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>18</v>
       </c>
@@ -11377,7 +11344,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>18</v>
       </c>
@@ -11394,7 +11361,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>18</v>
       </c>
@@ -11411,7 +11378,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>18</v>
       </c>
@@ -11428,7 +11395,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>18</v>
       </c>
@@ -11445,7 +11412,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>18</v>
       </c>
@@ -11462,7 +11429,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>18</v>
       </c>
@@ -11479,7 +11446,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>18</v>
       </c>
@@ -11496,7 +11463,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>18</v>
       </c>
@@ -11513,7 +11480,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>18</v>
       </c>
@@ -11530,7 +11497,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>19</v>
       </c>
@@ -11547,7 +11514,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>19</v>
       </c>
@@ -11564,7 +11531,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>19</v>
       </c>
@@ -11581,7 +11548,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>19</v>
       </c>
@@ -11598,7 +11565,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>19</v>
       </c>
@@ -11615,7 +11582,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>19</v>
       </c>
@@ -11632,7 +11599,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>19</v>
       </c>
@@ -11649,7 +11616,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>19</v>
       </c>
@@ -11666,7 +11633,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>19</v>
       </c>
@@ -11683,7 +11650,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>19</v>
       </c>
@@ -11700,7 +11667,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>19</v>
       </c>
@@ -11717,7 +11684,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>19</v>
       </c>
@@ -11734,7 +11701,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>19</v>
       </c>
@@ -11751,7 +11718,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>19</v>
       </c>
@@ -11768,7 +11735,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>19</v>
       </c>
@@ -11785,7 +11752,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>19</v>
       </c>
@@ -11802,7 +11769,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>19</v>
       </c>
@@ -11819,7 +11786,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>19</v>
       </c>
@@ -11836,7 +11803,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>19</v>
       </c>
@@ -11853,7 +11820,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>19</v>
       </c>
@@ -11870,7 +11837,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>19</v>
       </c>
@@ -11887,7 +11854,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>19</v>
       </c>
@@ -11904,7 +11871,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>19</v>
       </c>
@@ -11921,7 +11888,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>19</v>
       </c>
@@ -11938,7 +11905,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>19</v>
       </c>

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16542C7B-15B1-4E99-BCCE-B1C26AEC06AC}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD154FBD-E387-408D-94C0-C5DEEA634DE8}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1296" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="362">
   <si>
     <t>Template Test Case</t>
   </si>
@@ -1109,6 +1109,12 @@
   </si>
   <si>
     <t>769.16</t>
+  </si>
+  <si>
+    <t>BOTDMS_011</t>
+  </si>
+  <si>
+    <t>BOTDMS_012</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1274,6 +1280,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1299,22 +1306,31 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1721,7 +1737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2025,6 +2041,12 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2036,9 +2058,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2055,6 +2074,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2374,7 +2397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DB19"/>
+  <dimension ref="A1:DB23"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
@@ -2757,28 +2780,28 @@
       </c>
     </row>
     <row r="4" spans="1:106" s="7" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="113" t="s">
+      <c r="N4" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="115"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116"/>
+      <c r="V4" s="116"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="116"/>
+      <c r="Y4" s="116"/>
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="116"/>
+      <c r="AE4" s="116"/>
+      <c r="AF4" s="116"/>
+      <c r="AG4" s="117"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2851,14 +2874,14 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="116" t="s">
+      <c r="CW4" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="116"/>
-      <c r="CY4" s="116"/>
-      <c r="CZ4" s="116"/>
-      <c r="DA4" s="116"/>
-      <c r="DB4" s="116"/>
+      <c r="CX4" s="118"/>
+      <c r="CY4" s="118"/>
+      <c r="CZ4" s="118"/>
+      <c r="DA4" s="118"/>
+      <c r="DB4" s="118"/>
     </row>
     <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
@@ -5382,7 +5405,7 @@
       <c r="BJ16" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="BK16" s="107"/>
+      <c r="BK16" s="113"/>
       <c r="BL16" s="83"/>
       <c r="BM16" s="107"/>
       <c r="BN16" s="83"/>
@@ -5575,7 +5598,7 @@
       <c r="BJ17" s="86" t="s">
         <v>187</v>
       </c>
-      <c r="BK17" s="111"/>
+      <c r="BK17" s="114"/>
       <c r="BL17" s="86"/>
       <c r="BM17" s="111"/>
       <c r="BN17" s="86"/>
@@ -5768,7 +5791,7 @@
       <c r="BJ18" s="90" t="s">
         <v>187</v>
       </c>
-      <c r="BK18" s="107"/>
+      <c r="BK18" s="113"/>
       <c r="BL18" s="90"/>
       <c r="BM18" s="107"/>
       <c r="BN18" s="90"/>
@@ -5829,7 +5852,7 @@
       <c r="J19" s="90"/>
       <c r="K19" s="90"/>
       <c r="L19" s="90"/>
-      <c r="M19" s="117"/>
+      <c r="M19" s="113"/>
       <c r="N19" s="107"/>
       <c r="O19" s="107"/>
       <c r="P19" s="90"/>
@@ -5891,7 +5914,7 @@
       <c r="BJ19" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="BK19" s="107"/>
+      <c r="BK19" s="113"/>
       <c r="BL19" s="90"/>
       <c r="BM19" s="107"/>
       <c r="BN19" s="90"/>
@@ -5929,11 +5952,32 @@
       <c r="CT19" s="99"/>
       <c r="CU19" s="99"/>
     </row>
+    <row r="20" spans="1:99" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="72" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:99" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="96" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:99" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="72" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:99" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="96" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="N4:AG4"/>
     <mergeCell ref="CW4:DB4"/>
   </mergeCells>
+  <phoneticPr fontId="31" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CW6:DB10" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16542C7B-15B1-4E99-BCCE-B1C26AEC06AC}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B22A1F-BF91-52E6-B2BC-B827D381FBB7}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1296" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -2025,6 +2025,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2036,9 +2039,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2055,6 +2055,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2757,28 +2761,28 @@
       </c>
     </row>
     <row r="4" spans="1:106" s="7" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="113" t="s">
+      <c r="N4" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="116"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2851,14 +2855,14 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="116" t="s">
+      <c r="CW4" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="116"/>
-      <c r="CY4" s="116"/>
-      <c r="CZ4" s="116"/>
-      <c r="DA4" s="116"/>
-      <c r="DB4" s="116"/>
+      <c r="CX4" s="117"/>
+      <c r="CY4" s="117"/>
+      <c r="CZ4" s="117"/>
+      <c r="DA4" s="117"/>
+      <c r="DB4" s="117"/>
     </row>
     <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
@@ -5829,7 +5833,7 @@
       <c r="J19" s="90"/>
       <c r="K19" s="90"/>
       <c r="L19" s="90"/>
-      <c r="M19" s="117"/>
+      <c r="M19" s="113"/>
       <c r="N19" s="107"/>
       <c r="O19" s="107"/>
       <c r="P19" s="90"/>
@@ -5934,7 +5938,7 @@
     <mergeCell ref="N4:AG4"/>
     <mergeCell ref="CW4:DB4"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CW6:DB10" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B22A1F-BF91-52E6-B2BC-B827D381FBB7}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE9510F7-D86D-4BCD-B4C1-0F5FAE124DEB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -1721,7 +1721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2027,6 +2027,9 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2379,89 +2382,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DB19"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="32.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" customWidth="1"/>
-    <col min="14" max="14" width="21.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" customWidth="1"/>
-    <col min="16" max="16" width="27.42578125" customWidth="1"/>
-    <col min="17" max="17" width="25.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" customWidth="1"/>
+    <col min="15" max="15" width="19.6640625" customWidth="1"/>
+    <col min="16" max="16" width="27.44140625" customWidth="1"/>
+    <col min="17" max="17" width="25.109375" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="21.7109375" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="31.140625" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" customWidth="1"/>
-    <col min="23" max="23" width="25.42578125" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" customWidth="1"/>
-    <col min="28" max="28" width="16.85546875" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" customWidth="1"/>
-    <col min="30" max="30" width="24.5703125" customWidth="1"/>
+    <col min="19" max="19" width="21.6640625" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="31.109375" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="25.44140625" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="14.88671875" customWidth="1"/>
+    <col min="27" max="27" width="15.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.88671875" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" customWidth="1"/>
+    <col min="30" max="30" width="24.5546875" customWidth="1"/>
     <col min="31" max="31" width="24" customWidth="1"/>
-    <col min="32" max="32" width="27.7109375" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" customWidth="1"/>
-    <col min="34" max="34" width="18.28515625" customWidth="1"/>
+    <col min="32" max="32" width="27.6640625" customWidth="1"/>
+    <col min="33" max="33" width="17.44140625" customWidth="1"/>
+    <col min="34" max="34" width="18.33203125" customWidth="1"/>
     <col min="35" max="35" width="24" customWidth="1"/>
-    <col min="36" max="36" width="16.28515625" customWidth="1"/>
+    <col min="36" max="36" width="16.33203125" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="27.42578125" customWidth="1"/>
-    <col min="39" max="39" width="21.42578125" customWidth="1"/>
-    <col min="40" max="40" width="15.28515625" customWidth="1"/>
+    <col min="38" max="38" width="27.44140625" customWidth="1"/>
+    <col min="39" max="39" width="21.44140625" customWidth="1"/>
+    <col min="40" max="40" width="15.33203125" customWidth="1"/>
     <col min="41" max="41" width="29" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="8.140625" customWidth="1"/>
+    <col min="43" max="43" width="8.109375" customWidth="1"/>
     <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="45" max="45" width="14.42578125" customWidth="1"/>
-    <col min="46" max="46" width="23.42578125" customWidth="1"/>
-    <col min="47" max="47" width="23.140625" customWidth="1"/>
-    <col min="48" max="48" width="17.42578125" customWidth="1"/>
-    <col min="49" max="49" width="14.140625" customWidth="1"/>
-    <col min="50" max="50" width="18.7109375" customWidth="1"/>
-    <col min="51" max="51" width="23.42578125" customWidth="1"/>
-    <col min="52" max="52" width="24.7109375" customWidth="1"/>
-    <col min="53" max="55" width="12.5703125" customWidth="1"/>
-    <col min="56" max="56" width="25.42578125" customWidth="1"/>
-    <col min="57" max="57" width="22.42578125" customWidth="1"/>
-    <col min="58" max="58" width="13.42578125" customWidth="1"/>
-    <col min="59" max="59" width="15.140625" customWidth="1"/>
-    <col min="60" max="60" width="13.42578125" customWidth="1"/>
-    <col min="61" max="61" width="14.42578125" customWidth="1"/>
-    <col min="62" max="62" width="15.42578125" customWidth="1"/>
-    <col min="63" max="63" width="17.85546875" customWidth="1"/>
-    <col min="64" max="64" width="12.5703125" customWidth="1"/>
-    <col min="65" max="65" width="27.42578125" customWidth="1"/>
-    <col min="66" max="66" width="24.42578125" customWidth="1"/>
-    <col min="67" max="73" width="12.5703125" customWidth="1"/>
-    <col min="74" max="74" width="27.42578125" customWidth="1"/>
-    <col min="75" max="75" width="24.42578125" customWidth="1"/>
-    <col min="76" max="87" width="12.5703125" customWidth="1"/>
-    <col min="88" max="88" width="15.7109375" customWidth="1"/>
-    <col min="89" max="95" width="12.5703125" customWidth="1"/>
-    <col min="96" max="96" width="15.7109375" customWidth="1"/>
-    <col min="97" max="97" width="17.7109375" customWidth="1"/>
-    <col min="98" max="98" width="19.5703125" customWidth="1"/>
+    <col min="45" max="45" width="14.44140625" customWidth="1"/>
+    <col min="46" max="46" width="23.44140625" customWidth="1"/>
+    <col min="47" max="47" width="23.109375" customWidth="1"/>
+    <col min="48" max="48" width="17.44140625" customWidth="1"/>
+    <col min="49" max="49" width="14.109375" customWidth="1"/>
+    <col min="50" max="50" width="18.6640625" customWidth="1"/>
+    <col min="51" max="51" width="23.44140625" customWidth="1"/>
+    <col min="52" max="52" width="24.6640625" customWidth="1"/>
+    <col min="53" max="55" width="12.5546875" customWidth="1"/>
+    <col min="56" max="56" width="25.44140625" customWidth="1"/>
+    <col min="57" max="57" width="22.44140625" customWidth="1"/>
+    <col min="58" max="58" width="13.44140625" customWidth="1"/>
+    <col min="59" max="59" width="15.109375" customWidth="1"/>
+    <col min="60" max="60" width="13.44140625" customWidth="1"/>
+    <col min="61" max="61" width="14.44140625" customWidth="1"/>
+    <col min="62" max="62" width="15.44140625" customWidth="1"/>
+    <col min="63" max="63" width="17.88671875" customWidth="1"/>
+    <col min="64" max="64" width="12.5546875" customWidth="1"/>
+    <col min="65" max="65" width="27.44140625" customWidth="1"/>
+    <col min="66" max="66" width="24.44140625" customWidth="1"/>
+    <col min="67" max="73" width="12.5546875" customWidth="1"/>
+    <col min="74" max="74" width="27.44140625" customWidth="1"/>
+    <col min="75" max="75" width="24.44140625" customWidth="1"/>
+    <col min="76" max="87" width="12.5546875" customWidth="1"/>
+    <col min="88" max="88" width="15.6640625" customWidth="1"/>
+    <col min="89" max="95" width="12.5546875" customWidth="1"/>
+    <col min="96" max="96" width="15.6640625" customWidth="1"/>
+    <col min="97" max="97" width="17.6640625" customWidth="1"/>
+    <col min="98" max="98" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:106" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2760,29 +2763,29 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="114" t="s">
+    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="115"/>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
-      <c r="AE4" s="115"/>
-      <c r="AF4" s="115"/>
-      <c r="AG4" s="116"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116"/>
+      <c r="V4" s="116"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="116"/>
+      <c r="Y4" s="116"/>
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="116"/>
+      <c r="AE4" s="116"/>
+      <c r="AF4" s="116"/>
+      <c r="AG4" s="117"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2855,16 +2858,16 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="117" t="s">
+      <c r="CW4" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="117"/>
-      <c r="CY4" s="117"/>
-      <c r="CZ4" s="117"/>
-      <c r="DA4" s="117"/>
-      <c r="DB4" s="117"/>
-    </row>
-    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CX4" s="118"/>
+      <c r="CY4" s="118"/>
+      <c r="CZ4" s="118"/>
+      <c r="DA4" s="118"/>
+      <c r="DB4" s="118"/>
+    </row>
+    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>7</v>
@@ -3179,7 +3182,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
       <c r="B6" s="36" t="s">
         <v>111</v>
@@ -3393,7 +3396,7 @@
       <c r="DA6" s="46"/>
       <c r="DB6" s="46"/>
     </row>
-    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
       <c r="B7" s="36" t="s">
         <v>150</v>
@@ -3601,7 +3604,7 @@
       <c r="DA7" s="42"/>
       <c r="DB7" s="42"/>
     </row>
-    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
       <c r="B8" s="36" t="s">
         <v>177</v>
@@ -3775,7 +3778,7 @@
       <c r="BU8" s="50"/>
       <c r="BV8" s="50"/>
       <c r="BW8" s="50"/>
-      <c r="BX8" s="50"/>
+      <c r="BX8" s="114"/>
       <c r="BY8" s="50"/>
       <c r="BZ8" s="50"/>
       <c r="CA8" s="50"/>
@@ -3806,7 +3809,7 @@
       <c r="DA8" s="42"/>
       <c r="DB8" s="42"/>
     </row>
-    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
       <c r="B9" s="36" t="s">
         <v>198</v>
@@ -3987,11 +3990,11 @@
       <c r="BS9" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="BT9" s="50"/>
+      <c r="BT9" s="114"/>
       <c r="BU9" s="50"/>
       <c r="BV9" s="50"/>
       <c r="BW9" s="50"/>
-      <c r="BX9" s="50"/>
+      <c r="BX9" s="114"/>
       <c r="BY9" s="50"/>
       <c r="BZ9" s="50"/>
       <c r="CA9" s="50"/>
@@ -4022,7 +4025,7 @@
       <c r="DA9" s="42"/>
       <c r="DB9" s="42"/>
     </row>
-    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
       <c r="B10" s="36" t="s">
         <v>217</v>
@@ -4159,7 +4162,7 @@
       <c r="DA10" s="42"/>
       <c r="DB10" s="42"/>
     </row>
-    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
       <c r="B11" s="67" t="s">
         <v>222</v>
@@ -4371,7 +4374,7 @@
       <c r="CT11" s="50"/>
       <c r="CU11" s="51"/>
     </row>
-    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="71"/>
       <c r="B12" s="72" t="s">
         <v>234</v>
@@ -4558,7 +4561,7 @@
       </c>
       <c r="BT12" s="50"/>
       <c r="BU12" s="50"/>
-      <c r="BV12" s="50"/>
+      <c r="BV12" s="114"/>
       <c r="BW12" s="50"/>
       <c r="BX12" s="50"/>
       <c r="BY12" s="50"/>
@@ -4585,7 +4588,7 @@
       <c r="CT12" s="50"/>
       <c r="CU12" s="51"/>
     </row>
-    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="71"/>
       <c r="B13" s="72" t="s">
         <v>243</v>
@@ -4772,8 +4775,8 @@
       </c>
       <c r="BT13" s="50"/>
       <c r="BU13" s="50"/>
-      <c r="BV13" s="50"/>
-      <c r="BW13" s="50"/>
+      <c r="BV13" s="114"/>
+      <c r="BW13" s="114"/>
       <c r="BX13" s="50"/>
       <c r="BY13" s="50"/>
       <c r="BZ13" s="50"/>
@@ -4799,7 +4802,7 @@
       <c r="CT13" s="50"/>
       <c r="CU13" s="51"/>
     </row>
-    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="71"/>
       <c r="B14" s="72" t="s">
         <v>250</v>
@@ -5011,7 +5014,7 @@
       <c r="CT14" s="50"/>
       <c r="CU14" s="51"/>
     </row>
-    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="71"/>
       <c r="B15" s="72" t="s">
         <v>256</v>
@@ -5229,7 +5232,7 @@
       <c r="CT15" s="50"/>
       <c r="CU15" s="51"/>
     </row>
-    <row r="16" spans="1:106" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:106" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="77"/>
       <c r="B16" s="72" t="s">
         <v>265</v>
@@ -5424,7 +5427,7 @@
       <c r="CT16" s="81"/>
       <c r="CU16" s="81"/>
     </row>
-    <row r="17" spans="1:99" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="82"/>
       <c r="B17" s="36" t="s">
         <v>273</v>
@@ -5617,7 +5620,7 @@
       <c r="CT17" s="81"/>
       <c r="CU17" s="81"/>
     </row>
-    <row r="18" spans="1:99" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="89"/>
       <c r="B18" s="72" t="s">
         <v>281</v>
@@ -5810,7 +5813,7 @@
       <c r="CT18" s="92"/>
       <c r="CU18" s="92"/>
     </row>
-    <row r="19" spans="1:99" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="89"/>
       <c r="B19" s="96" t="s">
         <v>287</v>
@@ -5950,7 +5953,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5959,7 +5962,7 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="102" t="s">
         <v>289</v>
       </c>
@@ -5976,7 +5979,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>6</v>
       </c>
@@ -5993,7 +5996,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>6</v>
       </c>
@@ -6010,7 +6013,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
@@ -6027,7 +6030,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>6</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -6061,7 +6064,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6078,7 +6081,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6095,7 +6098,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -6112,7 +6115,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6129,7 +6132,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -6146,7 +6149,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -6163,7 +6166,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
@@ -6180,7 +6183,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -6214,7 +6217,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
@@ -6231,7 +6234,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -6248,7 +6251,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -6265,7 +6268,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>6</v>
       </c>
@@ -6299,7 +6302,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6</v>
       </c>
@@ -6316,7 +6319,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6</v>
       </c>
@@ -6333,7 +6336,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>6</v>
       </c>
@@ -6350,7 +6353,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6367,7 +6370,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>6</v>
       </c>
@@ -6384,7 +6387,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -6401,7 +6404,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -6418,7 +6421,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -6435,7 +6438,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>7</v>
       </c>
@@ -6452,7 +6455,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>7</v>
       </c>
@@ -6469,7 +6472,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>7</v>
       </c>
@@ -6486,7 +6489,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -6503,7 +6506,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>7</v>
       </c>
@@ -6520,7 +6523,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>7</v>
       </c>
@@ -6537,7 +6540,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>7</v>
       </c>
@@ -6554,7 +6557,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>7</v>
       </c>
@@ -6571,7 +6574,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>7</v>
       </c>
@@ -6588,7 +6591,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>7</v>
       </c>
@@ -6605,7 +6608,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>7</v>
       </c>
@@ -6639,7 +6642,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>7</v>
       </c>
@@ -6656,7 +6659,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>7</v>
       </c>
@@ -6673,7 +6676,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>7</v>
       </c>
@@ -6690,7 +6693,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>7</v>
       </c>
@@ -6707,7 +6710,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>7</v>
       </c>
@@ -6724,7 +6727,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>7</v>
       </c>
@@ -6741,7 +6744,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>7</v>
       </c>
@@ -6758,7 +6761,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>7</v>
       </c>
@@ -6775,7 +6778,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>7</v>
       </c>
@@ -6792,7 +6795,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>7</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>7</v>
       </c>
@@ -6826,7 +6829,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>8</v>
       </c>
@@ -6843,7 +6846,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>8</v>
       </c>
@@ -6860,7 +6863,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>8</v>
       </c>
@@ -6877,7 +6880,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>8</v>
       </c>
@@ -6894,7 +6897,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>8</v>
       </c>
@@ -6911,7 +6914,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>8</v>
       </c>
@@ -6928,7 +6931,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>8</v>
       </c>
@@ -6945,7 +6948,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>8</v>
       </c>
@@ -6962,7 +6965,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>8</v>
       </c>
@@ -6979,7 +6982,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>8</v>
       </c>
@@ -6996,7 +6999,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>8</v>
       </c>
@@ -7013,7 +7016,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>8</v>
       </c>
@@ -7030,7 +7033,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>8</v>
       </c>
@@ -7047,7 +7050,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>8</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>8</v>
       </c>
@@ -7081,7 +7084,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>8</v>
       </c>
@@ -7098,7 +7101,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>8</v>
       </c>
@@ -7115,7 +7118,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -7132,7 +7135,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>8</v>
       </c>
@@ -7149,7 +7152,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>8</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -7183,7 +7186,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7200,7 +7203,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -7217,7 +7220,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8</v>
       </c>
@@ -7234,7 +7237,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8</v>
       </c>
@@ -7251,7 +7254,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9</v>
       </c>
@@ -7268,7 +7271,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9</v>
       </c>
@@ -7285,7 +7288,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>9</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>9</v>
       </c>
@@ -7319,7 +7322,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>9</v>
       </c>
@@ -7336,7 +7339,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -7353,7 +7356,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>9</v>
       </c>
@@ -7370,7 +7373,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>9</v>
       </c>
@@ -7387,7 +7390,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>9</v>
       </c>
@@ -7404,7 +7407,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>9</v>
       </c>
@@ -7421,7 +7424,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>9</v>
       </c>
@@ -7438,7 +7441,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7455,7 +7458,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7472,7 +7475,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7489,7 +7492,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7506,7 +7509,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7523,7 +7526,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7557,7 +7560,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7574,7 +7577,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7591,7 +7594,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7608,7 +7611,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7625,7 +7628,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7642,7 +7645,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7659,7 +7662,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7676,7 +7679,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10</v>
       </c>
@@ -7693,7 +7696,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10</v>
       </c>
@@ -7710,7 +7713,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10</v>
       </c>
@@ -7727,7 +7730,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10</v>
       </c>
@@ -7744,7 +7747,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>10</v>
       </c>
@@ -7761,7 +7764,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -7778,7 +7781,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>10</v>
       </c>
@@ -7795,7 +7798,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>10</v>
       </c>
@@ -7812,7 +7815,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>10</v>
       </c>
@@ -7829,7 +7832,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>10</v>
       </c>
@@ -7846,7 +7849,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>10</v>
       </c>
@@ -7863,7 +7866,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>10</v>
       </c>
@@ -7880,7 +7883,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>10</v>
       </c>
@@ -7897,7 +7900,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>10</v>
       </c>
@@ -7914,7 +7917,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>10</v>
       </c>
@@ -7931,7 +7934,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>10</v>
       </c>
@@ -7948,7 +7951,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>10</v>
       </c>
@@ -7965,7 +7968,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10</v>
       </c>
@@ -7982,7 +7985,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>10</v>
       </c>
@@ -7999,7 +8002,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>10</v>
       </c>
@@ -8016,7 +8019,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10</v>
       </c>
@@ -8033,7 +8036,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>10</v>
       </c>
@@ -8050,7 +8053,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>10</v>
       </c>
@@ -8067,7 +8070,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>10</v>
       </c>
@@ -8084,7 +8087,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>10</v>
       </c>
@@ -8101,7 +8104,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>11</v>
       </c>
@@ -8118,7 +8121,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>11</v>
       </c>
@@ -8135,7 +8138,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>11</v>
       </c>
@@ -8152,7 +8155,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>11</v>
       </c>
@@ -8169,7 +8172,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>11</v>
       </c>
@@ -8186,7 +8189,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>11</v>
       </c>
@@ -8203,7 +8206,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>11</v>
       </c>
@@ -8220,7 +8223,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>11</v>
       </c>
@@ -8237,7 +8240,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>11</v>
       </c>
@@ -8254,7 +8257,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>11</v>
       </c>
@@ -8271,7 +8274,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>11</v>
       </c>
@@ -8288,7 +8291,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>11</v>
       </c>
@@ -8305,7 +8308,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>11</v>
       </c>
@@ -8322,7 +8325,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>11</v>
       </c>
@@ -8339,7 +8342,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>11</v>
       </c>
@@ -8356,7 +8359,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>11</v>
       </c>
@@ -8373,7 +8376,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>11</v>
       </c>
@@ -8390,7 +8393,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>11</v>
       </c>
@@ -8407,7 +8410,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>11</v>
       </c>
@@ -8424,7 +8427,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>11</v>
       </c>
@@ -8441,7 +8444,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>11</v>
       </c>
@@ -8458,7 +8461,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>11</v>
       </c>
@@ -8475,7 +8478,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>11</v>
       </c>
@@ -8492,7 +8495,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>11</v>
       </c>
@@ -8509,7 +8512,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>11</v>
       </c>
@@ -8526,7 +8529,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>12</v>
       </c>
@@ -8543,7 +8546,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>12</v>
       </c>
@@ -8560,7 +8563,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>12</v>
       </c>
@@ -8577,7 +8580,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>12</v>
       </c>
@@ -8594,7 +8597,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>12</v>
       </c>
@@ -8611,7 +8614,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>12</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>12</v>
       </c>
@@ -8645,7 +8648,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>12</v>
       </c>
@@ -8662,7 +8665,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>12</v>
       </c>
@@ -8679,7 +8682,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>12</v>
       </c>
@@ -8696,7 +8699,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>12</v>
       </c>
@@ -8713,7 +8716,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>12</v>
       </c>
@@ -8730,7 +8733,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>12</v>
       </c>
@@ -8747,7 +8750,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>12</v>
       </c>
@@ -8764,7 +8767,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>12</v>
       </c>
@@ -8781,7 +8784,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>12</v>
       </c>
@@ -8798,7 +8801,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>12</v>
       </c>
@@ -8815,7 +8818,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>12</v>
       </c>
@@ -8832,7 +8835,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>12</v>
       </c>
@@ -8849,7 +8852,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>12</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>12</v>
       </c>
@@ -8883,7 +8886,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>12</v>
       </c>
@@ -8900,7 +8903,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>12</v>
       </c>
@@ -8917,7 +8920,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>12</v>
       </c>
@@ -8934,7 +8937,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>12</v>
       </c>
@@ -8951,7 +8954,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>13</v>
       </c>
@@ -8968,7 +8971,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>13</v>
       </c>
@@ -8985,7 +8988,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>13</v>
       </c>
@@ -9002,7 +9005,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>13</v>
       </c>
@@ -9019,7 +9022,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>13</v>
       </c>
@@ -9036,7 +9039,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>13</v>
       </c>
@@ -9053,7 +9056,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>13</v>
       </c>
@@ -9070,7 +9073,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>13</v>
       </c>
@@ -9087,7 +9090,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>13</v>
       </c>
@@ -9104,7 +9107,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>13</v>
       </c>
@@ -9121,7 +9124,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>13</v>
       </c>
@@ -9138,7 +9141,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>13</v>
       </c>
@@ -9155,7 +9158,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>13</v>
       </c>
@@ -9172,7 +9175,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>13</v>
       </c>
@@ -9189,7 +9192,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>13</v>
       </c>
@@ -9206,7 +9209,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>13</v>
       </c>
@@ -9223,7 +9226,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>13</v>
       </c>
@@ -9240,7 +9243,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>13</v>
       </c>
@@ -9257,7 +9260,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>13</v>
       </c>
@@ -9274,7 +9277,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>13</v>
       </c>
@@ -9291,7 +9294,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>13</v>
       </c>
@@ -9308,7 +9311,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>13</v>
       </c>
@@ -9325,7 +9328,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>13</v>
       </c>
@@ -9342,7 +9345,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>13</v>
       </c>
@@ -9359,7 +9362,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>13</v>
       </c>
@@ -9376,7 +9379,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>14</v>
       </c>
@@ -9393,7 +9396,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>14</v>
       </c>
@@ -9410,7 +9413,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>14</v>
       </c>
@@ -9427,7 +9430,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>14</v>
       </c>
@@ -9444,7 +9447,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>14</v>
       </c>
@@ -9461,7 +9464,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14</v>
       </c>
@@ -9478,7 +9481,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>14</v>
       </c>
@@ -9495,7 +9498,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>14</v>
       </c>
@@ -9512,7 +9515,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>14</v>
       </c>
@@ -9529,7 +9532,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>14</v>
       </c>
@@ -9546,7 +9549,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>14</v>
       </c>
@@ -9563,7 +9566,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>14</v>
       </c>
@@ -9580,7 +9583,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>14</v>
       </c>
@@ -9597,7 +9600,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>14</v>
       </c>
@@ -9614,7 +9617,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>14</v>
       </c>
@@ -9631,7 +9634,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>14</v>
       </c>
@@ -9648,7 +9651,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>14</v>
       </c>
@@ -9665,7 +9668,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>14</v>
       </c>
@@ -9682,7 +9685,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>14</v>
       </c>
@@ -9699,7 +9702,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>14</v>
       </c>
@@ -9716,7 +9719,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>14</v>
       </c>
@@ -9733,7 +9736,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>14</v>
       </c>
@@ -9750,7 +9753,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>14</v>
       </c>
@@ -9767,7 +9770,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>14</v>
       </c>
@@ -9784,7 +9787,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>14</v>
       </c>
@@ -9801,7 +9804,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>15</v>
       </c>
@@ -9818,7 +9821,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>15</v>
       </c>
@@ -9835,7 +9838,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>15</v>
       </c>
@@ -9852,7 +9855,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>15</v>
       </c>
@@ -9869,7 +9872,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>15</v>
       </c>
@@ -9886,7 +9889,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>15</v>
       </c>
@@ -9903,7 +9906,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>15</v>
       </c>
@@ -9920,7 +9923,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>15</v>
       </c>
@@ -9937,7 +9940,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>15</v>
       </c>
@@ -9954,7 +9957,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>15</v>
       </c>
@@ -9971,7 +9974,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>15</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>15</v>
       </c>
@@ -10005,7 +10008,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>15</v>
       </c>
@@ -10022,7 +10025,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>15</v>
       </c>
@@ -10039,7 +10042,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>15</v>
       </c>
@@ -10056,7 +10059,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>15</v>
       </c>
@@ -10073,7 +10076,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>15</v>
       </c>
@@ -10090,7 +10093,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>15</v>
       </c>
@@ -10107,7 +10110,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>15</v>
       </c>
@@ -10124,7 +10127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>15</v>
       </c>
@@ -10141,7 +10144,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>15</v>
       </c>
@@ -10158,7 +10161,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>15</v>
       </c>
@@ -10175,7 +10178,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>15</v>
       </c>
@@ -10192,7 +10195,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>15</v>
       </c>
@@ -10209,7 +10212,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>15</v>
       </c>
@@ -10226,7 +10229,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>16</v>
       </c>
@@ -10243,7 +10246,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>16</v>
       </c>
@@ -10260,7 +10263,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>16</v>
       </c>
@@ -10277,7 +10280,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>16</v>
       </c>
@@ -10294,7 +10297,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>16</v>
       </c>
@@ -10311,7 +10314,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>16</v>
       </c>
@@ -10328,7 +10331,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>16</v>
       </c>
@@ -10345,7 +10348,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>16</v>
       </c>
@@ -10362,7 +10365,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>16</v>
       </c>
@@ -10379,7 +10382,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>16</v>
       </c>
@@ -10396,7 +10399,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>16</v>
       </c>
@@ -10413,7 +10416,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>16</v>
       </c>
@@ -10430,7 +10433,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>16</v>
       </c>
@@ -10447,7 +10450,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>16</v>
       </c>
@@ -10464,7 +10467,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>16</v>
       </c>
@@ -10481,7 +10484,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>16</v>
       </c>
@@ -10498,7 +10501,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>16</v>
       </c>
@@ -10515,7 +10518,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>16</v>
       </c>
@@ -10532,7 +10535,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>16</v>
       </c>
@@ -10549,7 +10552,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>16</v>
       </c>
@@ -10566,7 +10569,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>16</v>
       </c>
@@ -10583,7 +10586,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>16</v>
       </c>
@@ -10600,7 +10603,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>16</v>
       </c>
@@ -10617,7 +10620,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>16</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>16</v>
       </c>
@@ -10651,7 +10654,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10668,7 +10671,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>17</v>
       </c>
@@ -10685,7 +10688,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>17</v>
       </c>
@@ -10702,7 +10705,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>17</v>
       </c>
@@ -10719,7 +10722,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>17</v>
       </c>
@@ -10736,7 +10739,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>17</v>
       </c>
@@ -10753,7 +10756,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>17</v>
       </c>
@@ -10770,7 +10773,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>17</v>
       </c>
@@ -10787,7 +10790,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>17</v>
       </c>
@@ -10804,7 +10807,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>17</v>
       </c>
@@ -10821,7 +10824,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10838,7 +10841,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>17</v>
       </c>
@@ -10855,7 +10858,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>17</v>
       </c>
@@ -10872,7 +10875,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>17</v>
       </c>
@@ -10889,7 +10892,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>17</v>
       </c>
@@ -10906,7 +10909,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>17</v>
       </c>
@@ -10923,7 +10926,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>17</v>
       </c>
@@ -10940,7 +10943,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>17</v>
       </c>
@@ -10957,7 +10960,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>17</v>
       </c>
@@ -10974,7 +10977,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>17</v>
       </c>
@@ -10991,7 +10994,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>17</v>
       </c>
@@ -11008,7 +11011,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>17</v>
       </c>
@@ -11025,7 +11028,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>17</v>
       </c>
@@ -11042,7 +11045,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>17</v>
       </c>
@@ -11059,7 +11062,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>17</v>
       </c>
@@ -11076,7 +11079,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>18</v>
       </c>
@@ -11093,7 +11096,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>18</v>
       </c>
@@ -11110,7 +11113,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>18</v>
       </c>
@@ -11127,7 +11130,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>18</v>
       </c>
@@ -11144,7 +11147,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>18</v>
       </c>
@@ -11161,7 +11164,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>18</v>
       </c>
@@ -11178,7 +11181,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>18</v>
       </c>
@@ -11195,7 +11198,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>18</v>
       </c>
@@ -11212,7 +11215,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>18</v>
       </c>
@@ -11229,7 +11232,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>18</v>
       </c>
@@ -11246,7 +11249,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>18</v>
       </c>
@@ -11263,7 +11266,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>18</v>
       </c>
@@ -11280,7 +11283,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>18</v>
       </c>
@@ -11297,7 +11300,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>18</v>
       </c>
@@ -11314,7 +11317,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>18</v>
       </c>
@@ -11331,7 +11334,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>18</v>
       </c>
@@ -11348,7 +11351,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>18</v>
       </c>
@@ -11365,7 +11368,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>18</v>
       </c>
@@ -11382,7 +11385,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>18</v>
       </c>
@@ -11399,7 +11402,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>18</v>
       </c>
@@ -11416,7 +11419,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>18</v>
       </c>
@@ -11433,7 +11436,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>18</v>
       </c>
@@ -11450,7 +11453,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>18</v>
       </c>
@@ -11467,7 +11470,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>18</v>
       </c>
@@ -11484,7 +11487,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>18</v>
       </c>
@@ -11501,7 +11504,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>19</v>
       </c>
@@ -11518,7 +11521,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>19</v>
       </c>
@@ -11535,7 +11538,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>19</v>
       </c>
@@ -11552,7 +11555,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>19</v>
       </c>
@@ -11569,7 +11572,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>19</v>
       </c>
@@ -11586,7 +11589,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>19</v>
       </c>
@@ -11603,7 +11606,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>19</v>
       </c>
@@ -11620,7 +11623,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>19</v>
       </c>
@@ -11637,7 +11640,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>19</v>
       </c>
@@ -11654,7 +11657,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>19</v>
       </c>
@@ -11671,7 +11674,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>19</v>
       </c>
@@ -11688,7 +11691,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>19</v>
       </c>
@@ -11705,7 +11708,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>19</v>
       </c>
@@ -11722,7 +11725,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>19</v>
       </c>
@@ -11739,7 +11742,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>19</v>
       </c>
@@ -11756,7 +11759,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>19</v>
       </c>
@@ -11773,7 +11776,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>19</v>
       </c>
@@ -11790,7 +11793,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>19</v>
       </c>
@@ -11807,7 +11810,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>19</v>
       </c>
@@ -11824,7 +11827,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>19</v>
       </c>
@@ -11841,7 +11844,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>19</v>
       </c>
@@ -11858,7 +11861,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>19</v>
       </c>
@@ -11875,7 +11878,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>19</v>
       </c>
@@ -11892,7 +11895,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>19</v>
       </c>
@@ -11909,7 +11912,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>19</v>
       </c>

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B22A1F-BF91-52E6-B2BC-B827D381FBB7}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CC01C36-C36C-43ED-BB85-10F8BAB08CE9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -1317,7 +1317,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1449,6 +1449,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1721,7 +1727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1903,9 +1909,6 @@
     <xf numFmtId="0" fontId="18" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1916,9 +1919,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1982,9 +1982,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2039,6 +2036,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2379,89 +2394,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DB19"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="32.453125" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" customWidth="1"/>
-    <col min="14" max="14" width="21.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" customWidth="1"/>
-    <col min="16" max="16" width="27.42578125" customWidth="1"/>
-    <col min="17" max="17" width="25.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="14" max="14" width="21.453125" customWidth="1"/>
+    <col min="15" max="15" width="19.7265625" customWidth="1"/>
+    <col min="16" max="16" width="27.453125" customWidth="1"/>
+    <col min="17" max="17" width="25.1796875" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="21.7109375" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="31.140625" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" customWidth="1"/>
-    <col min="23" max="23" width="25.42578125" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" customWidth="1"/>
-    <col min="28" max="28" width="16.85546875" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" customWidth="1"/>
-    <col min="30" max="30" width="24.5703125" customWidth="1"/>
+    <col min="19" max="19" width="21.7265625" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" customWidth="1"/>
+    <col min="21" max="21" width="31.1796875" customWidth="1"/>
+    <col min="22" max="22" width="16.453125" customWidth="1"/>
+    <col min="23" max="23" width="25.453125" customWidth="1"/>
+    <col min="24" max="24" width="8.453125" customWidth="1"/>
+    <col min="25" max="25" width="15.453125" customWidth="1"/>
+    <col min="26" max="26" width="14.81640625" customWidth="1"/>
+    <col min="27" max="27" width="15.453125" customWidth="1"/>
+    <col min="28" max="28" width="16.81640625" customWidth="1"/>
+    <col min="29" max="29" width="19.453125" customWidth="1"/>
+    <col min="30" max="30" width="24.54296875" customWidth="1"/>
     <col min="31" max="31" width="24" customWidth="1"/>
-    <col min="32" max="32" width="27.7109375" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" customWidth="1"/>
-    <col min="34" max="34" width="18.28515625" customWidth="1"/>
+    <col min="32" max="32" width="27.7265625" customWidth="1"/>
+    <col min="33" max="33" width="17.453125" customWidth="1"/>
+    <col min="34" max="34" width="18.26953125" customWidth="1"/>
     <col min="35" max="35" width="24" customWidth="1"/>
-    <col min="36" max="36" width="16.28515625" customWidth="1"/>
+    <col min="36" max="36" width="16.26953125" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="27.42578125" customWidth="1"/>
-    <col min="39" max="39" width="21.42578125" customWidth="1"/>
-    <col min="40" max="40" width="15.28515625" customWidth="1"/>
+    <col min="38" max="38" width="27.453125" customWidth="1"/>
+    <col min="39" max="39" width="21.453125" customWidth="1"/>
+    <col min="40" max="40" width="15.26953125" customWidth="1"/>
     <col min="41" max="41" width="29" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="8.140625" customWidth="1"/>
+    <col min="43" max="43" width="8.1796875" customWidth="1"/>
     <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="45" max="45" width="14.42578125" customWidth="1"/>
-    <col min="46" max="46" width="23.42578125" customWidth="1"/>
-    <col min="47" max="47" width="23.140625" customWidth="1"/>
-    <col min="48" max="48" width="17.42578125" customWidth="1"/>
-    <col min="49" max="49" width="14.140625" customWidth="1"/>
-    <col min="50" max="50" width="18.7109375" customWidth="1"/>
-    <col min="51" max="51" width="23.42578125" customWidth="1"/>
-    <col min="52" max="52" width="24.7109375" customWidth="1"/>
-    <col min="53" max="55" width="12.5703125" customWidth="1"/>
-    <col min="56" max="56" width="25.42578125" customWidth="1"/>
-    <col min="57" max="57" width="22.42578125" customWidth="1"/>
-    <col min="58" max="58" width="13.42578125" customWidth="1"/>
-    <col min="59" max="59" width="15.140625" customWidth="1"/>
-    <col min="60" max="60" width="13.42578125" customWidth="1"/>
-    <col min="61" max="61" width="14.42578125" customWidth="1"/>
-    <col min="62" max="62" width="15.42578125" customWidth="1"/>
-    <col min="63" max="63" width="17.85546875" customWidth="1"/>
-    <col min="64" max="64" width="12.5703125" customWidth="1"/>
-    <col min="65" max="65" width="27.42578125" customWidth="1"/>
-    <col min="66" max="66" width="24.42578125" customWidth="1"/>
-    <col min="67" max="73" width="12.5703125" customWidth="1"/>
-    <col min="74" max="74" width="27.42578125" customWidth="1"/>
-    <col min="75" max="75" width="24.42578125" customWidth="1"/>
-    <col min="76" max="87" width="12.5703125" customWidth="1"/>
-    <col min="88" max="88" width="15.7109375" customWidth="1"/>
-    <col min="89" max="95" width="12.5703125" customWidth="1"/>
-    <col min="96" max="96" width="15.7109375" customWidth="1"/>
-    <col min="97" max="97" width="17.7109375" customWidth="1"/>
-    <col min="98" max="98" width="19.5703125" customWidth="1"/>
+    <col min="45" max="45" width="14.453125" customWidth="1"/>
+    <col min="46" max="46" width="23.453125" customWidth="1"/>
+    <col min="47" max="47" width="23.1796875" customWidth="1"/>
+    <col min="48" max="48" width="17.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.1796875" customWidth="1"/>
+    <col min="50" max="50" width="18.7265625" customWidth="1"/>
+    <col min="51" max="51" width="23.453125" customWidth="1"/>
+    <col min="52" max="52" width="24.7265625" customWidth="1"/>
+    <col min="53" max="55" width="12.54296875" customWidth="1"/>
+    <col min="56" max="56" width="25.453125" customWidth="1"/>
+    <col min="57" max="57" width="22.453125" customWidth="1"/>
+    <col min="58" max="58" width="13.453125" customWidth="1"/>
+    <col min="59" max="59" width="15.1796875" customWidth="1"/>
+    <col min="60" max="60" width="13.453125" customWidth="1"/>
+    <col min="61" max="61" width="14.453125" customWidth="1"/>
+    <col min="62" max="62" width="15.453125" customWidth="1"/>
+    <col min="63" max="63" width="17.81640625" customWidth="1"/>
+    <col min="64" max="64" width="12.54296875" customWidth="1"/>
+    <col min="65" max="65" width="27.453125" customWidth="1"/>
+    <col min="66" max="66" width="24.453125" customWidth="1"/>
+    <col min="67" max="73" width="12.54296875" customWidth="1"/>
+    <col min="74" max="74" width="27.453125" customWidth="1"/>
+    <col min="75" max="75" width="24.453125" customWidth="1"/>
+    <col min="76" max="87" width="12.54296875" customWidth="1"/>
+    <col min="88" max="88" width="15.7265625" customWidth="1"/>
+    <col min="89" max="95" width="12.54296875" customWidth="1"/>
+    <col min="96" max="96" width="15.7265625" customWidth="1"/>
+    <col min="97" max="97" width="17.7265625" customWidth="1"/>
+    <col min="98" max="98" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2760,29 +2775,29 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="114" t="s">
+    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N4" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="115"/>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
-      <c r="AE4" s="115"/>
-      <c r="AF4" s="115"/>
-      <c r="AG4" s="116"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="113"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2855,16 +2870,16 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="117" t="s">
+      <c r="CW4" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="117"/>
-      <c r="CY4" s="117"/>
-      <c r="CZ4" s="117"/>
-      <c r="DA4" s="117"/>
-      <c r="DB4" s="117"/>
-    </row>
-    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CX4" s="114"/>
+      <c r="CY4" s="114"/>
+      <c r="CZ4" s="114"/>
+      <c r="DA4" s="114"/>
+      <c r="DB4" s="114"/>
+    </row>
+    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>7</v>
@@ -3179,9 +3194,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35"/>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="115" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="37" t="s">
@@ -3193,7 +3208,7 @@
       <c r="E6" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="118" t="s">
         <v>115</v>
       </c>
       <c r="G6" s="38" t="s">
@@ -3294,7 +3309,7 @@
       <c r="AO6" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="AP6" s="109"/>
+      <c r="AP6" s="106"/>
       <c r="AQ6" s="38"/>
       <c r="AR6" s="38"/>
       <c r="AS6" s="38"/>
@@ -3302,7 +3317,7 @@
         <v>145</v>
       </c>
       <c r="AU6" s="38"/>
-      <c r="AV6" s="109"/>
+      <c r="AV6" s="106"/>
       <c r="AW6" s="38" t="s">
         <v>134</v>
       </c>
@@ -3393,9 +3408,9 @@
       <c r="DA6" s="46"/>
       <c r="DB6" s="46"/>
     </row>
-    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="35"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="115" t="s">
         <v>150</v>
       </c>
       <c r="C7" s="37" t="s">
@@ -3407,7 +3422,7 @@
       <c r="E7" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="118" t="s">
         <v>153</v>
       </c>
       <c r="G7" s="38" t="s">
@@ -3508,7 +3523,7 @@
       <c r="AO7" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="AP7" s="109"/>
+      <c r="AP7" s="106"/>
       <c r="AQ7" s="38"/>
       <c r="AR7" s="38"/>
       <c r="AS7" s="38"/>
@@ -3516,7 +3531,7 @@
         <v>145</v>
       </c>
       <c r="AU7" s="38"/>
-      <c r="AV7" s="109"/>
+      <c r="AV7" s="106"/>
       <c r="AW7" s="38" t="s">
         <v>174</v>
       </c>
@@ -3551,7 +3566,7 @@
       <c r="BJ7" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="BK7" s="109"/>
+      <c r="BK7" s="106"/>
       <c r="BL7" s="38" t="s">
         <v>147</v>
       </c>
@@ -3564,7 +3579,7 @@
       <c r="BO7" s="50"/>
       <c r="BP7" s="50"/>
       <c r="BQ7" s="50"/>
-      <c r="BR7" s="109"/>
+      <c r="BR7" s="106"/>
       <c r="BS7" s="38"/>
       <c r="BT7" s="50"/>
       <c r="BU7" s="50"/>
@@ -3601,9 +3616,9 @@
       <c r="DA7" s="42"/>
       <c r="DB7" s="42"/>
     </row>
-    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35"/>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="115" t="s">
         <v>177</v>
       </c>
       <c r="C8" s="52" t="s">
@@ -3615,7 +3630,7 @@
       <c r="E8" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="118" t="s">
         <v>180</v>
       </c>
       <c r="G8" s="38" t="s">
@@ -3713,7 +3728,7 @@
       <c r="AO8" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="AP8" s="109"/>
+      <c r="AP8" s="106"/>
       <c r="AQ8" s="38"/>
       <c r="AR8" s="38"/>
       <c r="AS8" s="38"/>
@@ -3721,7 +3736,7 @@
         <v>145</v>
       </c>
       <c r="AU8" s="38"/>
-      <c r="AV8" s="109"/>
+      <c r="AV8" s="106"/>
       <c r="AW8" s="38" t="s">
         <v>165</v>
       </c>
@@ -3756,7 +3771,7 @@
       <c r="BJ8" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="BK8" s="109"/>
+      <c r="BK8" s="106"/>
       <c r="BL8" s="38" t="s">
         <v>147</v>
       </c>
@@ -3769,7 +3784,7 @@
       <c r="BO8" s="50"/>
       <c r="BP8" s="50"/>
       <c r="BQ8" s="50"/>
-      <c r="BR8" s="109"/>
+      <c r="BR8" s="106"/>
       <c r="BS8" s="38"/>
       <c r="BT8" s="50"/>
       <c r="BU8" s="50"/>
@@ -3806,9 +3821,9 @@
       <c r="DA8" s="42"/>
       <c r="DB8" s="42"/>
     </row>
-    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="35"/>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="115" t="s">
         <v>198</v>
       </c>
       <c r="C9" s="37" t="s">
@@ -3820,7 +3835,7 @@
       <c r="E9" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="119" t="s">
         <v>201</v>
       </c>
       <c r="G9" s="38" t="s">
@@ -3923,7 +3938,7 @@
       <c r="AO9" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="AP9" s="109"/>
+      <c r="AP9" s="106"/>
       <c r="AQ9" s="38"/>
       <c r="AR9" s="38"/>
       <c r="AS9" s="38"/>
@@ -3931,7 +3946,7 @@
         <v>145</v>
       </c>
       <c r="AU9" s="38"/>
-      <c r="AV9" s="109"/>
+      <c r="AV9" s="106"/>
       <c r="AW9" s="38" t="s">
         <v>174</v>
       </c>
@@ -4022,9 +4037,9 @@
       <c r="DA9" s="42"/>
       <c r="DB9" s="42"/>
     </row>
-    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35"/>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="115" t="s">
         <v>217</v>
       </c>
       <c r="C10" s="54" t="s">
@@ -4036,7 +4051,7 @@
       <c r="E10" s="55">
         <v>0.74733796296277433</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="120" t="s">
         <v>219</v>
       </c>
       <c r="G10" s="57"/>
@@ -4047,32 +4062,32 @@
       <c r="J10" s="59"/>
       <c r="K10" s="59"/>
       <c r="L10" s="59"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="103"/>
       <c r="P10" s="59"/>
       <c r="Q10" s="59"/>
-      <c r="R10" s="106"/>
+      <c r="R10" s="103"/>
       <c r="S10" s="60" t="s">
         <v>220</v>
       </c>
       <c r="T10" s="59"/>
-      <c r="U10" s="106"/>
+      <c r="U10" s="103"/>
       <c r="V10" s="59"/>
       <c r="W10" s="59"/>
       <c r="X10" s="59"/>
-      <c r="Y10" s="106"/>
+      <c r="Y10" s="103"/>
       <c r="Z10" s="59"/>
       <c r="AA10" s="61" t="s">
         <v>139</v>
       </c>
       <c r="AB10" s="59"/>
-      <c r="AC10" s="108"/>
+      <c r="AC10" s="105"/>
       <c r="AD10" s="56">
         <v>0</v>
       </c>
       <c r="AE10" s="59"/>
-      <c r="AF10" s="106"/>
+      <c r="AF10" s="103"/>
       <c r="AG10" s="59"/>
       <c r="AH10" s="62">
         <v>0.32</v>
@@ -4082,29 +4097,29 @@
       </c>
       <c r="AJ10" s="59"/>
       <c r="AK10" s="59"/>
-      <c r="AL10" s="106"/>
+      <c r="AL10" s="103"/>
       <c r="AM10" s="59"/>
       <c r="AN10" s="59"/>
       <c r="AO10" s="63">
         <v>7775014694</v>
       </c>
-      <c r="AP10" s="106"/>
+      <c r="AP10" s="103"/>
       <c r="AQ10" s="59"/>
       <c r="AR10" s="59"/>
       <c r="AS10" s="59"/>
       <c r="AT10" s="59"/>
       <c r="AU10" s="59"/>
-      <c r="AV10" s="106"/>
+      <c r="AV10" s="103"/>
       <c r="AW10" s="59" t="s">
         <v>139</v>
       </c>
       <c r="AX10" s="59"/>
-      <c r="AY10" s="106"/>
-      <c r="AZ10" s="106"/>
+      <c r="AY10" s="103"/>
+      <c r="AZ10" s="103"/>
       <c r="BA10" s="42"/>
-      <c r="BB10" s="112"/>
+      <c r="BB10" s="109"/>
       <c r="BC10" s="59"/>
-      <c r="BD10" s="112"/>
+      <c r="BD10" s="109"/>
       <c r="BE10" s="50"/>
       <c r="BF10" s="49"/>
       <c r="BG10" s="49"/>
@@ -4115,14 +4130,14 @@
       <c r="BJ10" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="BK10" s="106"/>
+      <c r="BK10" s="103"/>
       <c r="BL10" s="59"/>
-      <c r="BM10" s="106"/>
+      <c r="BM10" s="103"/>
       <c r="BN10" s="50"/>
       <c r="BO10" s="50"/>
       <c r="BP10" s="50"/>
       <c r="BQ10" s="50"/>
-      <c r="BR10" s="106"/>
+      <c r="BR10" s="103"/>
       <c r="BS10" s="59"/>
       <c r="BT10" s="50"/>
       <c r="BU10" s="50"/>
@@ -4159,39 +4174,39 @@
       <c r="DA10" s="42"/>
       <c r="DB10" s="42"/>
     </row>
-    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="66"/>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="116" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="67" t="s">
         <v>223</v>
       </c>
       <c r="D11" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="69">
+      <c r="E11" s="68">
         <v>0.46600694444350665</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="81" t="s">
         <v>225</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="I11" s="68" t="s">
+      <c r="I11" s="67" t="s">
         <v>224</v>
       </c>
-      <c r="J11" s="68" t="s">
+      <c r="J11" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="K11" s="68" t="s">
+      <c r="K11" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="L11" s="68" t="s">
+      <c r="L11" s="67" t="s">
         <v>119</v>
       </c>
       <c r="M11" s="61" t="s">
@@ -4203,10 +4218,10 @@
       <c r="O11" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="P11" s="68" t="s">
+      <c r="P11" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="Q11" s="68" t="s">
+      <c r="Q11" s="67" t="s">
         <v>124</v>
       </c>
       <c r="R11" s="61" t="s">
@@ -4215,31 +4230,31 @@
       <c r="S11" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="T11" s="68">
+      <c r="T11" s="67">
         <v>983031158</v>
       </c>
       <c r="U11" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="V11" s="68">
+      <c r="V11" s="67">
         <v>600</v>
       </c>
-      <c r="W11" s="68" t="s">
+      <c r="W11" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="X11" s="68" t="s">
+      <c r="X11" s="67" t="s">
         <v>131</v>
       </c>
       <c r="Y11" s="61">
         <v>318004</v>
       </c>
-      <c r="Z11" s="68" t="s">
+      <c r="Z11" s="67" t="s">
         <v>230</v>
       </c>
       <c r="AA11" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="AB11" s="68">
+      <c r="AB11" s="67">
         <v>0.88989130000000005</v>
       </c>
       <c r="AC11" s="47">
@@ -4248,55 +4263,55 @@
       <c r="AD11" s="61">
         <v>86.46</v>
       </c>
-      <c r="AE11" s="70">
+      <c r="AE11" s="69">
         <f>+AC11-AD11</f>
         <v>9.6000000000000085</v>
       </c>
       <c r="AF11" s="61">
         <v>3216.92</v>
       </c>
-      <c r="AG11" s="68" t="s">
+      <c r="AG11" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AH11" s="68">
+      <c r="AH11" s="67">
         <v>76.94</v>
       </c>
-      <c r="AI11" s="68" t="s">
+      <c r="AI11" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="AJ11" s="68">
+      <c r="AJ11" s="67">
         <v>155.97</v>
       </c>
-      <c r="AK11" s="68" t="s">
+      <c r="AK11" s="67" t="s">
         <v>228</v>
       </c>
       <c r="AL11" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="AM11" s="68" t="s">
+      <c r="AM11" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AN11" s="68" t="s">
+      <c r="AN11" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="AO11" s="68">
+      <c r="AO11" s="67">
         <v>1233321</v>
       </c>
-      <c r="AP11" s="107"/>
-      <c r="AQ11" s="68"/>
-      <c r="AR11" s="68" t="s">
+      <c r="AP11" s="104"/>
+      <c r="AQ11" s="67"/>
+      <c r="AR11" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AS11" s="68"/>
-      <c r="AT11" s="68" t="s">
+      <c r="AS11" s="67"/>
+      <c r="AT11" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AU11" s="68"/>
-      <c r="AV11" s="107"/>
-      <c r="AW11" s="68" t="s">
+      <c r="AU11" s="67"/>
+      <c r="AV11" s="104"/>
+      <c r="AW11" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="AX11" s="68">
+      <c r="AX11" s="67">
         <v>0.88989130000000005</v>
       </c>
       <c r="AY11" s="61">
@@ -4309,7 +4324,7 @@
       <c r="BB11" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="BC11" s="68" t="s">
+      <c r="BC11" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BD11" s="61" t="s">
@@ -4324,11 +4339,11 @@
       <c r="BI11" s="61">
         <v>9.6</v>
       </c>
-      <c r="BJ11" s="68" t="s">
+      <c r="BJ11" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="BK11" s="107"/>
-      <c r="BL11" s="68" t="s">
+      <c r="BK11" s="104"/>
+      <c r="BL11" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BM11" s="61" t="s">
@@ -4340,8 +4355,8 @@
       <c r="BO11" s="50"/>
       <c r="BP11" s="50"/>
       <c r="BQ11" s="50"/>
-      <c r="BR11" s="107"/>
-      <c r="BS11" s="68"/>
+      <c r="BR11" s="104"/>
+      <c r="BS11" s="67"/>
       <c r="BT11" s="50"/>
       <c r="BU11" s="50"/>
       <c r="BV11" s="50"/>
@@ -4371,39 +4386,39 @@
       <c r="CT11" s="50"/>
       <c r="CU11" s="51"/>
     </row>
-    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72" t="s">
+    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="70"/>
+      <c r="B12" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="71" t="s">
         <v>235</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="69">
+      <c r="E12" s="68">
         <v>0.55619212962847087</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="H12" s="68" t="s">
+      <c r="H12" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="J12" s="68" t="s">
+      <c r="J12" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="K12" s="68" t="s">
+      <c r="K12" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="L12" s="68" t="s">
+      <c r="L12" s="67" t="s">
         <v>119</v>
       </c>
       <c r="M12" s="61" t="s">
@@ -4415,10 +4430,10 @@
       <c r="O12" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="P12" s="68" t="s">
+      <c r="P12" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="Q12" s="68" t="s">
+      <c r="Q12" s="67" t="s">
         <v>124</v>
       </c>
       <c r="R12" s="61" t="s">
@@ -4427,31 +4442,31 @@
       <c r="S12" s="61">
         <v>7775009485</v>
       </c>
-      <c r="T12" s="68">
+      <c r="T12" s="67">
         <v>983031158</v>
       </c>
       <c r="U12" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="V12" s="68">
+      <c r="V12" s="67">
         <v>606</v>
       </c>
-      <c r="W12" s="68" t="s">
+      <c r="W12" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="X12" s="68" t="s">
+      <c r="X12" s="67" t="s">
         <v>131</v>
       </c>
       <c r="Y12" s="61">
         <v>318033</v>
       </c>
-      <c r="Z12" s="68" t="s">
+      <c r="Z12" s="67" t="s">
         <v>240</v>
       </c>
       <c r="AA12" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="AB12" s="68">
+      <c r="AB12" s="67">
         <v>1.1533477000000001</v>
       </c>
       <c r="AC12" s="47">
@@ -4460,55 +4475,55 @@
       <c r="AD12" s="61">
         <v>13.89</v>
       </c>
-      <c r="AE12" s="70">
+      <c r="AE12" s="69">
         <f>+AC12-AD12</f>
         <v>9.3000000000000007</v>
       </c>
       <c r="AF12" s="61">
         <v>525.23</v>
       </c>
-      <c r="AG12" s="68" t="s">
+      <c r="AG12" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AH12" s="68">
+      <c r="AH12" s="67">
         <v>16.02</v>
       </c>
-      <c r="AI12" s="68" t="s">
+      <c r="AI12" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="AJ12" s="68">
+      <c r="AJ12" s="67">
         <v>156.03</v>
       </c>
-      <c r="AK12" s="68" t="s">
+      <c r="AK12" s="67" t="s">
         <v>228</v>
       </c>
       <c r="AL12" s="61" t="s">
         <v>241</v>
       </c>
-      <c r="AM12" s="68">
+      <c r="AM12" s="67">
         <v>40</v>
       </c>
-      <c r="AN12" s="68" t="s">
+      <c r="AN12" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="AO12" s="68">
+      <c r="AO12" s="67">
         <v>1234567</v>
       </c>
-      <c r="AP12" s="107"/>
-      <c r="AQ12" s="68"/>
-      <c r="AR12" s="68" t="s">
+      <c r="AP12" s="104"/>
+      <c r="AQ12" s="67"/>
+      <c r="AR12" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AS12" s="68"/>
-      <c r="AT12" s="68" t="s">
+      <c r="AS12" s="67"/>
+      <c r="AT12" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AU12" s="68"/>
-      <c r="AV12" s="107"/>
-      <c r="AW12" s="68" t="s">
+      <c r="AU12" s="67"/>
+      <c r="AV12" s="104"/>
+      <c r="AW12" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="AX12" s="68">
+      <c r="AX12" s="67">
         <v>1.1533477000000001</v>
       </c>
       <c r="AY12" s="61">
@@ -4521,7 +4536,7 @@
       <c r="BB12" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="BC12" s="68" t="s">
+      <c r="BC12" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BD12" s="61" t="s">
@@ -4536,11 +4551,11 @@
       <c r="BI12" s="61">
         <v>9.3000000000000007</v>
       </c>
-      <c r="BJ12" s="74" t="s">
+      <c r="BJ12" s="72" t="s">
         <v>231</v>
       </c>
-      <c r="BK12" s="107"/>
-      <c r="BL12" s="68" t="s">
+      <c r="BK12" s="104"/>
+      <c r="BL12" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BM12" s="61" t="s">
@@ -4552,8 +4567,8 @@
       <c r="BO12" s="50"/>
       <c r="BP12" s="50"/>
       <c r="BQ12" s="50"/>
-      <c r="BR12" s="107"/>
-      <c r="BS12" s="68" t="s">
+      <c r="BR12" s="104"/>
+      <c r="BS12" s="67" t="s">
         <v>228</v>
       </c>
       <c r="BT12" s="50"/>
@@ -4585,39 +4600,39 @@
       <c r="CT12" s="50"/>
       <c r="CU12" s="51"/>
     </row>
-    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72" t="s">
+    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="70"/>
+      <c r="B13" s="75" t="s">
         <v>243</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="73" t="s">
         <v>244</v>
       </c>
       <c r="D13" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="74">
         <v>0.46855324074203963</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="76" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="75" t="s">
+      <c r="G13" s="73" t="s">
         <v>246</v>
       </c>
-      <c r="H13" s="75" t="s">
+      <c r="H13" s="73" t="s">
         <v>247</v>
       </c>
-      <c r="I13" s="75" t="s">
+      <c r="I13" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="J13" s="75" t="s">
+      <c r="J13" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="K13" s="75" t="s">
+      <c r="K13" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="L13" s="75" t="s">
+      <c r="L13" s="73" t="s">
         <v>119</v>
       </c>
       <c r="M13" s="60" t="s">
@@ -4629,10 +4644,10 @@
       <c r="O13" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="P13" s="75" t="s">
+      <c r="P13" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="Q13" s="75" t="s">
+      <c r="Q13" s="73" t="s">
         <v>124</v>
       </c>
       <c r="R13" s="60" t="s">
@@ -4641,31 +4656,31 @@
       <c r="S13" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="T13" s="75">
+      <c r="T13" s="73">
         <v>983031158</v>
       </c>
       <c r="U13" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="V13" s="75">
+      <c r="V13" s="73">
         <v>600</v>
       </c>
-      <c r="W13" s="75" t="s">
+      <c r="W13" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="X13" s="75" t="s">
+      <c r="X13" s="73" t="s">
         <v>131</v>
       </c>
       <c r="Y13" s="60">
         <v>318024</v>
       </c>
-      <c r="Z13" s="75" t="s">
+      <c r="Z13" s="73" t="s">
         <v>248</v>
       </c>
       <c r="AA13" s="60" t="s">
         <v>231</v>
       </c>
-      <c r="AB13" s="75">
+      <c r="AB13" s="73">
         <v>1.0564150999999999</v>
       </c>
       <c r="AC13" s="47">
@@ -4674,55 +4689,55 @@
       <c r="AD13" s="60">
         <v>425.95</v>
       </c>
-      <c r="AE13" s="70">
+      <c r="AE13" s="69">
         <f>+AC13-AD13</f>
         <v>9.6000000000000227</v>
       </c>
       <c r="AF13" s="60">
         <v>15848.34</v>
       </c>
-      <c r="AG13" s="75" t="s">
+      <c r="AG13" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AH13" s="75">
+      <c r="AH13" s="73">
         <v>449.98</v>
       </c>
-      <c r="AI13" s="75" t="s">
+      <c r="AI13" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="AJ13" s="75">
+      <c r="AJ13" s="73">
         <v>7.7781000000000002</v>
       </c>
-      <c r="AK13" s="75" t="s">
+      <c r="AK13" s="73" t="s">
         <v>228</v>
       </c>
       <c r="AL13" s="60" t="s">
         <v>249</v>
       </c>
-      <c r="AM13" s="75" t="s">
+      <c r="AM13" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AN13" s="75" t="s">
+      <c r="AN13" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="AO13" s="75">
+      <c r="AO13" s="73">
         <v>5643234</v>
       </c>
-      <c r="AP13" s="110"/>
-      <c r="AQ13" s="75"/>
-      <c r="AR13" s="75" t="s">
+      <c r="AP13" s="107"/>
+      <c r="AQ13" s="73"/>
+      <c r="AR13" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AS13" s="75"/>
-      <c r="AT13" s="75" t="s">
+      <c r="AS13" s="73"/>
+      <c r="AT13" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="AU13" s="75"/>
-      <c r="AV13" s="110"/>
-      <c r="AW13" s="75" t="s">
+      <c r="AU13" s="73"/>
+      <c r="AV13" s="107"/>
+      <c r="AW13" s="73" t="s">
         <v>134</v>
       </c>
-      <c r="AX13" s="75">
+      <c r="AX13" s="73">
         <v>1.0564150999999999</v>
       </c>
       <c r="AY13" s="60">
@@ -4735,7 +4750,7 @@
       <c r="BB13" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="BC13" s="75" t="s">
+      <c r="BC13" s="73" t="s">
         <v>147</v>
       </c>
       <c r="BD13" s="60" t="s">
@@ -4750,11 +4765,11 @@
       <c r="BI13" s="60">
         <v>9.6</v>
       </c>
-      <c r="BJ13" s="75" t="s">
+      <c r="BJ13" s="73" t="s">
         <v>231</v>
       </c>
-      <c r="BK13" s="110"/>
-      <c r="BL13" s="75" t="s">
+      <c r="BK13" s="107"/>
+      <c r="BL13" s="73" t="s">
         <v>147</v>
       </c>
       <c r="BM13" s="60" t="s">
@@ -4766,8 +4781,8 @@
       <c r="BO13" s="50"/>
       <c r="BP13" s="50"/>
       <c r="BQ13" s="50"/>
-      <c r="BR13" s="107"/>
-      <c r="BS13" s="68" t="s">
+      <c r="BR13" s="104"/>
+      <c r="BS13" s="67" t="s">
         <v>228</v>
       </c>
       <c r="BT13" s="50"/>
@@ -4799,39 +4814,39 @@
       <c r="CT13" s="50"/>
       <c r="CU13" s="51"/>
     </row>
-    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72" t="s">
+    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="70"/>
+      <c r="B14" s="75" t="s">
         <v>250</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="71" t="s">
         <v>251</v>
       </c>
       <c r="D14" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="68">
         <v>0.56629629629605915</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="81" t="s">
         <v>252</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="67" t="s">
         <v>253</v>
       </c>
-      <c r="H14" s="68" t="s">
+      <c r="H14" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="I14" s="68" t="s">
+      <c r="I14" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="J14" s="68" t="s">
+      <c r="J14" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="K14" s="68" t="s">
+      <c r="K14" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="L14" s="68" t="s">
+      <c r="L14" s="67" t="s">
         <v>119</v>
       </c>
       <c r="M14" s="61" t="s">
@@ -4843,10 +4858,10 @@
       <c r="O14" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="68" t="s">
+      <c r="P14" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="Q14" s="68" t="s">
+      <c r="Q14" s="67" t="s">
         <v>124</v>
       </c>
       <c r="R14" s="61" t="s">
@@ -4855,31 +4870,31 @@
       <c r="S14" s="61">
         <v>7775009485</v>
       </c>
-      <c r="T14" s="68">
+      <c r="T14" s="67">
         <v>983031158</v>
       </c>
       <c r="U14" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="V14" s="68">
+      <c r="V14" s="67">
         <v>606</v>
       </c>
-      <c r="W14" s="68" t="s">
+      <c r="W14" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="X14" s="68" t="s">
+      <c r="X14" s="67" t="s">
         <v>131</v>
       </c>
       <c r="Y14" s="61">
         <v>318033</v>
       </c>
-      <c r="Z14" s="68" t="s">
+      <c r="Z14" s="67" t="s">
         <v>240</v>
       </c>
       <c r="AA14" s="61" t="s">
         <v>231</v>
       </c>
-      <c r="AB14" s="68">
+      <c r="AB14" s="67">
         <v>1.1532137</v>
       </c>
       <c r="AC14" s="47">
@@ -4888,55 +4903,55 @@
       <c r="AD14" s="61">
         <v>166.63</v>
       </c>
-      <c r="AE14" s="70">
+      <c r="AE14" s="69">
         <f>+AC14-AD14</f>
         <v>9.3000000000000114</v>
       </c>
       <c r="AF14" s="61">
         <v>6300.88</v>
       </c>
-      <c r="AG14" s="68" t="s">
+      <c r="AG14" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AH14" s="68">
+      <c r="AH14" s="67">
         <v>192.16</v>
       </c>
-      <c r="AI14" s="68" t="s">
+      <c r="AI14" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="AJ14" s="68">
+      <c r="AJ14" s="67">
         <v>156.12</v>
       </c>
-      <c r="AK14" s="68" t="s">
+      <c r="AK14" s="67" t="s">
         <v>228</v>
       </c>
       <c r="AL14" s="61" t="s">
         <v>255</v>
       </c>
-      <c r="AM14" s="68">
+      <c r="AM14" s="67">
         <v>40</v>
       </c>
-      <c r="AN14" s="68" t="s">
+      <c r="AN14" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="AO14" s="68">
+      <c r="AO14" s="67">
         <v>1234567</v>
       </c>
-      <c r="AP14" s="107"/>
-      <c r="AQ14" s="68"/>
-      <c r="AR14" s="68" t="s">
+      <c r="AP14" s="104"/>
+      <c r="AQ14" s="67"/>
+      <c r="AR14" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="AS14" s="68"/>
-      <c r="AT14" s="68" t="s">
+      <c r="AS14" s="67"/>
+      <c r="AT14" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AU14" s="68"/>
-      <c r="AV14" s="107"/>
-      <c r="AW14" s="68" t="s">
+      <c r="AU14" s="67"/>
+      <c r="AV14" s="104"/>
+      <c r="AW14" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="AX14" s="68">
+      <c r="AX14" s="67">
         <v>1.1532137</v>
       </c>
       <c r="AY14" s="61">
@@ -4949,7 +4964,7 @@
       <c r="BB14" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="BC14" s="68" t="s">
+      <c r="BC14" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BD14" s="61" t="s">
@@ -4964,11 +4979,11 @@
       <c r="BI14" s="61">
         <v>9.3000000000000007</v>
       </c>
-      <c r="BJ14" s="68" t="s">
+      <c r="BJ14" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="BK14" s="107"/>
-      <c r="BL14" s="68" t="s">
+      <c r="BK14" s="104"/>
+      <c r="BL14" s="67" t="s">
         <v>147</v>
       </c>
       <c r="BM14" s="61" t="s">
@@ -4980,8 +4995,8 @@
       <c r="BO14" s="50"/>
       <c r="BP14" s="50"/>
       <c r="BQ14" s="50"/>
-      <c r="BR14" s="107"/>
-      <c r="BS14" s="68"/>
+      <c r="BR14" s="104"/>
+      <c r="BS14" s="67"/>
       <c r="BT14" s="50"/>
       <c r="BU14" s="50"/>
       <c r="BV14" s="50"/>
@@ -5011,39 +5026,39 @@
       <c r="CT14" s="50"/>
       <c r="CU14" s="51"/>
     </row>
-    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
-      <c r="B15" s="72" t="s">
+    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="70"/>
+      <c r="B15" s="75" t="s">
         <v>256</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="71" t="s">
         <v>257</v>
       </c>
       <c r="D15" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="74">
         <v>0.7070138888884685</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="76" t="s">
         <v>258</v>
       </c>
-      <c r="G15" s="75" t="s">
+      <c r="G15" s="73" t="s">
         <v>259</v>
       </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="73" t="s">
         <v>260</v>
       </c>
-      <c r="I15" s="75" t="s">
+      <c r="I15" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="J15" s="75" t="s">
+      <c r="J15" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="K15" s="75" t="s">
+      <c r="K15" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="L15" s="75" t="s">
+      <c r="L15" s="73" t="s">
         <v>119</v>
       </c>
       <c r="M15" s="60" t="s">
@@ -5055,10 +5070,10 @@
       <c r="O15" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="P15" s="75" t="s">
+      <c r="P15" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="Q15" s="75" t="s">
+      <c r="Q15" s="73" t="s">
         <v>124</v>
       </c>
       <c r="R15" s="60" t="s">
@@ -5067,31 +5082,31 @@
       <c r="S15" s="60">
         <v>7775011241</v>
       </c>
-      <c r="T15" s="75">
+      <c r="T15" s="73">
         <v>983031158</v>
       </c>
       <c r="U15" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="V15" s="75">
+      <c r="V15" s="73">
         <v>903</v>
       </c>
-      <c r="W15" s="75" t="s">
+      <c r="W15" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="X15" s="75" t="s">
+      <c r="X15" s="73" t="s">
         <v>131</v>
       </c>
       <c r="Y15" s="60">
         <v>318033</v>
       </c>
-      <c r="Z15" s="75" t="s">
+      <c r="Z15" s="73" t="s">
         <v>240</v>
       </c>
       <c r="AA15" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="AB15" s="75" t="s">
+      <c r="AB15" s="73" t="s">
         <v>228</v>
       </c>
       <c r="AC15" s="47">
@@ -5100,55 +5115,55 @@
       <c r="AD15" s="60">
         <v>120</v>
       </c>
-      <c r="AE15" s="70">
+      <c r="AE15" s="69">
         <f>+AC15-AD15</f>
         <v>26.189999999999998</v>
       </c>
       <c r="AF15" s="60">
         <v>3894.96</v>
       </c>
-      <c r="AG15" s="75" t="s">
+      <c r="AG15" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AH15" s="75">
+      <c r="AH15" s="73">
         <v>120</v>
       </c>
-      <c r="AI15" s="75" t="s">
+      <c r="AI15" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="AJ15" s="75">
+      <c r="AJ15" s="73">
         <v>1</v>
       </c>
-      <c r="AK15" s="75" t="s">
+      <c r="AK15" s="73" t="s">
         <v>228</v>
       </c>
       <c r="AL15" s="60" t="s">
         <v>262</v>
       </c>
-      <c r="AM15" s="75" t="s">
+      <c r="AM15" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AN15" s="75" t="s">
+      <c r="AN15" s="73" t="s">
         <v>263</v>
       </c>
-      <c r="AO15" s="75">
+      <c r="AO15" s="73">
         <v>1234567</v>
       </c>
-      <c r="AP15" s="110"/>
-      <c r="AQ15" s="75"/>
-      <c r="AR15" s="75" t="s">
+      <c r="AP15" s="107"/>
+      <c r="AQ15" s="73"/>
+      <c r="AR15" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="AS15" s="75"/>
-      <c r="AT15" s="75" t="s">
+      <c r="AS15" s="73"/>
+      <c r="AT15" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="AU15" s="75"/>
-      <c r="AV15" s="110"/>
-      <c r="AW15" s="75" t="s">
+      <c r="AU15" s="73"/>
+      <c r="AV15" s="107"/>
+      <c r="AW15" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="AX15" s="75" t="s">
+      <c r="AX15" s="73" t="s">
         <v>228</v>
       </c>
       <c r="AY15" s="60">
@@ -5161,7 +5176,7 @@
       <c r="BB15" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="BC15" s="75" t="s">
+      <c r="BC15" s="73" t="s">
         <v>147</v>
       </c>
       <c r="BD15" s="60" t="s">
@@ -5176,13 +5191,13 @@
       <c r="BI15" s="60">
         <v>10.78</v>
       </c>
-      <c r="BJ15" s="75" t="s">
+      <c r="BJ15" s="73" t="s">
         <v>139</v>
       </c>
       <c r="BK15" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="BL15" s="75" t="s">
+      <c r="BL15" s="73" t="s">
         <v>147</v>
       </c>
       <c r="BM15" s="60" t="s">
@@ -5197,7 +5212,7 @@
       <c r="BR15" s="60">
         <v>15.41</v>
       </c>
-      <c r="BS15" s="75" t="s">
+      <c r="BS15" s="73" t="s">
         <v>139</v>
       </c>
       <c r="BT15" s="50"/>
@@ -5229,37 +5244,37 @@
       <c r="CT15" s="50"/>
       <c r="CU15" s="51"/>
     </row>
-    <row r="16" spans="1:106" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
-      <c r="B16" s="72" t="s">
+    <row r="16" spans="1:106" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="75"/>
+      <c r="B16" s="75" t="s">
         <v>265</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="76" t="s">
         <v>266</v>
       </c>
       <c r="D16" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="77">
         <v>0.47150462962963502</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="76" t="s">
         <v>267</v>
       </c>
-      <c r="G16" s="78" t="s">
+      <c r="G16" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="H16" s="78" t="s">
+      <c r="H16" s="76" t="s">
         <v>269</v>
       </c>
-      <c r="I16" s="78" t="s">
+      <c r="I16" s="76" t="s">
         <v>224</v>
       </c>
-      <c r="J16" s="78" t="s">
+      <c r="J16" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78" t="s">
+      <c r="K16" s="76"/>
+      <c r="L16" s="76" t="s">
         <v>119</v>
       </c>
       <c r="M16" s="60" t="s">
@@ -5271,10 +5286,10 @@
       <c r="O16" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="P16" s="78" t="s">
+      <c r="P16" s="76" t="s">
         <v>123</v>
       </c>
-      <c r="Q16" s="78" t="s">
+      <c r="Q16" s="76" t="s">
         <v>124</v>
       </c>
       <c r="R16" s="60" t="s">
@@ -5283,31 +5298,31 @@
       <c r="S16" s="60">
         <v>19673860</v>
       </c>
-      <c r="T16" s="78">
+      <c r="T16" s="76">
         <v>983031158</v>
       </c>
       <c r="U16" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="V16" s="78">
+      <c r="V16" s="76">
         <v>600</v>
       </c>
-      <c r="W16" s="78" t="s">
+      <c r="W16" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="X16" s="78" t="s">
+      <c r="X16" s="76" t="s">
         <v>131</v>
       </c>
       <c r="Y16" s="60">
         <v>318025</v>
       </c>
-      <c r="Z16" s="78" t="s">
+      <c r="Z16" s="76" t="s">
         <v>270</v>
       </c>
       <c r="AA16" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="AB16" s="78">
+      <c r="AB16" s="76">
         <v>37.700000000000003</v>
       </c>
       <c r="AC16" s="47">
@@ -5316,48 +5331,48 @@
       <c r="AD16" s="60">
         <v>15080</v>
       </c>
-      <c r="AE16" s="80">
+      <c r="AE16" s="78">
         <v>350</v>
       </c>
       <c r="AF16" s="60">
         <v>15080</v>
       </c>
-      <c r="AG16" s="78"/>
-      <c r="AH16" s="78">
+      <c r="AG16" s="76"/>
+      <c r="AH16" s="76">
         <v>400</v>
       </c>
-      <c r="AI16" s="78" t="s">
+      <c r="AI16" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="AJ16" s="78">
+      <c r="AJ16" s="76">
         <v>1</v>
       </c>
-      <c r="AK16" s="78"/>
+      <c r="AK16" s="76"/>
       <c r="AL16" s="60" t="s">
         <v>271</v>
       </c>
-      <c r="AM16" s="78"/>
-      <c r="AN16" s="78" t="s">
+      <c r="AM16" s="76"/>
+      <c r="AN16" s="76" t="s">
         <v>272</v>
       </c>
-      <c r="AO16" s="78">
+      <c r="AO16" s="76">
         <v>7776665</v>
       </c>
-      <c r="AP16" s="110"/>
-      <c r="AQ16" s="81"/>
-      <c r="AR16" s="81"/>
-      <c r="AS16" s="81"/>
-      <c r="AT16" s="78" t="s">
+      <c r="AP16" s="107"/>
+      <c r="AQ16" s="79"/>
+      <c r="AR16" s="79"/>
+      <c r="AS16" s="79"/>
+      <c r="AT16" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="AU16" s="78"/>
+      <c r="AU16" s="76"/>
       <c r="AV16" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="AW16" s="78" t="s">
+      <c r="AW16" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="AX16" s="78">
+      <c r="AX16" s="76">
         <v>37.700000000000003</v>
       </c>
       <c r="AY16" s="60">
@@ -5366,288 +5381,288 @@
       <c r="AZ16" s="60">
         <v>15080</v>
       </c>
-      <c r="BA16" s="78"/>
+      <c r="BA16" s="76"/>
       <c r="BB16" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="BC16" s="78" t="s">
+      <c r="BC16" s="76" t="s">
         <v>147</v>
       </c>
       <c r="BD16" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="BE16" s="81"/>
-      <c r="BF16" s="81"/>
-      <c r="BG16" s="81"/>
-      <c r="BH16" s="82"/>
+      <c r="BE16" s="79"/>
+      <c r="BF16" s="79"/>
+      <c r="BG16" s="79"/>
+      <c r="BH16" s="80"/>
       <c r="BI16" s="60">
         <v>350</v>
       </c>
-      <c r="BJ16" s="78" t="s">
+      <c r="BJ16" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="BK16" s="107"/>
-      <c r="BL16" s="83"/>
-      <c r="BM16" s="107"/>
-      <c r="BN16" s="83"/>
-      <c r="BO16" s="83"/>
-      <c r="BP16" s="78"/>
-      <c r="BQ16" s="78"/>
-      <c r="BR16" s="110"/>
-      <c r="BS16" s="78"/>
-      <c r="BT16" s="82"/>
-      <c r="BU16" s="78"/>
-      <c r="BV16" s="78"/>
-      <c r="BW16" s="81"/>
-      <c r="BX16" s="84"/>
-      <c r="BY16" s="85"/>
-      <c r="BZ16" s="85"/>
-      <c r="CA16" s="85"/>
-      <c r="CB16" s="85"/>
-      <c r="CC16" s="85"/>
-      <c r="CD16" s="81"/>
-      <c r="CE16" s="81"/>
-      <c r="CF16" s="81"/>
-      <c r="CG16" s="81"/>
-      <c r="CH16" s="81"/>
-      <c r="CI16" s="81"/>
-      <c r="CJ16" s="81"/>
-      <c r="CK16" s="81"/>
-      <c r="CL16" s="81"/>
-      <c r="CM16" s="81"/>
-      <c r="CN16" s="81"/>
-      <c r="CO16" s="81"/>
-      <c r="CP16" s="81"/>
-      <c r="CQ16" s="81"/>
-      <c r="CR16" s="81"/>
-      <c r="CS16" s="81"/>
-      <c r="CT16" s="81"/>
-      <c r="CU16" s="81"/>
-    </row>
-    <row r="17" spans="1:99" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="82"/>
-      <c r="B17" s="36" t="s">
+      <c r="BK16" s="104"/>
+      <c r="BL16" s="81"/>
+      <c r="BM16" s="104"/>
+      <c r="BN16" s="81"/>
+      <c r="BO16" s="81"/>
+      <c r="BP16" s="76"/>
+      <c r="BQ16" s="76"/>
+      <c r="BR16" s="107"/>
+      <c r="BS16" s="76"/>
+      <c r="BT16" s="80"/>
+      <c r="BU16" s="76"/>
+      <c r="BV16" s="76"/>
+      <c r="BW16" s="79"/>
+      <c r="BX16" s="82"/>
+      <c r="BY16" s="83"/>
+      <c r="BZ16" s="83"/>
+      <c r="CA16" s="83"/>
+      <c r="CB16" s="83"/>
+      <c r="CC16" s="83"/>
+      <c r="CD16" s="79"/>
+      <c r="CE16" s="79"/>
+      <c r="CF16" s="79"/>
+      <c r="CG16" s="79"/>
+      <c r="CH16" s="79"/>
+      <c r="CI16" s="79"/>
+      <c r="CJ16" s="79"/>
+      <c r="CK16" s="79"/>
+      <c r="CL16" s="79"/>
+      <c r="CM16" s="79"/>
+      <c r="CN16" s="79"/>
+      <c r="CO16" s="79"/>
+      <c r="CP16" s="79"/>
+      <c r="CQ16" s="79"/>
+      <c r="CR16" s="79"/>
+      <c r="CS16" s="79"/>
+      <c r="CT16" s="79"/>
+      <c r="CU16" s="79"/>
+    </row>
+    <row r="17" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="80"/>
+      <c r="B17" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="87" t="s">
+      <c r="D17" s="85" t="s">
         <v>224</v>
       </c>
-      <c r="E17" s="88">
+      <c r="E17" s="86">
         <v>0.69283564814759302</v>
       </c>
-      <c r="F17" s="87" t="s">
+      <c r="F17" s="84" t="s">
         <v>275</v>
       </c>
-      <c r="G17" s="86" t="s">
+      <c r="G17" s="84" t="s">
         <v>276</v>
       </c>
-      <c r="H17" s="86" t="s">
+      <c r="H17" s="84" t="s">
         <v>277</v>
       </c>
-      <c r="I17" s="86" t="s">
+      <c r="I17" s="84" t="s">
         <v>224</v>
       </c>
-      <c r="J17" s="86" t="s">
+      <c r="J17" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86" t="s">
+      <c r="K17" s="84"/>
+      <c r="L17" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="M17" s="87" t="s">
+      <c r="M17" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="N17" s="87">
+      <c r="N17" s="85">
         <v>23057027</v>
       </c>
-      <c r="O17" s="87" t="s">
+      <c r="O17" s="85" t="s">
         <v>158</v>
       </c>
-      <c r="P17" s="86" t="s">
+      <c r="P17" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="Q17" s="86" t="s">
+      <c r="Q17" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="R17" s="87" t="s">
+      <c r="R17" s="85" t="s">
         <v>183</v>
       </c>
-      <c r="S17" s="87">
+      <c r="S17" s="85">
         <v>19586907</v>
       </c>
-      <c r="T17" s="86">
+      <c r="T17" s="84">
         <v>983031158</v>
       </c>
-      <c r="U17" s="87" t="s">
+      <c r="U17" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="V17" s="86">
+      <c r="V17" s="84">
         <v>606</v>
       </c>
-      <c r="W17" s="86" t="s">
+      <c r="W17" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="X17" s="86" t="s">
+      <c r="X17" s="84" t="s">
         <v>131</v>
       </c>
-      <c r="Y17" s="87">
+      <c r="Y17" s="85">
         <v>318033</v>
       </c>
-      <c r="Z17" s="86" t="s">
+      <c r="Z17" s="84" t="s">
         <v>240</v>
       </c>
-      <c r="AA17" s="87" t="s">
+      <c r="AA17" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="AB17" s="86">
+      <c r="AB17" s="84">
         <v>33.883566999999999</v>
       </c>
       <c r="AC17" s="47">
         <v>3830.52</v>
       </c>
-      <c r="AD17" s="87">
+      <c r="AD17" s="85">
         <v>3480.52</v>
       </c>
-      <c r="AE17" s="86"/>
-      <c r="AF17" s="87">
+      <c r="AE17" s="84"/>
+      <c r="AF17" s="85">
         <v>3480.52</v>
       </c>
-      <c r="AG17" s="86"/>
-      <c r="AH17" s="86">
+      <c r="AG17" s="84"/>
+      <c r="AH17" s="84">
         <v>102.72</v>
       </c>
-      <c r="AI17" s="86" t="s">
+      <c r="AI17" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="AJ17" s="86">
+      <c r="AJ17" s="84">
         <v>1.5382</v>
       </c>
-      <c r="AK17" s="86"/>
-      <c r="AL17" s="87" t="s">
+      <c r="AK17" s="84"/>
+      <c r="AL17" s="85" t="s">
         <v>278</v>
       </c>
-      <c r="AM17" s="86"/>
-      <c r="AN17" s="86" t="s">
+      <c r="AM17" s="84"/>
+      <c r="AN17" s="84" t="s">
         <v>279</v>
       </c>
-      <c r="AO17" s="86">
+      <c r="AO17" s="84">
         <v>6767679</v>
       </c>
-      <c r="AP17" s="111"/>
-      <c r="AQ17" s="81"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="86" t="s">
+      <c r="AP17" s="108"/>
+      <c r="AQ17" s="79"/>
+      <c r="AR17" s="79"/>
+      <c r="AS17" s="79"/>
+      <c r="AT17" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="AU17" s="86"/>
-      <c r="AV17" s="87" t="s">
+      <c r="AU17" s="84"/>
+      <c r="AV17" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="AW17" s="86" t="s">
+      <c r="AW17" s="84" t="s">
         <v>165</v>
       </c>
-      <c r="AX17" s="86">
+      <c r="AX17" s="84">
         <v>33.883566999999999</v>
       </c>
-      <c r="AY17" s="87">
+      <c r="AY17" s="85">
         <v>158</v>
       </c>
-      <c r="AZ17" s="87">
+      <c r="AZ17" s="85">
         <v>3480.52</v>
       </c>
-      <c r="BA17" s="86"/>
-      <c r="BB17" s="87" t="s">
+      <c r="BA17" s="84"/>
+      <c r="BB17" s="85" t="s">
         <v>146</v>
       </c>
-      <c r="BC17" s="86" t="s">
+      <c r="BC17" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="BD17" s="87" t="s">
+      <c r="BD17" s="85" t="s">
         <v>280</v>
       </c>
-      <c r="BE17" s="81"/>
-      <c r="BF17" s="81"/>
-      <c r="BG17" s="81"/>
-      <c r="BH17" s="82"/>
-      <c r="BI17" s="87">
+      <c r="BE17" s="79"/>
+      <c r="BF17" s="79"/>
+      <c r="BG17" s="79"/>
+      <c r="BH17" s="80"/>
+      <c r="BI17" s="85">
         <v>350</v>
       </c>
-      <c r="BJ17" s="86" t="s">
+      <c r="BJ17" s="84" t="s">
         <v>187</v>
       </c>
-      <c r="BK17" s="111"/>
-      <c r="BL17" s="86"/>
-      <c r="BM17" s="111"/>
-      <c r="BN17" s="86"/>
-      <c r="BO17" s="86"/>
-      <c r="BP17" s="86"/>
-      <c r="BQ17" s="86"/>
-      <c r="BR17" s="111"/>
-      <c r="BS17" s="86"/>
-      <c r="BT17" s="82"/>
-      <c r="BU17" s="86"/>
-      <c r="BV17" s="86"/>
-      <c r="BW17" s="81"/>
-      <c r="BX17" s="84"/>
-      <c r="BY17" s="85"/>
-      <c r="BZ17" s="85"/>
-      <c r="CA17" s="85"/>
-      <c r="CB17" s="85"/>
-      <c r="CC17" s="85"/>
-      <c r="CD17" s="81"/>
-      <c r="CE17" s="81"/>
-      <c r="CF17" s="81"/>
-      <c r="CG17" s="81"/>
-      <c r="CH17" s="81"/>
-      <c r="CI17" s="81"/>
-      <c r="CJ17" s="81"/>
-      <c r="CK17" s="81"/>
-      <c r="CL17" s="81"/>
-      <c r="CM17" s="81"/>
-      <c r="CN17" s="81"/>
-      <c r="CO17" s="81"/>
-      <c r="CP17" s="81"/>
-      <c r="CQ17" s="81"/>
-      <c r="CR17" s="81"/>
-      <c r="CS17" s="81"/>
-      <c r="CT17" s="81"/>
-      <c r="CU17" s="81"/>
-    </row>
-    <row r="18" spans="1:99" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="89"/>
-      <c r="B18" s="72" t="s">
+      <c r="BK17" s="108"/>
+      <c r="BL17" s="84"/>
+      <c r="BM17" s="108"/>
+      <c r="BN17" s="84"/>
+      <c r="BO17" s="84"/>
+      <c r="BP17" s="84"/>
+      <c r="BQ17" s="84"/>
+      <c r="BR17" s="108"/>
+      <c r="BS17" s="84"/>
+      <c r="BT17" s="80"/>
+      <c r="BU17" s="84"/>
+      <c r="BV17" s="84"/>
+      <c r="BW17" s="79"/>
+      <c r="BX17" s="82"/>
+      <c r="BY17" s="83"/>
+      <c r="BZ17" s="83"/>
+      <c r="CA17" s="83"/>
+      <c r="CB17" s="83"/>
+      <c r="CC17" s="83"/>
+      <c r="CD17" s="79"/>
+      <c r="CE17" s="79"/>
+      <c r="CF17" s="79"/>
+      <c r="CG17" s="79"/>
+      <c r="CH17" s="79"/>
+      <c r="CI17" s="79"/>
+      <c r="CJ17" s="79"/>
+      <c r="CK17" s="79"/>
+      <c r="CL17" s="79"/>
+      <c r="CM17" s="79"/>
+      <c r="CN17" s="79"/>
+      <c r="CO17" s="79"/>
+      <c r="CP17" s="79"/>
+      <c r="CQ17" s="79"/>
+      <c r="CR17" s="79"/>
+      <c r="CS17" s="79"/>
+      <c r="CT17" s="79"/>
+      <c r="CU17" s="79"/>
+    </row>
+    <row r="18" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="87"/>
+      <c r="B18" s="117" t="s">
         <v>281</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="88" t="s">
         <v>282</v>
       </c>
       <c r="D18" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="E18" s="91">
+      <c r="E18" s="89">
         <v>0.55278935185197042</v>
       </c>
-      <c r="F18" s="61" t="s">
+      <c r="F18" s="88" t="s">
         <v>283</v>
       </c>
-      <c r="G18" s="90" t="s">
+      <c r="G18" s="88" t="s">
         <v>284</v>
       </c>
-      <c r="H18" s="90" t="s">
+      <c r="H18" s="88" t="s">
         <v>285</v>
       </c>
-      <c r="I18" s="90" t="s">
+      <c r="I18" s="88" t="s">
         <v>224</v>
       </c>
-      <c r="J18" s="90" t="s">
+      <c r="J18" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90" t="s">
+      <c r="K18" s="88"/>
+      <c r="L18" s="88" t="s">
         <v>119</v>
       </c>
       <c r="M18" s="61" t="s">
@@ -5659,10 +5674,10 @@
       <c r="O18" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="P18" s="90" t="s">
+      <c r="P18" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="90" t="s">
+      <c r="Q18" s="88" t="s">
         <v>124</v>
       </c>
       <c r="R18" s="61" t="s">
@@ -5671,31 +5686,31 @@
       <c r="S18" s="61">
         <v>19586907</v>
       </c>
-      <c r="T18" s="90">
+      <c r="T18" s="88">
         <v>983031158</v>
       </c>
       <c r="U18" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="V18" s="90">
+      <c r="V18" s="88">
         <v>606</v>
       </c>
-      <c r="W18" s="90" t="s">
+      <c r="W18" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="X18" s="90" t="s">
+      <c r="X18" s="88" t="s">
         <v>131</v>
       </c>
       <c r="Y18" s="61">
         <v>318033</v>
       </c>
-      <c r="Z18" s="90" t="s">
+      <c r="Z18" s="88" t="s">
         <v>240</v>
       </c>
       <c r="AA18" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="AB18" s="90">
+      <c r="AB18" s="88">
         <v>33.843293899999999</v>
       </c>
       <c r="AC18" s="47">
@@ -5704,46 +5719,46 @@
       <c r="AD18" s="61">
         <v>2202.86</v>
       </c>
-      <c r="AE18" s="90"/>
+      <c r="AE18" s="88"/>
       <c r="AF18" s="61">
         <v>2202.86</v>
       </c>
-      <c r="AG18" s="90"/>
-      <c r="AH18" s="90">
+      <c r="AG18" s="88"/>
+      <c r="AH18" s="88">
         <v>65.09</v>
       </c>
-      <c r="AI18" s="90" t="s">
+      <c r="AI18" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="AJ18" s="90">
+      <c r="AJ18" s="88">
         <v>1.5363</v>
       </c>
-      <c r="AK18" s="90"/>
+      <c r="AK18" s="88"/>
       <c r="AL18" s="61" t="s">
         <v>286</v>
       </c>
-      <c r="AM18" s="90"/>
-      <c r="AN18" s="90" t="s">
+      <c r="AM18" s="88"/>
+      <c r="AN18" s="88" t="s">
         <v>279</v>
       </c>
-      <c r="AO18" s="90">
+      <c r="AO18" s="88">
         <v>5656578</v>
       </c>
-      <c r="AP18" s="107"/>
-      <c r="AQ18" s="92"/>
-      <c r="AR18" s="92"/>
-      <c r="AS18" s="92"/>
-      <c r="AT18" s="90" t="s">
+      <c r="AP18" s="104"/>
+      <c r="AQ18" s="90"/>
+      <c r="AR18" s="90"/>
+      <c r="AS18" s="90"/>
+      <c r="AT18" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="AU18" s="90"/>
+      <c r="AU18" s="88"/>
       <c r="AV18" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="AW18" s="90" t="s">
+      <c r="AW18" s="88" t="s">
         <v>165</v>
       </c>
-      <c r="AX18" s="90">
+      <c r="AX18" s="88">
         <v>33.843293899999999</v>
       </c>
       <c r="AY18" s="61">
@@ -5752,186 +5767,186 @@
       <c r="AZ18" s="61">
         <v>2202.86</v>
       </c>
-      <c r="BA18" s="90"/>
+      <c r="BA18" s="88"/>
       <c r="BB18" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="BC18" s="90" t="s">
+      <c r="BC18" s="88" t="s">
         <v>147</v>
       </c>
       <c r="BD18" s="61" t="s">
         <v>280</v>
       </c>
-      <c r="BE18" s="92"/>
-      <c r="BF18" s="92"/>
-      <c r="BG18" s="92"/>
-      <c r="BH18" s="90"/>
+      <c r="BE18" s="90"/>
+      <c r="BF18" s="90"/>
+      <c r="BG18" s="90"/>
+      <c r="BH18" s="88"/>
       <c r="BI18" s="61">
         <v>350</v>
       </c>
-      <c r="BJ18" s="90" t="s">
+      <c r="BJ18" s="88" t="s">
         <v>187</v>
       </c>
-      <c r="BK18" s="107"/>
-      <c r="BL18" s="90"/>
-      <c r="BM18" s="107"/>
-      <c r="BN18" s="90"/>
-      <c r="BO18" s="90"/>
-      <c r="BP18" s="90"/>
-      <c r="BQ18" s="90"/>
-      <c r="BR18" s="107"/>
-      <c r="BS18" s="90"/>
-      <c r="BT18" s="93"/>
-      <c r="BU18" s="90"/>
-      <c r="BV18" s="90"/>
-      <c r="BW18" s="92"/>
-      <c r="BX18" s="94"/>
-      <c r="BY18" s="95"/>
-      <c r="BZ18" s="95"/>
-      <c r="CA18" s="95"/>
-      <c r="CB18" s="95"/>
-      <c r="CC18" s="95"/>
-      <c r="CD18" s="92"/>
-      <c r="CE18" s="92"/>
-      <c r="CF18" s="92"/>
-      <c r="CG18" s="92"/>
-      <c r="CH18" s="92"/>
-      <c r="CI18" s="92"/>
-      <c r="CJ18" s="92"/>
-      <c r="CK18" s="92"/>
-      <c r="CL18" s="92"/>
-      <c r="CM18" s="92"/>
-      <c r="CN18" s="92"/>
-      <c r="CO18" s="92"/>
-      <c r="CP18" s="92"/>
-      <c r="CQ18" s="92"/>
-      <c r="CR18" s="92"/>
-      <c r="CS18" s="92"/>
-      <c r="CT18" s="92"/>
-      <c r="CU18" s="92"/>
-    </row>
-    <row r="19" spans="1:99" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="89"/>
-      <c r="B19" s="96" t="s">
+      <c r="BK18" s="104"/>
+      <c r="BL18" s="88"/>
+      <c r="BM18" s="104"/>
+      <c r="BN18" s="88"/>
+      <c r="BO18" s="88"/>
+      <c r="BP18" s="88"/>
+      <c r="BQ18" s="88"/>
+      <c r="BR18" s="104"/>
+      <c r="BS18" s="88"/>
+      <c r="BT18" s="91"/>
+      <c r="BU18" s="88"/>
+      <c r="BV18" s="88"/>
+      <c r="BW18" s="90"/>
+      <c r="BX18" s="92"/>
+      <c r="BY18" s="93"/>
+      <c r="BZ18" s="93"/>
+      <c r="CA18" s="93"/>
+      <c r="CB18" s="93"/>
+      <c r="CC18" s="93"/>
+      <c r="CD18" s="90"/>
+      <c r="CE18" s="90"/>
+      <c r="CF18" s="90"/>
+      <c r="CG18" s="90"/>
+      <c r="CH18" s="90"/>
+      <c r="CI18" s="90"/>
+      <c r="CJ18" s="90"/>
+      <c r="CK18" s="90"/>
+      <c r="CL18" s="90"/>
+      <c r="CM18" s="90"/>
+      <c r="CN18" s="90"/>
+      <c r="CO18" s="90"/>
+      <c r="CP18" s="90"/>
+      <c r="CQ18" s="90"/>
+      <c r="CR18" s="90"/>
+      <c r="CS18" s="90"/>
+      <c r="CT18" s="90"/>
+      <c r="CU18" s="90"/>
+    </row>
+    <row r="19" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="87"/>
+      <c r="B19" s="87" t="s">
         <v>287</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="94" t="s">
         <v>218</v>
       </c>
       <c r="D19" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="91">
+      <c r="E19" s="89">
         <v>0.58141203703780775</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="88" t="s">
         <v>288</v>
       </c>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="107"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-      <c r="Y19" s="107"/>
-      <c r="Z19" s="90"/>
-      <c r="AA19" s="107"/>
-      <c r="AB19" s="90"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="104"/>
+      <c r="S19" s="104"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="104"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="104"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="104"/>
+      <c r="AB19" s="88"/>
       <c r="AC19" s="47">
         <v>769.16</v>
       </c>
-      <c r="AD19" s="107"/>
-      <c r="AE19" s="90"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="90"/>
-      <c r="AH19" s="98">
+      <c r="AD19" s="104"/>
+      <c r="AE19" s="88"/>
+      <c r="AF19" s="104"/>
+      <c r="AG19" s="88"/>
+      <c r="AH19" s="95">
         <v>65.09</v>
       </c>
-      <c r="AI19" s="98" t="s">
+      <c r="AI19" s="95" t="s">
         <v>139</v>
       </c>
-      <c r="AJ19" s="90"/>
-      <c r="AK19" s="90"/>
-      <c r="AL19" s="107"/>
-      <c r="AM19" s="90"/>
-      <c r="AN19" s="90"/>
-      <c r="AO19" s="90"/>
-      <c r="AP19" s="107"/>
-      <c r="AQ19" s="99"/>
-      <c r="AR19" s="99"/>
-      <c r="AS19" s="99"/>
-      <c r="AT19" s="90"/>
-      <c r="AU19" s="90"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="90"/>
-      <c r="AX19" s="90"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
-      <c r="BA19" s="90"/>
-      <c r="BB19" s="87" t="s">
+      <c r="AJ19" s="88"/>
+      <c r="AK19" s="88"/>
+      <c r="AL19" s="104"/>
+      <c r="AM19" s="88"/>
+      <c r="AN19" s="88"/>
+      <c r="AO19" s="88"/>
+      <c r="AP19" s="104"/>
+      <c r="AQ19" s="96"/>
+      <c r="AR19" s="96"/>
+      <c r="AS19" s="96"/>
+      <c r="AT19" s="88"/>
+      <c r="AU19" s="88"/>
+      <c r="AV19" s="104"/>
+      <c r="AW19" s="88"/>
+      <c r="AX19" s="88"/>
+      <c r="AY19" s="104"/>
+      <c r="AZ19" s="104"/>
+      <c r="BA19" s="88"/>
+      <c r="BB19" s="85" t="s">
         <v>146</v>
       </c>
-      <c r="BC19" s="90"/>
-      <c r="BD19" s="107"/>
-      <c r="BE19" s="99"/>
-      <c r="BF19" s="99"/>
-      <c r="BG19" s="99"/>
-      <c r="BH19" s="93"/>
-      <c r="BI19" s="100">
+      <c r="BC19" s="88"/>
+      <c r="BD19" s="104"/>
+      <c r="BE19" s="96"/>
+      <c r="BF19" s="96"/>
+      <c r="BG19" s="96"/>
+      <c r="BH19" s="91"/>
+      <c r="BI19" s="97">
         <v>769.16</v>
       </c>
-      <c r="BJ19" s="98" t="s">
+      <c r="BJ19" s="95" t="s">
         <v>187</v>
       </c>
-      <c r="BK19" s="107"/>
-      <c r="BL19" s="90"/>
-      <c r="BM19" s="107"/>
-      <c r="BN19" s="90"/>
-      <c r="BO19" s="90"/>
-      <c r="BP19" s="90"/>
-      <c r="BQ19" s="90"/>
-      <c r="BR19" s="107"/>
-      <c r="BS19" s="90"/>
-      <c r="BT19" s="101"/>
-      <c r="BU19" s="90"/>
-      <c r="BV19" s="90"/>
-      <c r="BW19" s="92"/>
-      <c r="BX19" s="99"/>
-      <c r="BY19" s="99"/>
-      <c r="BZ19" s="99"/>
-      <c r="CA19" s="99"/>
-      <c r="CB19" s="99"/>
-      <c r="CC19" s="99"/>
-      <c r="CD19" s="99"/>
-      <c r="CE19" s="99"/>
-      <c r="CF19" s="99"/>
-      <c r="CG19" s="99"/>
-      <c r="CH19" s="99"/>
-      <c r="CI19" s="99"/>
-      <c r="CJ19" s="99"/>
-      <c r="CK19" s="99"/>
-      <c r="CL19" s="99"/>
-      <c r="CM19" s="99"/>
-      <c r="CN19" s="99"/>
-      <c r="CO19" s="99"/>
-      <c r="CP19" s="99"/>
-      <c r="CQ19" s="99"/>
-      <c r="CR19" s="99"/>
-      <c r="CS19" s="99"/>
-      <c r="CT19" s="99"/>
-      <c r="CU19" s="99"/>
+      <c r="BK19" s="104"/>
+      <c r="BL19" s="88"/>
+      <c r="BM19" s="104"/>
+      <c r="BN19" s="88"/>
+      <c r="BO19" s="88"/>
+      <c r="BP19" s="88"/>
+      <c r="BQ19" s="88"/>
+      <c r="BR19" s="104"/>
+      <c r="BS19" s="88"/>
+      <c r="BT19" s="98"/>
+      <c r="BU19" s="88"/>
+      <c r="BV19" s="88"/>
+      <c r="BW19" s="90"/>
+      <c r="BX19" s="96"/>
+      <c r="BY19" s="96"/>
+      <c r="BZ19" s="96"/>
+      <c r="CA19" s="96"/>
+      <c r="CB19" s="96"/>
+      <c r="CC19" s="96"/>
+      <c r="CD19" s="96"/>
+      <c r="CE19" s="96"/>
+      <c r="CF19" s="96"/>
+      <c r="CG19" s="96"/>
+      <c r="CH19" s="96"/>
+      <c r="CI19" s="96"/>
+      <c r="CJ19" s="96"/>
+      <c r="CK19" s="96"/>
+      <c r="CL19" s="96"/>
+      <c r="CM19" s="96"/>
+      <c r="CN19" s="96"/>
+      <c r="CO19" s="96"/>
+      <c r="CP19" s="96"/>
+      <c r="CQ19" s="96"/>
+      <c r="CR19" s="96"/>
+      <c r="CS19" s="96"/>
+      <c r="CT19" s="96"/>
+      <c r="CU19" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5950,7 +5965,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5959,5967 +5974,5967 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="99" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="99" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="99" t="s">
         <v>291</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="99" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="100" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="D2" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="D3" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="103" t="s">
+      <c r="C4" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="D4" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>294</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="100" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="103" t="s">
+      <c r="D6" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E6" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="100" t="s">
         <v>296</v>
       </c>
-      <c r="D7" s="103" t="s">
+      <c r="D7" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="100" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E9" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="103" t="s">
+      <c r="D10" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="103" t="s">
+      <c r="D11" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E11" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="100" t="s">
         <v>137</v>
       </c>
-      <c r="D12" s="103" t="s">
+      <c r="D12" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E12" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>6</v>
       </c>
       <c r="B13" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="103" t="s">
+      <c r="D13" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E13" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="103" t="s">
+      <c r="C14" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="103" t="s">
+      <c r="D14" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E14" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D15" s="104" t="s">
+      <c r="D15" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>6</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="103" t="s">
+      <c r="C16" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="103" t="s">
+      <c r="D16" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E16" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D17" s="104" t="s">
+      <c r="D17" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E17" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>6</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E18" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>6</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="103" t="s">
+      <c r="C19" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="103" t="s">
+      <c r="D19" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E19" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>6</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="103" t="s">
+      <c r="C20" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="103" t="s">
+      <c r="D20" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E20" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>6</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="103" t="s">
+      <c r="C21" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="103" t="s">
+      <c r="D21" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E21" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>6</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="103" t="s">
+      <c r="C22" s="100" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="103" t="s">
+      <c r="D22" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E22" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>6</v>
       </c>
       <c r="B23" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="100" t="s">
         <v>301</v>
       </c>
-      <c r="D23" s="103" t="s">
+      <c r="D23" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E23" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>6</v>
       </c>
       <c r="B24" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="103" t="s">
+      <c r="C24" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="103" t="s">
+      <c r="D24" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E24" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>6</v>
       </c>
       <c r="B25" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="103" t="s">
+      <c r="C25" s="100" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="103" t="s">
+      <c r="D25" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E25" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>6</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="103" t="s">
+      <c r="C26" s="100" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="103" t="s">
+      <c r="D26" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E26" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>7</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="103" t="s">
+      <c r="C27" s="100" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="103" t="s">
+      <c r="D27" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E27" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>7</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="103" t="s">
+      <c r="C28" s="100" t="s">
         <v>150</v>
       </c>
-      <c r="D28" s="103" t="s">
+      <c r="D28" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E28" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>7</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="103" t="s">
+      <c r="C29" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="103" t="s">
+      <c r="D29" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E29" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>7</v>
       </c>
       <c r="B30" t="s">
         <v>294</v>
       </c>
-      <c r="C30" s="103" t="s">
+      <c r="C30" s="100" t="s">
         <v>159</v>
       </c>
-      <c r="D30" s="103" t="s">
+      <c r="D30" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E30" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>7</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="103" t="s">
+      <c r="C31" s="100" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="103" t="s">
+      <c r="D31" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E31" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>7</v>
       </c>
       <c r="B32" t="s">
         <v>295</v>
       </c>
-      <c r="C32" s="103" t="s">
+      <c r="C32" s="100" t="s">
         <v>303</v>
       </c>
-      <c r="D32" s="103" t="s">
+      <c r="D32" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>7</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="103" t="s">
+      <c r="C33" s="100" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="103" t="s">
+      <c r="D33" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E33" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>7</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="103" t="s">
+      <c r="C34" s="100" t="s">
         <v>168</v>
       </c>
-      <c r="D34" s="103" t="s">
+      <c r="D34" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E34" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>7</v>
       </c>
       <c r="B35" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="103" t="s">
+      <c r="C35" s="100" t="s">
         <v>163</v>
       </c>
-      <c r="D35" s="103" t="s">
+      <c r="D35" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E35" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>7</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="103" t="s">
+      <c r="C36" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="103" t="s">
+      <c r="D36" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E36" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>7</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="103" t="s">
+      <c r="C37" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="103" t="s">
+      <c r="D37" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E37" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>7</v>
       </c>
       <c r="B38" t="s">
         <v>297</v>
       </c>
-      <c r="C38" s="103" t="s">
+      <c r="C38" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="103" t="s">
+      <c r="D38" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E38" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>7</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="103" t="s">
+      <c r="C39" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D39" s="103" t="s">
+      <c r="D39" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E39" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>7</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="104" t="s">
+      <c r="C40" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D40" s="104" t="s">
+      <c r="D40" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E40" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="103" t="s">
+      <c r="C41" s="100" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="103" t="s">
+      <c r="D41" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E41" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="104" t="s">
+      <c r="C42" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D42" s="104" t="s">
+      <c r="D42" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E42" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>7</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="103" t="s">
+      <c r="C43" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="103" t="s">
+      <c r="D43" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E43" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>7</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="103" t="s">
+      <c r="C44" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="103" t="s">
+      <c r="D44" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E44" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>7</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="103" t="s">
+      <c r="C45" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="103" t="s">
+      <c r="D45" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E45" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>7</v>
       </c>
       <c r="B46" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="103" t="s">
+      <c r="C46" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D46" s="103" t="s">
+      <c r="D46" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E46" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>7</v>
       </c>
       <c r="B47" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="103" t="s">
+      <c r="C47" s="100" t="s">
         <v>176</v>
       </c>
-      <c r="D47" s="103" t="s">
+      <c r="D47" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E47" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>7</v>
       </c>
       <c r="B48" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="103" t="s">
+      <c r="C48" s="100" t="s">
         <v>304</v>
       </c>
-      <c r="D48" s="103" t="s">
+      <c r="D48" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E48" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>7</v>
       </c>
       <c r="B49" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="104" t="s">
+      <c r="C49" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D49" s="104" t="s">
+      <c r="D49" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E49" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>7</v>
       </c>
       <c r="B50" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="103" t="s">
+      <c r="C50" s="100" t="s">
         <v>176</v>
       </c>
-      <c r="D50" s="103" t="s">
+      <c r="D50" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E50" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>7</v>
       </c>
       <c r="B51" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="104" t="s">
+      <c r="C51" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E51" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>8</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="103" t="s">
+      <c r="C52" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="D52" s="103" t="s">
+      <c r="D52" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E52" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>8</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="103" t="s">
+      <c r="C53" s="100" t="s">
         <v>177</v>
       </c>
-      <c r="D53" s="103" t="s">
+      <c r="D53" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E53" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>8</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="103" t="s">
+      <c r="C54" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="103" t="s">
+      <c r="D54" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E54" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>8</v>
       </c>
       <c r="B55" t="s">
         <v>294</v>
       </c>
-      <c r="C55" s="103" t="s">
+      <c r="C55" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="103" t="s">
+      <c r="D55" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E55" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>8</v>
       </c>
       <c r="B56" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="103" t="s">
+      <c r="C56" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D56" s="103" t="s">
+      <c r="D56" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E56" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>8</v>
       </c>
       <c r="B57" t="s">
         <v>295</v>
       </c>
-      <c r="C57" s="103" t="s">
+      <c r="C57" s="100" t="s">
         <v>307</v>
       </c>
-      <c r="D57" s="103" t="s">
+      <c r="D57" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E57" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>8</v>
       </c>
       <c r="B58" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="103" t="s">
+      <c r="C58" s="100" t="s">
         <v>189</v>
       </c>
-      <c r="D58" s="103" t="s">
+      <c r="D58" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E58" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>8</v>
       </c>
       <c r="B59" t="s">
         <v>37</v>
       </c>
-      <c r="C59" s="103" t="s">
+      <c r="C59" s="100" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="103" t="s">
+      <c r="D59" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E59" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>8</v>
       </c>
       <c r="B60" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="100" t="s">
         <v>185</v>
       </c>
-      <c r="D60" s="103" t="s">
+      <c r="D60" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E60" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>8</v>
       </c>
       <c r="B61" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="103" t="s">
+      <c r="C61" s="100" t="s">
         <v>195</v>
       </c>
-      <c r="D61" s="103" t="s">
+      <c r="D61" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E61" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>8</v>
       </c>
       <c r="B62" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="103" t="s">
+      <c r="C62" s="100" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="103" t="s">
+      <c r="D62" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E62" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>8</v>
       </c>
       <c r="B63" t="s">
         <v>297</v>
       </c>
-      <c r="C63" s="103" t="s">
+      <c r="C63" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="103" t="s">
+      <c r="D63" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E63" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>8</v>
       </c>
       <c r="B64" t="s">
         <v>23</v>
       </c>
-      <c r="C64" s="103" t="s">
+      <c r="C64" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D64" s="103" t="s">
+      <c r="D64" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E64" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>8</v>
       </c>
       <c r="B65" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="104" t="s">
+      <c r="C65" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D65" s="104" t="s">
+      <c r="D65" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E65" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>8</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="103" t="s">
+      <c r="C66" s="100" t="s">
         <v>192</v>
       </c>
-      <c r="D66" s="103" t="s">
+      <c r="D66" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E66" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>8</v>
       </c>
       <c r="B67" t="s">
         <v>53</v>
       </c>
-      <c r="C67" s="104" t="s">
+      <c r="C67" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D67" s="104" t="s">
+      <c r="D67" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E67" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>8</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
-      <c r="C68" s="103" t="s">
+      <c r="C68" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D68" s="103" t="s">
+      <c r="D68" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E68" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>8</v>
       </c>
       <c r="B69" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="103" t="s">
+      <c r="C69" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="103" t="s">
+      <c r="D69" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E69" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>8</v>
       </c>
       <c r="B70" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="103" t="s">
+      <c r="C70" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="103" t="s">
+      <c r="D70" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E70" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>8</v>
       </c>
       <c r="B71" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="103" t="s">
+      <c r="C71" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D71" s="103" t="s">
+      <c r="D71" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E71" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>8</v>
       </c>
       <c r="B72" t="s">
         <v>61</v>
       </c>
-      <c r="C72" s="103" t="s">
+      <c r="C72" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="D72" s="103" t="s">
+      <c r="D72" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E72" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>8</v>
       </c>
       <c r="B73" t="s">
         <v>66</v>
       </c>
-      <c r="C73" s="103" t="s">
+      <c r="C73" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="D73" s="103" t="s">
+      <c r="D73" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E73" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>8</v>
       </c>
       <c r="B74" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="104" t="s">
+      <c r="C74" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="104" t="s">
+      <c r="D74" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E74" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>8</v>
       </c>
       <c r="B75" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="103" t="s">
+      <c r="C75" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="D75" s="103" t="s">
+      <c r="D75" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E75" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>8</v>
       </c>
       <c r="B76" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="104" t="s">
+      <c r="C76" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D76" s="104" t="s">
+      <c r="D76" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E76" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>9</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="103" t="s">
+      <c r="C77" s="100" t="s">
         <v>201</v>
       </c>
-      <c r="D77" s="103" t="s">
+      <c r="D77" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E77" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>9</v>
       </c>
       <c r="B78" t="s">
         <v>7</v>
       </c>
-      <c r="C78" s="103" t="s">
+      <c r="C78" s="100" t="s">
         <v>198</v>
       </c>
-      <c r="D78" s="103" t="s">
+      <c r="D78" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E78" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>9</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="103" t="s">
+      <c r="C79" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="D79" s="103" t="s">
+      <c r="D79" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E79" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>9</v>
       </c>
       <c r="B80" t="s">
         <v>294</v>
       </c>
-      <c r="C80" s="103" t="s">
+      <c r="C80" s="100" t="s">
         <v>206</v>
       </c>
-      <c r="D80" s="103" t="s">
+      <c r="D80" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E80" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>9</v>
       </c>
       <c r="B81" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="103" t="s">
+      <c r="C81" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="D81" s="103" t="s">
+      <c r="D81" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E81" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>9</v>
       </c>
       <c r="B82" t="s">
         <v>295</v>
       </c>
-      <c r="C82" s="103" t="s">
+      <c r="C82" s="100" t="s">
         <v>309</v>
       </c>
-      <c r="D82" s="103" t="s">
+      <c r="D82" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E82" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>9</v>
       </c>
       <c r="B83" t="s">
         <v>35</v>
       </c>
-      <c r="C83" s="103" t="s">
+      <c r="C83" s="100" t="s">
         <v>208</v>
       </c>
-      <c r="D83" s="103" t="s">
+      <c r="D83" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E83" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>9</v>
       </c>
       <c r="B84" t="s">
         <v>37</v>
       </c>
-      <c r="C84" s="103" t="s">
+      <c r="C84" s="100" t="s">
         <v>209</v>
       </c>
-      <c r="D84" s="103" t="s">
+      <c r="D84" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E84" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>9</v>
       </c>
       <c r="B85" t="s">
         <v>30</v>
       </c>
-      <c r="C85" s="103" t="s">
+      <c r="C85" s="100" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="103" t="s">
+      <c r="D85" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E85" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>9</v>
       </c>
       <c r="B86" t="s">
         <v>56</v>
       </c>
-      <c r="C86" s="103" t="s">
+      <c r="C86" s="100" t="s">
         <v>208</v>
       </c>
-      <c r="D86" s="103" t="s">
+      <c r="D86" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E86" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>9</v>
       </c>
       <c r="B87" t="s">
         <v>57</v>
       </c>
-      <c r="C87" s="103" t="s">
+      <c r="C87" s="100" t="s">
         <v>209</v>
       </c>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E87" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>9</v>
       </c>
       <c r="B88" t="s">
         <v>297</v>
       </c>
-      <c r="C88" s="103" t="s">
+      <c r="C88" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="103" t="s">
+      <c r="D88" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E88" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>9</v>
       </c>
       <c r="B89" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="103" t="s">
+      <c r="C89" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D89" s="103" t="s">
+      <c r="D89" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E89" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>9</v>
       </c>
       <c r="B90" t="s">
         <v>47</v>
       </c>
-      <c r="C90" s="104" t="s">
+      <c r="C90" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D90" s="104" t="s">
+      <c r="D90" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E90" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>9</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
       </c>
-      <c r="C91" s="103" t="s">
+      <c r="C91" s="100" t="s">
         <v>212</v>
       </c>
-      <c r="D91" s="103" t="s">
+      <c r="D91" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E91" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>9</v>
       </c>
       <c r="B92" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="104" t="s">
+      <c r="C92" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D92" s="104" t="s">
+      <c r="D92" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E92" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>9</v>
       </c>
       <c r="B93" t="s">
         <v>26</v>
       </c>
-      <c r="C93" s="103" t="s">
+      <c r="C93" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D93" s="103" t="s">
+      <c r="D93" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E93" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>9</v>
       </c>
       <c r="B94" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="103" t="s">
+      <c r="C94" s="100" t="s">
         <v>204</v>
       </c>
-      <c r="D94" s="103" t="s">
+      <c r="D94" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E94" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>9</v>
       </c>
       <c r="B95" t="s">
         <v>20</v>
       </c>
-      <c r="C95" s="103" t="s">
+      <c r="C95" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="D95" s="103" t="s">
+      <c r="D95" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E95" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>9</v>
       </c>
       <c r="B96" t="s">
         <v>59</v>
       </c>
-      <c r="C96" s="103" t="s">
+      <c r="C96" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="103" t="s">
+      <c r="D96" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E96" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>9</v>
       </c>
       <c r="B97" t="s">
         <v>61</v>
       </c>
-      <c r="C97" s="103" t="s">
+      <c r="C97" s="100" t="s">
         <v>215</v>
       </c>
-      <c r="D97" s="103" t="s">
+      <c r="D97" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E97" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>9</v>
       </c>
       <c r="B98" t="s">
         <v>66</v>
       </c>
-      <c r="C98" s="103" t="s">
+      <c r="C98" s="100" t="s">
         <v>310</v>
       </c>
-      <c r="D98" s="103" t="s">
+      <c r="D98" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E98" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>9</v>
       </c>
       <c r="B99" t="s">
         <v>68</v>
       </c>
-      <c r="C99" s="103" t="s">
+      <c r="C99" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="D99" s="103" t="s">
+      <c r="D99" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E99" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>9</v>
       </c>
       <c r="B100" t="s">
         <v>70</v>
       </c>
-      <c r="C100" s="103" t="s">
+      <c r="C100" s="100" t="s">
         <v>215</v>
       </c>
-      <c r="D100" s="103" t="s">
+      <c r="D100" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E100" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>9</v>
       </c>
       <c r="B101" t="s">
         <v>75</v>
       </c>
-      <c r="C101" s="103" t="s">
+      <c r="C101" s="100" t="s">
         <v>216</v>
       </c>
-      <c r="D101" s="103" t="s">
+      <c r="D101" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E101" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>10</v>
       </c>
       <c r="B102" t="s">
         <v>11</v>
       </c>
-      <c r="C102" s="103" t="s">
+      <c r="C102" s="100" t="s">
         <v>219</v>
       </c>
-      <c r="D102" s="103" t="s">
+      <c r="D102" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E102" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>10</v>
       </c>
       <c r="B103" t="s">
         <v>7</v>
       </c>
-      <c r="C103" s="103" t="s">
+      <c r="C103" s="100" t="s">
         <v>217</v>
       </c>
-      <c r="D103" s="103" t="s">
+      <c r="D103" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E103" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>10</v>
       </c>
       <c r="B104" t="s">
         <v>9</v>
       </c>
-      <c r="C104" s="103" t="s">
+      <c r="C104" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="D104" s="103" t="s">
+      <c r="D104" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E104" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>10</v>
       </c>
       <c r="B105" t="s">
         <v>294</v>
       </c>
-      <c r="C105" s="103" t="s">
+      <c r="C105" s="100" t="s">
         <v>220</v>
       </c>
-      <c r="D105" s="103" t="s">
+      <c r="D105" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E105" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>10</v>
       </c>
       <c r="B106" t="s">
         <v>32</v>
       </c>
-      <c r="C106" s="103" t="s">
+      <c r="C106" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="D106" s="103" t="s">
+      <c r="D106" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E106" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>10</v>
       </c>
       <c r="B107" t="s">
         <v>295</v>
       </c>
-      <c r="C107" s="104" t="s">
+      <c r="C107" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D107" s="104" t="s">
+      <c r="D107" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E107" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>10</v>
       </c>
       <c r="B108" t="s">
         <v>35</v>
       </c>
-      <c r="C108" s="103" t="s">
+      <c r="C108" s="100" t="s">
         <v>311</v>
       </c>
-      <c r="D108" s="103" t="s">
+      <c r="D108" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E108" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>10</v>
       </c>
       <c r="B109" t="s">
         <v>37</v>
       </c>
-      <c r="C109" s="104" t="s">
+      <c r="C109" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D109" s="104" t="s">
+      <c r="D109" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E109" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>10</v>
       </c>
       <c r="B110" t="s">
         <v>30</v>
       </c>
-      <c r="C110" s="104" t="s">
+      <c r="C110" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D110" s="104" t="s">
+      <c r="D110" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E110" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>10</v>
       </c>
       <c r="B111" t="s">
         <v>56</v>
       </c>
-      <c r="C111" s="104" t="s">
+      <c r="C111" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D111" s="104" t="s">
+      <c r="D111" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E111" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>10</v>
       </c>
       <c r="B112" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="104" t="s">
+      <c r="C112" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D112" s="104" t="s">
+      <c r="D112" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E112" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>10</v>
       </c>
       <c r="B113" t="s">
         <v>297</v>
       </c>
-      <c r="C113" s="104" t="s">
+      <c r="C113" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D113" s="104" t="s">
+      <c r="D113" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E113" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>10</v>
       </c>
       <c r="B114" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="104" t="s">
+      <c r="C114" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D114" s="104" t="s">
+      <c r="D114" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E114" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>10</v>
       </c>
       <c r="B115" t="s">
         <v>47</v>
       </c>
-      <c r="C115" s="104" t="s">
+      <c r="C115" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D115" s="104" t="s">
+      <c r="D115" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E115" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>10</v>
       </c>
       <c r="B116" t="s">
         <v>43</v>
       </c>
-      <c r="C116" s="104" t="s">
+      <c r="C116" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D116" s="104" t="s">
+      <c r="D116" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E116" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>10</v>
       </c>
       <c r="B117" t="s">
         <v>53</v>
       </c>
-      <c r="C117" s="104" t="s">
+      <c r="C117" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D117" s="104" t="s">
+      <c r="D117" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E117" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>10</v>
       </c>
       <c r="B118" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="104" t="s">
+      <c r="C118" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D118" s="104" t="s">
+      <c r="D118" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E118" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>10</v>
       </c>
       <c r="B119" t="s">
         <v>19</v>
       </c>
-      <c r="C119" s="104" t="s">
+      <c r="C119" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D119" s="104" t="s">
+      <c r="D119" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E119" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>10</v>
       </c>
       <c r="B120" t="s">
         <v>20</v>
       </c>
-      <c r="C120" s="104" t="s">
+      <c r="C120" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D120" s="104" t="s">
+      <c r="D120" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E120" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>10</v>
       </c>
       <c r="B121" t="s">
         <v>59</v>
       </c>
-      <c r="C121" s="105" t="s">
+      <c r="C121" s="102" t="s">
         <v>298</v>
       </c>
-      <c r="D121" s="105" t="s">
+      <c r="D121" s="102" t="s">
         <v>305</v>
       </c>
       <c r="E121" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>10</v>
       </c>
       <c r="B122" t="s">
         <v>61</v>
       </c>
-      <c r="C122" s="105" t="s">
+      <c r="C122" s="102" t="s">
         <v>298</v>
       </c>
-      <c r="D122" s="105" t="s">
+      <c r="D122" s="102" t="s">
         <v>305</v>
       </c>
       <c r="E122" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>10</v>
       </c>
       <c r="B123" t="s">
         <v>66</v>
       </c>
-      <c r="C123" s="103" t="s">
+      <c r="C123" s="100" t="s">
         <v>312</v>
       </c>
-      <c r="D123" s="103" t="s">
+      <c r="D123" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E123" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>10</v>
       </c>
       <c r="B124" t="s">
         <v>68</v>
       </c>
-      <c r="C124" s="104" t="s">
+      <c r="C124" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D124" s="104" t="s">
+      <c r="D124" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E124" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>10</v>
       </c>
       <c r="B125" t="s">
         <v>70</v>
       </c>
-      <c r="C125" s="104" t="s">
+      <c r="C125" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D125" s="104" t="s">
+      <c r="D125" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E125" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>10</v>
       </c>
       <c r="B126" t="s">
         <v>75</v>
       </c>
-      <c r="C126" s="104" t="s">
+      <c r="C126" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D126" s="104" t="s">
+      <c r="D126" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E126" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>11</v>
       </c>
       <c r="B127" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="103" t="s">
+      <c r="C127" s="100" t="s">
         <v>225</v>
       </c>
-      <c r="D127" s="103" t="s">
+      <c r="D127" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E127" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>11</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
-      <c r="C128" s="103" t="s">
+      <c r="C128" s="100" t="s">
         <v>222</v>
       </c>
-      <c r="D128" s="103" t="s">
+      <c r="D128" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E128" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>11</v>
       </c>
       <c r="B129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="103" t="s">
+      <c r="C129" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D129" s="103" t="s">
+      <c r="D129" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E129" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>11</v>
       </c>
       <c r="B130" t="s">
         <v>294</v>
       </c>
-      <c r="C130" s="103" t="s">
+      <c r="C130" s="100" t="s">
         <v>229</v>
       </c>
-      <c r="D130" s="103" t="s">
+      <c r="D130" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E130" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>11</v>
       </c>
       <c r="B131" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="103" t="s">
+      <c r="C131" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="D131" s="103" t="s">
+      <c r="D131" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E131" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>11</v>
       </c>
       <c r="B132" t="s">
         <v>295</v>
       </c>
-      <c r="C132" s="103" t="s">
+      <c r="C132" s="100" t="s">
         <v>314</v>
       </c>
-      <c r="D132" s="103" t="s">
+      <c r="D132" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E132" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>11</v>
       </c>
       <c r="B133" t="s">
         <v>35</v>
       </c>
-      <c r="C133" s="103" t="s">
+      <c r="C133" s="100" t="s">
         <v>315</v>
       </c>
-      <c r="D133" s="103" t="s">
+      <c r="D133" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E133" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>11</v>
       </c>
       <c r="B134" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="103" t="s">
+      <c r="C134" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="D134" s="103" t="s">
+      <c r="D134" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E134" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>11</v>
       </c>
       <c r="B135" t="s">
         <v>30</v>
       </c>
-      <c r="C135" s="103" t="s">
+      <c r="C135" s="100" t="s">
         <v>317</v>
       </c>
-      <c r="D135" s="103" t="s">
+      <c r="D135" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E135" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>11</v>
       </c>
       <c r="B136" t="s">
         <v>56</v>
       </c>
-      <c r="C136" s="103" t="s">
+      <c r="C136" s="100" t="s">
         <v>318</v>
       </c>
-      <c r="D136" s="103" t="s">
+      <c r="D136" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E136" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>11</v>
       </c>
       <c r="B137" t="s">
         <v>57</v>
       </c>
-      <c r="C137" s="103" t="s">
+      <c r="C137" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="D137" s="103" t="s">
+      <c r="D137" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E137" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>11</v>
       </c>
       <c r="B138" t="s">
         <v>297</v>
       </c>
-      <c r="C138" s="103" t="s">
+      <c r="C138" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D138" s="103" t="s">
+      <c r="D138" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E138" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>11</v>
       </c>
       <c r="B139" t="s">
         <v>23</v>
       </c>
-      <c r="C139" s="103" t="s">
+      <c r="C139" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D139" s="103" t="s">
+      <c r="D139" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E139" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>11</v>
       </c>
       <c r="B140" t="s">
         <v>47</v>
       </c>
-      <c r="C140" s="104" t="s">
+      <c r="C140" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D140" s="104" t="s">
+      <c r="D140" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E140" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>11</v>
       </c>
       <c r="B141" t="s">
         <v>43</v>
       </c>
-      <c r="C141" s="103" t="s">
+      <c r="C141" s="100" t="s">
         <v>232</v>
       </c>
-      <c r="D141" s="103" t="s">
+      <c r="D141" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E141" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>11</v>
       </c>
       <c r="B142" t="s">
         <v>53</v>
       </c>
-      <c r="C142" s="104" t="s">
+      <c r="C142" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D142" s="104" t="s">
+      <c r="D142" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E142" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>11</v>
       </c>
       <c r="B143" t="s">
         <v>26</v>
       </c>
-      <c r="C143" s="103" t="s">
+      <c r="C143" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D143" s="103" t="s">
+      <c r="D143" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E143" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>11</v>
       </c>
       <c r="B144" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="103" t="s">
+      <c r="C144" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D144" s="103" t="s">
+      <c r="D144" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E144" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>11</v>
       </c>
       <c r="B145" t="s">
         <v>20</v>
       </c>
-      <c r="C145" s="103" t="s">
+      <c r="C145" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D145" s="103" t="s">
+      <c r="D145" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E145" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>11</v>
       </c>
       <c r="B146" t="s">
         <v>59</v>
       </c>
-      <c r="C146" s="103" t="s">
+      <c r="C146" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D146" s="103" t="s">
+      <c r="D146" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E146" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>11</v>
       </c>
       <c r="B147" t="s">
         <v>61</v>
       </c>
-      <c r="C147" s="103" t="s">
+      <c r="C147" s="100" t="s">
         <v>233</v>
       </c>
-      <c r="D147" s="103" t="s">
+      <c r="D147" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E147" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>11</v>
       </c>
       <c r="B148" t="s">
         <v>66</v>
       </c>
-      <c r="C148" s="103" t="s">
+      <c r="C148" s="100" t="s">
         <v>320</v>
       </c>
-      <c r="D148" s="103" t="s">
+      <c r="D148" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E148" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>11</v>
       </c>
       <c r="B149" t="s">
         <v>68</v>
       </c>
-      <c r="C149" s="104" t="s">
+      <c r="C149" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D149" s="104" t="s">
+      <c r="D149" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E149" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>11</v>
       </c>
       <c r="B150" t="s">
         <v>70</v>
       </c>
-      <c r="C150" s="103" t="s">
+      <c r="C150" s="100" t="s">
         <v>233</v>
       </c>
-      <c r="D150" s="103" t="s">
+      <c r="D150" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E150" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>11</v>
       </c>
       <c r="B151" t="s">
         <v>75</v>
       </c>
-      <c r="C151" s="104" t="s">
+      <c r="C151" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D151" s="104" t="s">
+      <c r="D151" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E151" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>12</v>
       </c>
       <c r="B152" t="s">
         <v>11</v>
       </c>
-      <c r="C152" s="103" t="s">
+      <c r="C152" s="100" t="s">
         <v>237</v>
       </c>
-      <c r="D152" s="103" t="s">
+      <c r="D152" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E152" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>12</v>
       </c>
       <c r="B153" t="s">
         <v>7</v>
       </c>
-      <c r="C153" s="103" t="s">
+      <c r="C153" s="100" t="s">
         <v>234</v>
       </c>
-      <c r="D153" s="103" t="s">
+      <c r="D153" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E153" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>12</v>
       </c>
       <c r="B154" t="s">
         <v>9</v>
       </c>
-      <c r="C154" s="103" t="s">
+      <c r="C154" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="D154" s="103" t="s">
+      <c r="D154" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E154" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>12</v>
       </c>
       <c r="B155" t="s">
         <v>294</v>
       </c>
-      <c r="C155" s="103" t="s">
+      <c r="C155" s="100" t="s">
         <v>321</v>
       </c>
-      <c r="D155" s="103" t="s">
+      <c r="D155" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E155" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>12</v>
       </c>
       <c r="B156" t="s">
         <v>32</v>
       </c>
-      <c r="C156" s="103" t="s">
+      <c r="C156" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="D156" s="103" t="s">
+      <c r="D156" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E156" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>12</v>
       </c>
       <c r="B157" t="s">
         <v>295</v>
       </c>
-      <c r="C157" s="103" t="s">
+      <c r="C157" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="D157" s="103" t="s">
+      <c r="D157" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E157" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>12</v>
       </c>
       <c r="B158" t="s">
         <v>35</v>
       </c>
-      <c r="C158" s="103" t="s">
+      <c r="C158" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="D158" s="103" t="s">
+      <c r="D158" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E158" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>12</v>
       </c>
       <c r="B159" t="s">
         <v>37</v>
       </c>
-      <c r="C159" s="103" t="s">
+      <c r="C159" s="100" t="s">
         <v>324</v>
       </c>
-      <c r="D159" s="103" t="s">
+      <c r="D159" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E159" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>12</v>
       </c>
       <c r="B160" t="s">
         <v>30</v>
       </c>
-      <c r="C160" s="103" t="s">
+      <c r="C160" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D160" s="103" t="s">
+      <c r="D160" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E160" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>12</v>
       </c>
       <c r="B161" t="s">
         <v>56</v>
       </c>
-      <c r="C161" s="103" t="s">
+      <c r="C161" s="100" t="s">
         <v>326</v>
       </c>
-      <c r="D161" s="103" t="s">
+      <c r="D161" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E161" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>12</v>
       </c>
       <c r="B162" t="s">
         <v>57</v>
       </c>
-      <c r="C162" s="103" t="s">
+      <c r="C162" s="100" t="s">
         <v>327</v>
       </c>
-      <c r="D162" s="103" t="s">
+      <c r="D162" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E162" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>12</v>
       </c>
       <c r="B163" t="s">
         <v>297</v>
       </c>
-      <c r="C163" s="103" t="s">
+      <c r="C163" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D163" s="103" t="s">
+      <c r="D163" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E163" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>12</v>
       </c>
       <c r="B164" t="s">
         <v>23</v>
       </c>
-      <c r="C164" s="103" t="s">
+      <c r="C164" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D164" s="103" t="s">
+      <c r="D164" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E164" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>12</v>
       </c>
       <c r="B165" t="s">
         <v>47</v>
       </c>
-      <c r="C165" s="104" t="s">
+      <c r="C165" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D165" s="104" t="s">
+      <c r="D165" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E165" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>12</v>
       </c>
       <c r="B166" t="s">
         <v>43</v>
       </c>
-      <c r="C166" s="103" t="s">
+      <c r="C166" s="100" t="s">
         <v>241</v>
       </c>
-      <c r="D166" s="103" t="s">
+      <c r="D166" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E166" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>12</v>
       </c>
       <c r="B167" t="s">
         <v>53</v>
       </c>
-      <c r="C167" s="104" t="s">
+      <c r="C167" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D167" s="104" t="s">
+      <c r="D167" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E167" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>26</v>
       </c>
-      <c r="C168" s="103" t="s">
+      <c r="C168" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D168" s="103" t="s">
+      <c r="D168" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E168" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>12</v>
       </c>
       <c r="B169" t="s">
         <v>19</v>
       </c>
-      <c r="C169" s="103" t="s">
+      <c r="C169" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="D169" s="103" t="s">
+      <c r="D169" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E169" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>12</v>
       </c>
       <c r="B170" t="s">
         <v>20</v>
       </c>
-      <c r="C170" s="103" t="s">
+      <c r="C170" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="D170" s="103" t="s">
+      <c r="D170" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E170" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>12</v>
       </c>
       <c r="B171" t="s">
         <v>59</v>
       </c>
-      <c r="C171" s="103" t="s">
+      <c r="C171" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D171" s="103" t="s">
+      <c r="D171" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E171" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>12</v>
       </c>
       <c r="B172" t="s">
         <v>61</v>
       </c>
-      <c r="C172" s="103" t="s">
+      <c r="C172" s="100" t="s">
         <v>242</v>
       </c>
-      <c r="D172" s="103" t="s">
+      <c r="D172" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E172" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>12</v>
       </c>
       <c r="B173" t="s">
         <v>66</v>
       </c>
-      <c r="C173" s="103" t="s">
+      <c r="C173" s="100" t="s">
         <v>328</v>
       </c>
-      <c r="D173" s="103" t="s">
+      <c r="D173" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E173" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>12</v>
       </c>
       <c r="B174" t="s">
         <v>68</v>
       </c>
-      <c r="C174" s="104" t="s">
+      <c r="C174" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D174" s="104" t="s">
+      <c r="D174" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E174" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>12</v>
       </c>
       <c r="B175" t="s">
         <v>70</v>
       </c>
-      <c r="C175" s="103" t="s">
+      <c r="C175" s="100" t="s">
         <v>242</v>
       </c>
-      <c r="D175" s="103" t="s">
+      <c r="D175" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E175" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>12</v>
       </c>
       <c r="B176" t="s">
         <v>75</v>
       </c>
-      <c r="C176" s="104" t="s">
+      <c r="C176" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D176" s="104" t="s">
+      <c r="D176" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E176" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>13</v>
       </c>
       <c r="B177" t="s">
         <v>11</v>
       </c>
-      <c r="C177" s="103" t="s">
+      <c r="C177" s="100" t="s">
         <v>245</v>
       </c>
-      <c r="D177" s="103" t="s">
+      <c r="D177" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E177" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>13</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
       </c>
-      <c r="C178" s="103" t="s">
+      <c r="C178" s="100" t="s">
         <v>243</v>
       </c>
-      <c r="D178" s="103" t="s">
+      <c r="D178" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E178" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>13</v>
       </c>
       <c r="B179" t="s">
         <v>9</v>
       </c>
-      <c r="C179" s="103" t="s">
+      <c r="C179" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D179" s="103" t="s">
+      <c r="D179" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E179" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>13</v>
       </c>
       <c r="B180" t="s">
         <v>294</v>
       </c>
-      <c r="C180" s="103" t="s">
+      <c r="C180" s="100" t="s">
         <v>229</v>
       </c>
-      <c r="D180" s="103" t="s">
+      <c r="D180" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E180" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>13</v>
       </c>
       <c r="B181" t="s">
         <v>32</v>
       </c>
-      <c r="C181" s="103" t="s">
+      <c r="C181" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="D181" s="103" t="s">
+      <c r="D181" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E181" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>13</v>
       </c>
       <c r="B182" t="s">
         <v>295</v>
       </c>
-      <c r="C182" s="103" t="s">
+      <c r="C182" s="100" t="s">
         <v>329</v>
       </c>
-      <c r="D182" s="103" t="s">
+      <c r="D182" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E182" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>13</v>
       </c>
       <c r="B183" t="s">
         <v>35</v>
       </c>
-      <c r="C183" s="103" t="s">
+      <c r="C183" s="100" t="s">
         <v>330</v>
       </c>
-      <c r="D183" s="103" t="s">
+      <c r="D183" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E183" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>13</v>
       </c>
       <c r="B184" t="s">
         <v>37</v>
       </c>
-      <c r="C184" s="103" t="s">
+      <c r="C184" s="100" t="s">
         <v>331</v>
       </c>
-      <c r="D184" s="103" t="s">
+      <c r="D184" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E184" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>13</v>
       </c>
       <c r="B185" t="s">
         <v>30</v>
       </c>
-      <c r="C185" s="103" t="s">
+      <c r="C185" s="100" t="s">
         <v>332</v>
       </c>
-      <c r="D185" s="103" t="s">
+      <c r="D185" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E185" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>13</v>
       </c>
       <c r="B186" t="s">
         <v>56</v>
       </c>
-      <c r="C186" s="103" t="s">
+      <c r="C186" s="100" t="s">
         <v>333</v>
       </c>
-      <c r="D186" s="103" t="s">
+      <c r="D186" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E186" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>13</v>
       </c>
       <c r="B187" t="s">
         <v>57</v>
       </c>
-      <c r="C187" s="103" t="s">
+      <c r="C187" s="100" t="s">
         <v>334</v>
       </c>
-      <c r="D187" s="103" t="s">
+      <c r="D187" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E187" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>13</v>
       </c>
       <c r="B188" t="s">
         <v>297</v>
       </c>
-      <c r="C188" s="103" t="s">
+      <c r="C188" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D188" s="103" t="s">
+      <c r="D188" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E188" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>13</v>
       </c>
       <c r="B189" t="s">
         <v>23</v>
       </c>
-      <c r="C189" s="103" t="s">
+      <c r="C189" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D189" s="103" t="s">
+      <c r="D189" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E189" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>13</v>
       </c>
       <c r="B190" t="s">
         <v>47</v>
       </c>
-      <c r="C190" s="104" t="s">
+      <c r="C190" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D190" s="104" t="s">
+      <c r="D190" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E190" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>13</v>
       </c>
       <c r="B191" t="s">
         <v>43</v>
       </c>
-      <c r="C191" s="103" t="s">
+      <c r="C191" s="100" t="s">
         <v>249</v>
       </c>
-      <c r="D191" s="103" t="s">
+      <c r="D191" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E191" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>13</v>
       </c>
       <c r="B192" t="s">
         <v>53</v>
       </c>
-      <c r="C192" s="104" t="s">
+      <c r="C192" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D192" s="104" t="s">
+      <c r="D192" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E192" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>13</v>
       </c>
       <c r="B193" t="s">
         <v>26</v>
       </c>
-      <c r="C193" s="103" t="s">
+      <c r="C193" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D193" s="103" t="s">
+      <c r="D193" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E193" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>13</v>
       </c>
       <c r="B194" t="s">
         <v>19</v>
       </c>
-      <c r="C194" s="103" t="s">
+      <c r="C194" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D194" s="103" t="s">
+      <c r="D194" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E194" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>13</v>
       </c>
       <c r="B195" t="s">
         <v>20</v>
       </c>
-      <c r="C195" s="103" t="s">
+      <c r="C195" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D195" s="103" t="s">
+      <c r="D195" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E195" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>13</v>
       </c>
       <c r="B196" t="s">
         <v>59</v>
       </c>
-      <c r="C196" s="103" t="s">
+      <c r="C196" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D196" s="103" t="s">
+      <c r="D196" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E196" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>13</v>
       </c>
       <c r="B197" t="s">
         <v>61</v>
       </c>
-      <c r="C197" s="103" t="s">
+      <c r="C197" s="100" t="s">
         <v>233</v>
       </c>
-      <c r="D197" s="103" t="s">
+      <c r="D197" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E197" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>13</v>
       </c>
       <c r="B198" t="s">
         <v>66</v>
       </c>
-      <c r="C198" s="103" t="s">
+      <c r="C198" s="100" t="s">
         <v>320</v>
       </c>
-      <c r="D198" s="103" t="s">
+      <c r="D198" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E198" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>13</v>
       </c>
       <c r="B199" t="s">
         <v>68</v>
       </c>
-      <c r="C199" s="104" t="s">
+      <c r="C199" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D199" s="104" t="s">
+      <c r="D199" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E199" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>13</v>
       </c>
       <c r="B200" t="s">
         <v>70</v>
       </c>
-      <c r="C200" s="103" t="s">
+      <c r="C200" s="100" t="s">
         <v>233</v>
       </c>
-      <c r="D200" s="103" t="s">
+      <c r="D200" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E200" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>13</v>
       </c>
       <c r="B201" t="s">
         <v>75</v>
       </c>
-      <c r="C201" s="104" t="s">
+      <c r="C201" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D201" s="104" t="s">
+      <c r="D201" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E201" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>14</v>
       </c>
       <c r="B202" t="s">
         <v>11</v>
       </c>
-      <c r="C202" s="103" t="s">
+      <c r="C202" s="100" t="s">
         <v>252</v>
       </c>
-      <c r="D202" s="103" t="s">
+      <c r="D202" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E202" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>14</v>
       </c>
       <c r="B203" t="s">
         <v>7</v>
       </c>
-      <c r="C203" s="103" t="s">
+      <c r="C203" s="100" t="s">
         <v>250</v>
       </c>
-      <c r="D203" s="103" t="s">
+      <c r="D203" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E203" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>14</v>
       </c>
       <c r="B204" t="s">
         <v>9</v>
       </c>
-      <c r="C204" s="103" t="s">
+      <c r="C204" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="D204" s="103" t="s">
+      <c r="D204" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E204" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>14</v>
       </c>
       <c r="B205" t="s">
         <v>294</v>
       </c>
-      <c r="C205" s="103" t="s">
+      <c r="C205" s="100" t="s">
         <v>321</v>
       </c>
-      <c r="D205" s="103" t="s">
+      <c r="D205" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E205" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>14</v>
       </c>
       <c r="B206" t="s">
         <v>32</v>
       </c>
-      <c r="C206" s="103" t="s">
+      <c r="C206" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="D206" s="103" t="s">
+      <c r="D206" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E206" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>14</v>
       </c>
       <c r="B207" t="s">
         <v>295</v>
       </c>
-      <c r="C207" s="103" t="s">
+      <c r="C207" s="100" t="s">
         <v>335</v>
       </c>
-      <c r="D207" s="103" t="s">
+      <c r="D207" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E207" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>14</v>
       </c>
       <c r="B208" t="s">
         <v>35</v>
       </c>
-      <c r="C208" s="103" t="s">
+      <c r="C208" s="100" t="s">
         <v>336</v>
       </c>
-      <c r="D208" s="103" t="s">
+      <c r="D208" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E208" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>14</v>
       </c>
       <c r="B209" t="s">
         <v>37</v>
       </c>
-      <c r="C209" s="103" t="s">
+      <c r="C209" s="100" t="s">
         <v>337</v>
       </c>
-      <c r="D209" s="103" t="s">
+      <c r="D209" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E209" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>14</v>
       </c>
       <c r="B210" t="s">
         <v>30</v>
       </c>
-      <c r="C210" s="103" t="s">
+      <c r="C210" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D210" s="103" t="s">
+      <c r="D210" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E210" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>14</v>
       </c>
       <c r="B211" t="s">
         <v>56</v>
       </c>
-      <c r="C211" s="103" t="s">
+      <c r="C211" s="100" t="s">
         <v>338</v>
       </c>
-      <c r="D211" s="103" t="s">
+      <c r="D211" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E211" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>14</v>
       </c>
       <c r="B212" t="s">
         <v>57</v>
       </c>
-      <c r="C212" s="103" t="s">
+      <c r="C212" s="100" t="s">
         <v>339</v>
       </c>
-      <c r="D212" s="103" t="s">
+      <c r="D212" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E212" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>14</v>
       </c>
       <c r="B213" t="s">
         <v>297</v>
       </c>
-      <c r="C213" s="103" t="s">
+      <c r="C213" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D213" s="103" t="s">
+      <c r="D213" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E213" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>14</v>
       </c>
       <c r="B214" t="s">
         <v>23</v>
       </c>
-      <c r="C214" s="103" t="s">
+      <c r="C214" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D214" s="103" t="s">
+      <c r="D214" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E214" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>14</v>
       </c>
       <c r="B215" t="s">
         <v>47</v>
       </c>
-      <c r="C215" s="104" t="s">
+      <c r="C215" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D215" s="104" t="s">
+      <c r="D215" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E215" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>14</v>
       </c>
       <c r="B216" t="s">
         <v>43</v>
       </c>
-      <c r="C216" s="103" t="s">
+      <c r="C216" s="100" t="s">
         <v>255</v>
       </c>
-      <c r="D216" s="103" t="s">
+      <c r="D216" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E216" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>14</v>
       </c>
       <c r="B217" t="s">
         <v>53</v>
       </c>
-      <c r="C217" s="104" t="s">
+      <c r="C217" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D217" s="104" t="s">
+      <c r="D217" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E217" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>14</v>
       </c>
       <c r="B218" t="s">
         <v>26</v>
       </c>
-      <c r="C218" s="103" t="s">
+      <c r="C218" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D218" s="103" t="s">
+      <c r="D218" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E218" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>14</v>
       </c>
       <c r="B219" t="s">
         <v>19</v>
       </c>
-      <c r="C219" s="103" t="s">
+      <c r="C219" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="D219" s="103" t="s">
+      <c r="D219" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E219" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>14</v>
       </c>
       <c r="B220" t="s">
         <v>20</v>
       </c>
-      <c r="C220" s="103" t="s">
+      <c r="C220" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="D220" s="103" t="s">
+      <c r="D220" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E220" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>14</v>
       </c>
       <c r="B221" t="s">
         <v>59</v>
       </c>
-      <c r="C221" s="103" t="s">
+      <c r="C221" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D221" s="103" t="s">
+      <c r="D221" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E221" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>14</v>
       </c>
       <c r="B222" t="s">
         <v>61</v>
       </c>
-      <c r="C222" s="103" t="s">
+      <c r="C222" s="100" t="s">
         <v>242</v>
       </c>
-      <c r="D222" s="103" t="s">
+      <c r="D222" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E222" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>14</v>
       </c>
       <c r="B223" t="s">
         <v>66</v>
       </c>
-      <c r="C223" s="103" t="s">
+      <c r="C223" s="100" t="s">
         <v>328</v>
       </c>
-      <c r="D223" s="103" t="s">
+      <c r="D223" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E223" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>14</v>
       </c>
       <c r="B224" t="s">
         <v>68</v>
       </c>
-      <c r="C224" s="104" t="s">
+      <c r="C224" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D224" s="104" t="s">
+      <c r="D224" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E224" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>14</v>
       </c>
       <c r="B225" t="s">
         <v>70</v>
       </c>
-      <c r="C225" s="103" t="s">
+      <c r="C225" s="100" t="s">
         <v>242</v>
       </c>
-      <c r="D225" s="103" t="s">
+      <c r="D225" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E225" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>14</v>
       </c>
       <c r="B226" t="s">
         <v>75</v>
       </c>
-      <c r="C226" s="104" t="s">
+      <c r="C226" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D226" s="104" t="s">
+      <c r="D226" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E226" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>15</v>
       </c>
       <c r="B227" t="s">
         <v>11</v>
       </c>
-      <c r="C227" s="103" t="s">
+      <c r="C227" s="100" t="s">
         <v>258</v>
       </c>
-      <c r="D227" s="103" t="s">
+      <c r="D227" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E227" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>15</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
       </c>
-      <c r="C228" s="103" t="s">
+      <c r="C228" s="100" t="s">
         <v>256</v>
       </c>
-      <c r="D228" s="103" t="s">
+      <c r="D228" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E228" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>15</v>
       </c>
       <c r="B229" t="s">
         <v>9</v>
       </c>
-      <c r="C229" s="103" t="s">
+      <c r="C229" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D229" s="103" t="s">
+      <c r="D229" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E229" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>15</v>
       </c>
       <c r="B230" t="s">
         <v>294</v>
       </c>
-      <c r="C230" s="103" t="s">
+      <c r="C230" s="100" t="s">
         <v>340</v>
       </c>
-      <c r="D230" s="103" t="s">
+      <c r="D230" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E230" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>15</v>
       </c>
       <c r="B231" t="s">
         <v>32</v>
       </c>
-      <c r="C231" s="103" t="s">
+      <c r="C231" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="D231" s="103" t="s">
+      <c r="D231" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E231" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>15</v>
       </c>
       <c r="B232" t="s">
         <v>295</v>
       </c>
-      <c r="C232" s="103" t="s">
+      <c r="C232" s="100" t="s">
         <v>341</v>
       </c>
-      <c r="D232" s="103" t="s">
+      <c r="D232" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E232" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>15</v>
       </c>
       <c r="B233" t="s">
         <v>35</v>
       </c>
-      <c r="C233" s="103" t="s">
+      <c r="C233" s="100" t="s">
         <v>342</v>
       </c>
-      <c r="D233" s="103" t="s">
+      <c r="D233" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E233" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>15</v>
       </c>
       <c r="B234" t="s">
         <v>37</v>
       </c>
-      <c r="C234" s="103" t="s">
+      <c r="C234" s="100" t="s">
         <v>343</v>
       </c>
-      <c r="D234" s="103" t="s">
+      <c r="D234" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E234" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>15</v>
       </c>
       <c r="B235" t="s">
         <v>30</v>
       </c>
-      <c r="C235" s="103" t="s">
+      <c r="C235" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D235" s="103" t="s">
+      <c r="D235" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E235" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>15</v>
       </c>
       <c r="B236" t="s">
         <v>56</v>
       </c>
-      <c r="C236" s="103" t="s">
+      <c r="C236" s="100" t="s">
         <v>342</v>
       </c>
-      <c r="D236" s="103" t="s">
+      <c r="D236" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E236" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>15</v>
       </c>
       <c r="B237" t="s">
         <v>57</v>
       </c>
-      <c r="C237" s="103" t="s">
+      <c r="C237" s="100" t="s">
         <v>343</v>
       </c>
-      <c r="D237" s="103" t="s">
+      <c r="D237" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E237" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>15</v>
       </c>
       <c r="B238" t="s">
         <v>297</v>
       </c>
-      <c r="C238" s="103" t="s">
+      <c r="C238" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D238" s="103" t="s">
+      <c r="D238" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E238" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>15</v>
       </c>
       <c r="B239" t="s">
         <v>23</v>
       </c>
-      <c r="C239" s="103" t="s">
+      <c r="C239" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="D239" s="103" t="s">
+      <c r="D239" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E239" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>15</v>
       </c>
       <c r="B240" t="s">
         <v>47</v>
       </c>
-      <c r="C240" s="104" t="s">
+      <c r="C240" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D240" s="104" t="s">
+      <c r="D240" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E240" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>15</v>
       </c>
       <c r="B241" t="s">
         <v>43</v>
       </c>
-      <c r="C241" s="103" t="s">
+      <c r="C241" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="D241" s="103" t="s">
+      <c r="D241" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E241" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>15</v>
       </c>
       <c r="B242" t="s">
         <v>53</v>
       </c>
-      <c r="C242" s="104" t="s">
+      <c r="C242" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D242" s="104" t="s">
+      <c r="D242" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E242" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>15</v>
       </c>
       <c r="B243" t="s">
         <v>26</v>
       </c>
-      <c r="C243" s="103" t="s">
+      <c r="C243" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D243" s="103" t="s">
+      <c r="D243" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E243" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>15</v>
       </c>
       <c r="B244" t="s">
         <v>19</v>
       </c>
-      <c r="C244" s="103" t="s">
+      <c r="C244" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="D244" s="103" t="s">
+      <c r="D244" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E244" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>15</v>
       </c>
       <c r="B245" t="s">
         <v>20</v>
       </c>
-      <c r="C245" s="103" t="s">
+      <c r="C245" s="100" t="s">
         <v>261</v>
       </c>
-      <c r="D245" s="103" t="s">
+      <c r="D245" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E245" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>15</v>
       </c>
       <c r="B246" t="s">
         <v>59</v>
       </c>
-      <c r="C246" s="103" t="s">
+      <c r="C246" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D246" s="103" t="s">
+      <c r="D246" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E246" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>15</v>
       </c>
       <c r="B247" t="s">
         <v>61</v>
       </c>
-      <c r="C247" s="103" t="s">
+      <c r="C247" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="D247" s="103" t="s">
+      <c r="D247" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E247" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>15</v>
       </c>
       <c r="B248" t="s">
         <v>66</v>
       </c>
-      <c r="C248" s="103" t="s">
+      <c r="C248" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="D248" s="103" t="s">
+      <c r="D248" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E248" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>15</v>
       </c>
       <c r="B249" t="s">
         <v>68</v>
       </c>
-      <c r="C249" s="103" t="s">
+      <c r="C249" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="D249" s="103" t="s">
+      <c r="D249" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E249" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>15</v>
       </c>
       <c r="B250" t="s">
         <v>70</v>
       </c>
-      <c r="C250" s="103" t="s">
+      <c r="C250" s="100" t="s">
         <v>264</v>
       </c>
-      <c r="D250" s="103" t="s">
+      <c r="D250" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E250" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>15</v>
       </c>
       <c r="B251" t="s">
         <v>75</v>
       </c>
-      <c r="C251" s="103" t="s">
+      <c r="C251" s="100" t="s">
         <v>346</v>
       </c>
-      <c r="D251" s="103" t="s">
+      <c r="D251" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E251" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>16</v>
       </c>
       <c r="B252" t="s">
         <v>11</v>
       </c>
-      <c r="C252" s="103" t="s">
+      <c r="C252" s="100" t="s">
         <v>267</v>
       </c>
-      <c r="D252" s="103" t="s">
+      <c r="D252" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E252" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>16</v>
       </c>
       <c r="B253" t="s">
         <v>7</v>
       </c>
-      <c r="C253" s="103" t="s">
+      <c r="C253" s="100" t="s">
         <v>265</v>
       </c>
-      <c r="D253" s="103" t="s">
+      <c r="D253" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E253" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>16</v>
       </c>
       <c r="B254" t="s">
         <v>9</v>
       </c>
-      <c r="C254" s="103" t="s">
+      <c r="C254" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D254" s="103" t="s">
+      <c r="D254" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E254" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>16</v>
       </c>
       <c r="B255" t="s">
         <v>294</v>
       </c>
-      <c r="C255" s="103" t="s">
+      <c r="C255" s="100" t="s">
         <v>347</v>
       </c>
-      <c r="D255" s="103" t="s">
+      <c r="D255" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E255" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>16</v>
       </c>
       <c r="B256" t="s">
         <v>32</v>
       </c>
-      <c r="C256" s="103" t="s">
+      <c r="C256" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D256" s="103" t="s">
+      <c r="D256" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E256" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>16</v>
       </c>
       <c r="B257" t="s">
         <v>295</v>
       </c>
-      <c r="C257" s="103" t="s">
+      <c r="C257" s="100" t="s">
         <v>348</v>
       </c>
-      <c r="D257" s="103" t="s">
+      <c r="D257" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E257" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>16</v>
       </c>
       <c r="B258" t="s">
         <v>35</v>
       </c>
-      <c r="C258" s="103" t="s">
+      <c r="C258" s="100" t="s">
         <v>349</v>
       </c>
-      <c r="D258" s="103" t="s">
+      <c r="D258" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E258" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>16</v>
       </c>
       <c r="B259" t="s">
         <v>37</v>
       </c>
-      <c r="C259" s="103" t="s">
+      <c r="C259" s="100" t="s">
         <v>349</v>
       </c>
-      <c r="D259" s="103" t="s">
+      <c r="D259" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E259" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>16</v>
       </c>
       <c r="B260" t="s">
         <v>30</v>
       </c>
-      <c r="C260" s="103" t="s">
+      <c r="C260" s="100" t="s">
         <v>350</v>
       </c>
-      <c r="D260" s="103" t="s">
+      <c r="D260" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E260" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>16</v>
       </c>
       <c r="B261" t="s">
         <v>56</v>
       </c>
-      <c r="C261" s="103" t="s">
+      <c r="C261" s="100" t="s">
         <v>351</v>
       </c>
-      <c r="D261" s="103" t="s">
+      <c r="D261" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E261" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>16</v>
       </c>
       <c r="B262" t="s">
         <v>57</v>
       </c>
-      <c r="C262" s="103" t="s">
+      <c r="C262" s="100" t="s">
         <v>349</v>
       </c>
-      <c r="D262" s="103" t="s">
+      <c r="D262" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E262" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>16</v>
       </c>
       <c r="B263" t="s">
         <v>297</v>
       </c>
-      <c r="C263" s="103" t="s">
+      <c r="C263" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D263" s="103" t="s">
+      <c r="D263" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E263" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>16</v>
       </c>
       <c r="B264" t="s">
         <v>23</v>
       </c>
-      <c r="C264" s="103" t="s">
+      <c r="C264" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D264" s="103" t="s">
+      <c r="D264" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E264" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>16</v>
       </c>
       <c r="B265" t="s">
         <v>47</v>
       </c>
-      <c r="C265" s="104" t="s">
+      <c r="C265" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D265" s="104" t="s">
+      <c r="D265" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E265" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>16</v>
       </c>
       <c r="B266" t="s">
         <v>43</v>
       </c>
-      <c r="C266" s="103" t="s">
+      <c r="C266" s="100" t="s">
         <v>271</v>
       </c>
-      <c r="D266" s="103" t="s">
+      <c r="D266" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E266" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>16</v>
       </c>
       <c r="B267" t="s">
         <v>53</v>
       </c>
-      <c r="C267" s="103" t="s">
+      <c r="C267" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D267" s="103" t="s">
+      <c r="D267" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E267" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>16</v>
       </c>
       <c r="B268" t="s">
         <v>26</v>
       </c>
-      <c r="C268" s="103" t="s">
+      <c r="C268" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="D268" s="103" t="s">
+      <c r="D268" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E268" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>16</v>
       </c>
       <c r="B269" t="s">
         <v>19</v>
       </c>
-      <c r="C269" s="103" t="s">
+      <c r="C269" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D269" s="103" t="s">
+      <c r="D269" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E269" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>16</v>
       </c>
       <c r="B270" t="s">
         <v>20</v>
       </c>
-      <c r="C270" s="103" t="s">
+      <c r="C270" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D270" s="103" t="s">
+      <c r="D270" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E270" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>16</v>
       </c>
       <c r="B271" t="s">
         <v>59</v>
       </c>
-      <c r="C271" s="103" t="s">
+      <c r="C271" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D271" s="103" t="s">
+      <c r="D271" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E271" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>16</v>
       </c>
       <c r="B272" t="s">
         <v>61</v>
       </c>
-      <c r="C272" s="103" t="s">
+      <c r="C272" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="D272" s="103" t="s">
+      <c r="D272" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E272" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>16</v>
       </c>
       <c r="B273" t="s">
         <v>66</v>
       </c>
-      <c r="C273" s="103" t="s">
+      <c r="C273" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="D273" s="103" t="s">
+      <c r="D273" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E273" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>16</v>
       </c>
       <c r="B274" t="s">
         <v>68</v>
       </c>
-      <c r="C274" s="104" t="s">
+      <c r="C274" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D274" s="104" t="s">
+      <c r="D274" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E274" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>16</v>
       </c>
       <c r="B275" t="s">
         <v>70</v>
       </c>
-      <c r="C275" s="104" t="s">
+      <c r="C275" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D275" s="104" t="s">
+      <c r="D275" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E275" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>16</v>
       </c>
       <c r="B276" t="s">
         <v>75</v>
       </c>
-      <c r="C276" s="104" t="s">
+      <c r="C276" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D276" s="104" t="s">
+      <c r="D276" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E276" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>17</v>
       </c>
       <c r="B277" t="s">
         <v>11</v>
       </c>
-      <c r="C277" s="103" t="s">
+      <c r="C277" s="100" t="s">
         <v>275</v>
       </c>
-      <c r="D277" s="103" t="s">
+      <c r="D277" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E277" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>17</v>
       </c>
       <c r="B278" t="s">
         <v>7</v>
       </c>
-      <c r="C278" s="103" t="s">
+      <c r="C278" s="100" t="s">
         <v>273</v>
       </c>
-      <c r="D278" s="103" t="s">
+      <c r="D278" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E278" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>17</v>
       </c>
       <c r="B279" t="s">
         <v>9</v>
       </c>
-      <c r="C279" s="103" t="s">
+      <c r="C279" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D279" s="103" t="s">
+      <c r="D279" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E279" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>17</v>
       </c>
       <c r="B280" t="s">
         <v>294</v>
       </c>
-      <c r="C280" s="103" t="s">
+      <c r="C280" s="100" t="s">
         <v>352</v>
       </c>
-      <c r="D280" s="103" t="s">
+      <c r="D280" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E280" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>17</v>
       </c>
       <c r="B281" t="s">
         <v>32</v>
       </c>
-      <c r="C281" s="103" t="s">
+      <c r="C281" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D281" s="103" t="s">
+      <c r="D281" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E281" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>17</v>
       </c>
       <c r="B282" t="s">
         <v>295</v>
       </c>
-      <c r="C282" s="103" t="s">
+      <c r="C282" s="100" t="s">
         <v>353</v>
       </c>
-      <c r="D282" s="103" t="s">
+      <c r="D282" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E282" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>17</v>
       </c>
       <c r="B283" t="s">
         <v>35</v>
       </c>
-      <c r="C283" s="103" t="s">
+      <c r="C283" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="D283" s="103" t="s">
+      <c r="D283" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E283" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>17</v>
       </c>
       <c r="B284" t="s">
         <v>37</v>
       </c>
-      <c r="C284" s="103" t="s">
+      <c r="C284" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="D284" s="103" t="s">
+      <c r="D284" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E284" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>17</v>
       </c>
       <c r="B285" t="s">
         <v>30</v>
       </c>
-      <c r="C285" s="103" t="s">
+      <c r="C285" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D285" s="103" t="s">
+      <c r="D285" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E285" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>17</v>
       </c>
       <c r="B286" t="s">
         <v>56</v>
       </c>
-      <c r="C286" s="103" t="s">
+      <c r="C286" s="100" t="s">
         <v>355</v>
       </c>
-      <c r="D286" s="103" t="s">
+      <c r="D286" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E286" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>17</v>
       </c>
       <c r="B287" t="s">
         <v>57</v>
       </c>
-      <c r="C287" s="103" t="s">
+      <c r="C287" s="100" t="s">
         <v>354</v>
       </c>
-      <c r="D287" s="103" t="s">
+      <c r="D287" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E287" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>17</v>
       </c>
       <c r="B288" t="s">
         <v>297</v>
       </c>
-      <c r="C288" s="103" t="s">
+      <c r="C288" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D288" s="103" t="s">
+      <c r="D288" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E288" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>17</v>
       </c>
       <c r="B289" t="s">
         <v>23</v>
       </c>
-      <c r="C289" s="103" t="s">
+      <c r="C289" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D289" s="103" t="s">
+      <c r="D289" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E289" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>17</v>
       </c>
       <c r="B290" t="s">
         <v>47</v>
       </c>
-      <c r="C290" s="104" t="s">
+      <c r="C290" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D290" s="104" t="s">
+      <c r="D290" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E290" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>17</v>
       </c>
       <c r="B291" t="s">
         <v>43</v>
       </c>
-      <c r="C291" s="103" t="s">
+      <c r="C291" s="100" t="s">
         <v>278</v>
       </c>
-      <c r="D291" s="103" t="s">
+      <c r="D291" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E291" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>17</v>
       </c>
       <c r="B292" t="s">
         <v>53</v>
       </c>
-      <c r="C292" s="103" t="s">
+      <c r="C292" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D292" s="103" t="s">
+      <c r="D292" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E292" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>17</v>
       </c>
       <c r="B293" t="s">
         <v>26</v>
       </c>
-      <c r="C293" s="103" t="s">
+      <c r="C293" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D293" s="103" t="s">
+      <c r="D293" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E293" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>17</v>
       </c>
       <c r="B294" t="s">
         <v>19</v>
       </c>
-      <c r="C294" s="103" t="s">
+      <c r="C294" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="D294" s="103" t="s">
+      <c r="D294" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E294" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>17</v>
       </c>
       <c r="B295" t="s">
         <v>20</v>
       </c>
-      <c r="C295" s="103" t="s">
+      <c r="C295" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="D295" s="103" t="s">
+      <c r="D295" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E295" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>17</v>
       </c>
       <c r="B296" t="s">
         <v>59</v>
       </c>
-      <c r="C296" s="103" t="s">
+      <c r="C296" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D296" s="103" t="s">
+      <c r="D296" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E296" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>17</v>
       </c>
       <c r="B297" t="s">
         <v>61</v>
       </c>
-      <c r="C297" s="103" t="s">
+      <c r="C297" s="100" t="s">
         <v>280</v>
       </c>
-      <c r="D297" s="103" t="s">
+      <c r="D297" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E297" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>17</v>
       </c>
       <c r="B298" t="s">
         <v>66</v>
       </c>
-      <c r="C298" s="103" t="s">
+      <c r="C298" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="D298" s="103" t="s">
+      <c r="D298" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E298" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>17</v>
       </c>
       <c r="B299" t="s">
         <v>68</v>
       </c>
-      <c r="C299" s="104" t="s">
+      <c r="C299" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D299" s="104" t="s">
+      <c r="D299" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E299" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>17</v>
       </c>
       <c r="B300" t="s">
         <v>70</v>
       </c>
-      <c r="C300" s="104" t="s">
+      <c r="C300" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D300" s="104" t="s">
+      <c r="D300" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E300" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>17</v>
       </c>
       <c r="B301" t="s">
         <v>75</v>
       </c>
-      <c r="C301" s="104" t="s">
+      <c r="C301" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D301" s="104" t="s">
+      <c r="D301" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E301" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>18</v>
       </c>
       <c r="B302" t="s">
         <v>11</v>
       </c>
-      <c r="C302" s="103" t="s">
+      <c r="C302" s="100" t="s">
         <v>283</v>
       </c>
-      <c r="D302" s="103" t="s">
+      <c r="D302" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E302" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>18</v>
       </c>
       <c r="B303" t="s">
         <v>7</v>
       </c>
-      <c r="C303" s="103" t="s">
+      <c r="C303" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="D303" s="103" t="s">
+      <c r="D303" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E303" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>18</v>
       </c>
       <c r="B304" t="s">
         <v>9</v>
       </c>
-      <c r="C304" s="103" t="s">
+      <c r="C304" s="100" t="s">
         <v>224</v>
       </c>
-      <c r="D304" s="103" t="s">
+      <c r="D304" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E304" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>18</v>
       </c>
       <c r="B305" t="s">
         <v>294</v>
       </c>
-      <c r="C305" s="103" t="s">
+      <c r="C305" s="100" t="s">
         <v>352</v>
       </c>
-      <c r="D305" s="103" t="s">
+      <c r="D305" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E305" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>18</v>
       </c>
       <c r="B306" t="s">
         <v>32</v>
       </c>
-      <c r="C306" s="103" t="s">
+      <c r="C306" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D306" s="103" t="s">
+      <c r="D306" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E306" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>18</v>
       </c>
       <c r="B307" t="s">
         <v>295</v>
       </c>
-      <c r="C307" s="103" t="s">
+      <c r="C307" s="100" t="s">
         <v>356</v>
       </c>
-      <c r="D307" s="103" t="s">
+      <c r="D307" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E307" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>18</v>
       </c>
       <c r="B308" t="s">
         <v>35</v>
       </c>
-      <c r="C308" s="103" t="s">
+      <c r="C308" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="D308" s="103" t="s">
+      <c r="D308" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E308" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>18</v>
       </c>
       <c r="B309" t="s">
         <v>37</v>
       </c>
-      <c r="C309" s="103" t="s">
+      <c r="C309" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="D309" s="103" t="s">
+      <c r="D309" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E309" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>18</v>
       </c>
       <c r="B310" t="s">
         <v>30</v>
       </c>
-      <c r="C310" s="103" t="s">
+      <c r="C310" s="100" t="s">
         <v>325</v>
       </c>
-      <c r="D310" s="103" t="s">
+      <c r="D310" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E310" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>18</v>
       </c>
       <c r="B311" t="s">
         <v>56</v>
       </c>
-      <c r="C311" s="103" t="s">
+      <c r="C311" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="D311" s="103" t="s">
+      <c r="D311" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E311" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>18</v>
       </c>
       <c r="B312" t="s">
         <v>57</v>
       </c>
-      <c r="C312" s="103" t="s">
+      <c r="C312" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="D312" s="103" t="s">
+      <c r="D312" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E312" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>18</v>
       </c>
       <c r="B313" t="s">
         <v>297</v>
       </c>
-      <c r="C313" s="103" t="s">
+      <c r="C313" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="D313" s="103" t="s">
+      <c r="D313" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E313" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>18</v>
       </c>
       <c r="B314" t="s">
         <v>23</v>
       </c>
-      <c r="C314" s="103" t="s">
+      <c r="C314" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="D314" s="103" t="s">
+      <c r="D314" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E314" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>18</v>
       </c>
       <c r="B315" t="s">
         <v>47</v>
       </c>
-      <c r="C315" s="104" t="s">
+      <c r="C315" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D315" s="104" t="s">
+      <c r="D315" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E315" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>18</v>
       </c>
       <c r="B316" t="s">
         <v>43</v>
       </c>
-      <c r="C316" s="103" t="s">
+      <c r="C316" s="100" t="s">
         <v>286</v>
       </c>
-      <c r="D316" s="103" t="s">
+      <c r="D316" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E316" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>18</v>
       </c>
       <c r="B317" t="s">
         <v>53</v>
       </c>
-      <c r="C317" s="103" t="s">
+      <c r="C317" s="100" t="s">
         <v>187</v>
       </c>
-      <c r="D317" s="103" t="s">
+      <c r="D317" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E317" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>18</v>
       </c>
       <c r="B318" t="s">
         <v>26</v>
       </c>
-      <c r="C318" s="103" t="s">
+      <c r="C318" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="D318" s="103" t="s">
+      <c r="D318" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E318" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>18</v>
       </c>
       <c r="B319" t="s">
         <v>19</v>
       </c>
-      <c r="C319" s="103" t="s">
+      <c r="C319" s="100" t="s">
         <v>157</v>
       </c>
-      <c r="D319" s="103" t="s">
+      <c r="D319" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E319" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>18</v>
       </c>
       <c r="B320" t="s">
         <v>20</v>
       </c>
-      <c r="C320" s="103" t="s">
+      <c r="C320" s="100" t="s">
         <v>158</v>
       </c>
-      <c r="D320" s="103" t="s">
+      <c r="D320" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E320" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>18</v>
       </c>
       <c r="B321" t="s">
         <v>59</v>
       </c>
-      <c r="C321" s="103" t="s">
+      <c r="C321" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D321" s="103" t="s">
+      <c r="D321" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E321" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>18</v>
       </c>
       <c r="B322" t="s">
         <v>61</v>
       </c>
-      <c r="C322" s="103" t="s">
+      <c r="C322" s="100" t="s">
         <v>280</v>
       </c>
-      <c r="D322" s="103" t="s">
+      <c r="D322" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E322" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>18</v>
       </c>
       <c r="B323" t="s">
         <v>66</v>
       </c>
-      <c r="C323" s="103" t="s">
+      <c r="C323" s="100" t="s">
         <v>308</v>
       </c>
-      <c r="D323" s="103" t="s">
+      <c r="D323" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E323" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>18</v>
       </c>
       <c r="B324" t="s">
         <v>68</v>
       </c>
-      <c r="C324" s="104" t="s">
+      <c r="C324" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D324" s="104" t="s">
+      <c r="D324" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E324" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>18</v>
       </c>
       <c r="B325" t="s">
         <v>70</v>
       </c>
-      <c r="C325" s="104" t="s">
+      <c r="C325" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D325" s="104" t="s">
+      <c r="D325" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E325" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>18</v>
       </c>
       <c r="B326" t="s">
         <v>75</v>
       </c>
-      <c r="C326" s="104" t="s">
+      <c r="C326" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D326" s="104" t="s">
+      <c r="D326" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E326" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>19</v>
       </c>
       <c r="B327" t="s">
         <v>11</v>
       </c>
-      <c r="C327" s="103" t="s">
+      <c r="C327" s="100" t="s">
         <v>288</v>
       </c>
-      <c r="D327" s="103" t="s">
+      <c r="D327" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E327" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>19</v>
       </c>
       <c r="B328" t="s">
         <v>7</v>
       </c>
-      <c r="C328" s="103" t="s">
+      <c r="C328" s="100" t="s">
         <v>287</v>
       </c>
-      <c r="D328" s="103" t="s">
+      <c r="D328" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E328" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>19</v>
       </c>
       <c r="B329" t="s">
         <v>9</v>
       </c>
-      <c r="C329" s="103" t="s">
+      <c r="C329" s="100" t="s">
         <v>236</v>
       </c>
-      <c r="D329" s="103" t="s">
+      <c r="D329" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E329" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>19</v>
       </c>
       <c r="B330" t="s">
         <v>294</v>
       </c>
-      <c r="C330" s="104" t="s">
+      <c r="C330" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D330" s="104" t="s">
+      <c r="D330" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E330" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>19</v>
       </c>
       <c r="B331" t="s">
         <v>32</v>
       </c>
-      <c r="C331" s="104" t="s">
+      <c r="C331" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D331" s="104" t="s">
+      <c r="D331" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E331" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>19</v>
       </c>
       <c r="B332" t="s">
         <v>295</v>
       </c>
-      <c r="C332" s="103" t="s">
+      <c r="C332" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="D332" s="103" t="s">
+      <c r="D332" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E332" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>19</v>
       </c>
       <c r="B333" t="s">
         <v>35</v>
       </c>
-      <c r="C333" s="104" t="s">
+      <c r="C333" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D333" s="104" t="s">
+      <c r="D333" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E333" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>19</v>
       </c>
       <c r="B334" t="s">
         <v>37</v>
       </c>
-      <c r="C334" s="104" t="s">
+      <c r="C334" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D334" s="104" t="s">
+      <c r="D334" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E334" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>19</v>
       </c>
       <c r="B335" t="s">
         <v>30</v>
       </c>
-      <c r="C335" s="104" t="s">
+      <c r="C335" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D335" s="104" t="s">
+      <c r="D335" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E335" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>19</v>
       </c>
       <c r="B336" t="s">
         <v>56</v>
       </c>
-      <c r="C336" s="104" t="s">
+      <c r="C336" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D336" s="104" t="s">
+      <c r="D336" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E336" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>19</v>
       </c>
       <c r="B337" t="s">
         <v>57</v>
       </c>
-      <c r="C337" s="104" t="s">
+      <c r="C337" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D337" s="104" t="s">
+      <c r="D337" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E337" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>19</v>
       </c>
       <c r="B338" t="s">
         <v>297</v>
       </c>
-      <c r="C338" s="104" t="s">
+      <c r="C338" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D338" s="104" t="s">
+      <c r="D338" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E338" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>19</v>
       </c>
       <c r="B339" t="s">
         <v>23</v>
       </c>
-      <c r="C339" s="104" t="s">
+      <c r="C339" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D339" s="104" t="s">
+      <c r="D339" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E339" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>19</v>
       </c>
       <c r="B340" t="s">
         <v>47</v>
       </c>
-      <c r="C340" s="104" t="s">
+      <c r="C340" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D340" s="104" t="s">
+      <c r="D340" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E340" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>19</v>
       </c>
       <c r="B341" t="s">
         <v>43</v>
       </c>
-      <c r="C341" s="104" t="s">
+      <c r="C341" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D341" s="104" t="s">
+      <c r="D341" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E341" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>19</v>
       </c>
       <c r="B342" t="s">
         <v>53</v>
       </c>
-      <c r="C342" s="104" t="s">
+      <c r="C342" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D342" s="104" t="s">
+      <c r="D342" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E342" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>19</v>
       </c>
       <c r="B343" t="s">
         <v>26</v>
       </c>
-      <c r="C343" s="104" t="s">
+      <c r="C343" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D343" s="104" t="s">
+      <c r="D343" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E343" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>19</v>
       </c>
       <c r="B344" t="s">
         <v>19</v>
       </c>
-      <c r="C344" s="104" t="s">
+      <c r="C344" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D344" s="104" t="s">
+      <c r="D344" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E344" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>19</v>
       </c>
       <c r="B345" t="s">
         <v>20</v>
       </c>
-      <c r="C345" s="104" t="s">
+      <c r="C345" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D345" s="104" t="s">
+      <c r="D345" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E345" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>19</v>
       </c>
       <c r="B346" t="s">
         <v>59</v>
       </c>
-      <c r="C346" s="103" t="s">
+      <c r="C346" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="D346" s="103" t="s">
+      <c r="D346" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E346" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>19</v>
       </c>
       <c r="B347" t="s">
         <v>61</v>
       </c>
-      <c r="C347" s="104" t="s">
+      <c r="C347" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D347" s="104" t="s">
+      <c r="D347" s="101" t="s">
         <v>305</v>
       </c>
       <c r="E347" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>19</v>
       </c>
       <c r="B348" t="s">
         <v>66</v>
       </c>
-      <c r="C348" s="103" t="s">
+      <c r="C348" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="D348" s="103" t="s">
+      <c r="D348" s="100" t="s">
         <v>292</v>
       </c>
       <c r="E348" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>19</v>
       </c>
       <c r="B349" t="s">
         <v>68</v>
       </c>
-      <c r="C349" s="104" t="s">
+      <c r="C349" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D349" s="104" t="s">
+      <c r="D349" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E349" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>19</v>
       </c>
       <c r="B350" t="s">
         <v>70</v>
       </c>
-      <c r="C350" s="104" t="s">
+      <c r="C350" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D350" s="104" t="s">
+      <c r="D350" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E350" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>19</v>
       </c>
       <c r="B351" t="s">
         <v>75</v>
       </c>
-      <c r="C351" s="104" t="s">
+      <c r="C351" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="D351" s="104" t="s">
+      <c r="D351" s="101" t="s">
         <v>299</v>
       </c>
       <c r="E351" t="s">

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="22" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CC01C36-C36C-43ED-BB85-10F8BAB08CE9}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A5A702-3486-42BA-A041-A0B5C356BB42}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="360">
   <si>
     <t>Template Test Case</t>
   </si>
@@ -2025,18 +2025,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="24" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2055,6 +2043,18 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2070,10 +2070,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2394,89 +2390,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DB19"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
-    <col min="6" max="6" width="32.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="35.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="32.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8.1796875" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
-    <col min="14" max="14" width="21.453125" customWidth="1"/>
-    <col min="15" max="15" width="19.7265625" customWidth="1"/>
-    <col min="16" max="16" width="27.453125" customWidth="1"/>
-    <col min="17" max="17" width="25.1796875" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" customWidth="1"/>
+    <col min="16" max="16" width="27.44140625" customWidth="1"/>
+    <col min="17" max="17" width="25.21875" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="21.7265625" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="31.1796875" customWidth="1"/>
-    <col min="22" max="22" width="16.453125" customWidth="1"/>
-    <col min="23" max="23" width="25.453125" customWidth="1"/>
-    <col min="24" max="24" width="8.453125" customWidth="1"/>
-    <col min="25" max="25" width="15.453125" customWidth="1"/>
-    <col min="26" max="26" width="14.81640625" customWidth="1"/>
-    <col min="27" max="27" width="15.453125" customWidth="1"/>
-    <col min="28" max="28" width="16.81640625" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" customWidth="1"/>
-    <col min="30" max="30" width="24.54296875" customWidth="1"/>
+    <col min="19" max="19" width="21.77734375" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="31.21875" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="25.44140625" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="14.77734375" customWidth="1"/>
+    <col min="27" max="27" width="15.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.77734375" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" customWidth="1"/>
+    <col min="30" max="30" width="24.5546875" customWidth="1"/>
     <col min="31" max="31" width="24" customWidth="1"/>
-    <col min="32" max="32" width="27.7265625" customWidth="1"/>
-    <col min="33" max="33" width="17.453125" customWidth="1"/>
-    <col min="34" max="34" width="18.26953125" customWidth="1"/>
+    <col min="32" max="32" width="27.77734375" customWidth="1"/>
+    <col min="33" max="33" width="17.44140625" customWidth="1"/>
+    <col min="34" max="34" width="18.21875" customWidth="1"/>
     <col min="35" max="35" width="24" customWidth="1"/>
-    <col min="36" max="36" width="16.26953125" customWidth="1"/>
+    <col min="36" max="36" width="16.21875" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="27.453125" customWidth="1"/>
-    <col min="39" max="39" width="21.453125" customWidth="1"/>
-    <col min="40" max="40" width="15.26953125" customWidth="1"/>
+    <col min="38" max="38" width="27.44140625" customWidth="1"/>
+    <col min="39" max="39" width="21.44140625" customWidth="1"/>
+    <col min="40" max="40" width="15.21875" customWidth="1"/>
     <col min="41" max="41" width="29" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="8.1796875" customWidth="1"/>
+    <col min="43" max="43" width="8.21875" customWidth="1"/>
     <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="45" max="45" width="14.453125" customWidth="1"/>
-    <col min="46" max="46" width="23.453125" customWidth="1"/>
-    <col min="47" max="47" width="23.1796875" customWidth="1"/>
-    <col min="48" max="48" width="17.453125" customWidth="1"/>
-    <col min="49" max="49" width="14.1796875" customWidth="1"/>
-    <col min="50" max="50" width="18.7265625" customWidth="1"/>
-    <col min="51" max="51" width="23.453125" customWidth="1"/>
-    <col min="52" max="52" width="24.7265625" customWidth="1"/>
-    <col min="53" max="55" width="12.54296875" customWidth="1"/>
-    <col min="56" max="56" width="25.453125" customWidth="1"/>
-    <col min="57" max="57" width="22.453125" customWidth="1"/>
-    <col min="58" max="58" width="13.453125" customWidth="1"/>
-    <col min="59" max="59" width="15.1796875" customWidth="1"/>
-    <col min="60" max="60" width="13.453125" customWidth="1"/>
-    <col min="61" max="61" width="14.453125" customWidth="1"/>
-    <col min="62" max="62" width="15.453125" customWidth="1"/>
-    <col min="63" max="63" width="17.81640625" customWidth="1"/>
-    <col min="64" max="64" width="12.54296875" customWidth="1"/>
-    <col min="65" max="65" width="27.453125" customWidth="1"/>
-    <col min="66" max="66" width="24.453125" customWidth="1"/>
-    <col min="67" max="73" width="12.54296875" customWidth="1"/>
-    <col min="74" max="74" width="27.453125" customWidth="1"/>
-    <col min="75" max="75" width="24.453125" customWidth="1"/>
-    <col min="76" max="87" width="12.54296875" customWidth="1"/>
-    <col min="88" max="88" width="15.7265625" customWidth="1"/>
-    <col min="89" max="95" width="12.54296875" customWidth="1"/>
-    <col min="96" max="96" width="15.7265625" customWidth="1"/>
-    <col min="97" max="97" width="17.7265625" customWidth="1"/>
-    <col min="98" max="98" width="19.54296875" customWidth="1"/>
+    <col min="45" max="45" width="14.44140625" customWidth="1"/>
+    <col min="46" max="46" width="23.44140625" customWidth="1"/>
+    <col min="47" max="47" width="23.21875" customWidth="1"/>
+    <col min="48" max="48" width="17.44140625" customWidth="1"/>
+    <col min="49" max="49" width="14.21875" customWidth="1"/>
+    <col min="50" max="50" width="18.77734375" customWidth="1"/>
+    <col min="51" max="51" width="23.44140625" customWidth="1"/>
+    <col min="52" max="52" width="24.77734375" customWidth="1"/>
+    <col min="53" max="55" width="12.5546875" customWidth="1"/>
+    <col min="56" max="56" width="25.44140625" customWidth="1"/>
+    <col min="57" max="57" width="22.44140625" customWidth="1"/>
+    <col min="58" max="58" width="13.44140625" customWidth="1"/>
+    <col min="59" max="59" width="15.21875" customWidth="1"/>
+    <col min="60" max="60" width="13.44140625" customWidth="1"/>
+    <col min="61" max="61" width="14.44140625" customWidth="1"/>
+    <col min="62" max="62" width="15.44140625" customWidth="1"/>
+    <col min="63" max="63" width="17.77734375" customWidth="1"/>
+    <col min="64" max="64" width="12.5546875" customWidth="1"/>
+    <col min="65" max="65" width="27.44140625" customWidth="1"/>
+    <col min="66" max="66" width="24.44140625" customWidth="1"/>
+    <col min="67" max="73" width="12.5546875" customWidth="1"/>
+    <col min="74" max="74" width="27.44140625" customWidth="1"/>
+    <col min="75" max="75" width="24.44140625" customWidth="1"/>
+    <col min="76" max="87" width="12.5546875" customWidth="1"/>
+    <col min="88" max="88" width="15.77734375" customWidth="1"/>
+    <col min="89" max="95" width="12.5546875" customWidth="1"/>
+    <col min="96" max="96" width="15.77734375" customWidth="1"/>
+    <col min="97" max="97" width="17.77734375" customWidth="1"/>
+    <col min="98" max="98" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:106" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2775,29 +2771,29 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="N4" s="111" t="s">
+    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="113"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
+      <c r="AE4" s="118"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="119"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2870,16 +2866,16 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="114" t="s">
+      <c r="CW4" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="114"/>
-      <c r="CY4" s="114"/>
-      <c r="CZ4" s="114"/>
-      <c r="DA4" s="114"/>
-      <c r="DB4" s="114"/>
-    </row>
-    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CX4" s="120"/>
+      <c r="CY4" s="120"/>
+      <c r="CZ4" s="120"/>
+      <c r="DA4" s="120"/>
+      <c r="DB4" s="120"/>
+    </row>
+    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>7</v>
@@ -3194,11 +3190,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="115" t="s">
-        <v>111</v>
-      </c>
+      <c r="B6" s="111"/>
       <c r="C6" s="37" t="s">
         <v>112</v>
       </c>
@@ -3208,9 +3202,7 @@
       <c r="E6" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="118" t="s">
-        <v>115</v>
-      </c>
+      <c r="F6" s="114"/>
       <c r="G6" s="38" t="s">
         <v>116</v>
       </c>
@@ -3408,11 +3400,9 @@
       <c r="DA6" s="46"/>
       <c r="DB6" s="46"/>
     </row>
-    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="115" t="s">
-        <v>150</v>
-      </c>
+      <c r="B7" s="111"/>
       <c r="C7" s="37" t="s">
         <v>151</v>
       </c>
@@ -3422,9 +3412,7 @@
       <c r="E7" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="118" t="s">
-        <v>153</v>
-      </c>
+      <c r="F7" s="114"/>
       <c r="G7" s="38" t="s">
         <v>154</v>
       </c>
@@ -3616,11 +3604,9 @@
       <c r="DA7" s="42"/>
       <c r="DB7" s="42"/>
     </row>
-    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="115" t="s">
-        <v>177</v>
-      </c>
+      <c r="B8" s="111"/>
       <c r="C8" s="52" t="s">
         <v>178</v>
       </c>
@@ -3630,9 +3616,7 @@
       <c r="E8" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="F8" s="118" t="s">
-        <v>180</v>
-      </c>
+      <c r="F8" s="114"/>
       <c r="G8" s="38" t="s">
         <v>181</v>
       </c>
@@ -3821,11 +3805,9 @@
       <c r="DA8" s="42"/>
       <c r="DB8" s="42"/>
     </row>
-    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="115" t="s">
-        <v>198</v>
-      </c>
+      <c r="B9" s="111"/>
       <c r="C9" s="37" t="s">
         <v>199</v>
       </c>
@@ -3835,9 +3817,7 @@
       <c r="E9" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="119" t="s">
-        <v>201</v>
-      </c>
+      <c r="F9" s="115"/>
       <c r="G9" s="38" t="s">
         <v>202</v>
       </c>
@@ -4037,11 +4017,9 @@
       <c r="DA9" s="42"/>
       <c r="DB9" s="42"/>
     </row>
-    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="115" t="s">
-        <v>217</v>
-      </c>
+      <c r="B10" s="111"/>
       <c r="C10" s="54" t="s">
         <v>218</v>
       </c>
@@ -4051,9 +4029,7 @@
       <c r="E10" s="55">
         <v>0.74733796296277433</v>
       </c>
-      <c r="F10" s="120" t="s">
-        <v>219</v>
-      </c>
+      <c r="F10" s="116"/>
       <c r="G10" s="57"/>
       <c r="H10" s="57"/>
       <c r="I10" s="58" t="s">
@@ -4174,11 +4150,9 @@
       <c r="DA10" s="42"/>
       <c r="DB10" s="42"/>
     </row>
-    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
-      <c r="B11" s="116" t="s">
-        <v>222</v>
-      </c>
+      <c r="B11" s="112"/>
       <c r="C11" s="67" t="s">
         <v>223</v>
       </c>
@@ -4188,9 +4162,7 @@
       <c r="E11" s="68">
         <v>0.46600694444350665</v>
       </c>
-      <c r="F11" s="81" t="s">
-        <v>225</v>
-      </c>
+      <c r="F11" s="81"/>
       <c r="G11" s="67" t="s">
         <v>226</v>
       </c>
@@ -4386,11 +4358,9 @@
       <c r="CT11" s="50"/>
       <c r="CU11" s="51"/>
     </row>
-    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="70"/>
-      <c r="B12" s="75" t="s">
-        <v>234</v>
-      </c>
+      <c r="B12" s="75"/>
       <c r="C12" s="71" t="s">
         <v>235</v>
       </c>
@@ -4400,9 +4370,7 @@
       <c r="E12" s="68">
         <v>0.55619212962847087</v>
       </c>
-      <c r="F12" s="81" t="s">
-        <v>237</v>
-      </c>
+      <c r="F12" s="81"/>
       <c r="G12" s="67" t="s">
         <v>238</v>
       </c>
@@ -4600,11 +4568,9 @@
       <c r="CT12" s="50"/>
       <c r="CU12" s="51"/>
     </row>
-    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="70"/>
-      <c r="B13" s="75" t="s">
-        <v>243</v>
-      </c>
+      <c r="B13" s="75"/>
       <c r="C13" s="73" t="s">
         <v>244</v>
       </c>
@@ -4614,9 +4580,7 @@
       <c r="E13" s="74">
         <v>0.46855324074203963</v>
       </c>
-      <c r="F13" s="76" t="s">
-        <v>245</v>
-      </c>
+      <c r="F13" s="76"/>
       <c r="G13" s="73" t="s">
         <v>246</v>
       </c>
@@ -4814,11 +4778,9 @@
       <c r="CT13" s="50"/>
       <c r="CU13" s="51"/>
     </row>
-    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="70"/>
-      <c r="B14" s="75" t="s">
-        <v>250</v>
-      </c>
+      <c r="B14" s="75"/>
       <c r="C14" s="71" t="s">
         <v>251</v>
       </c>
@@ -4828,9 +4790,7 @@
       <c r="E14" s="68">
         <v>0.56629629629605915</v>
       </c>
-      <c r="F14" s="81" t="s">
-        <v>252</v>
-      </c>
+      <c r="F14" s="81"/>
       <c r="G14" s="67" t="s">
         <v>253</v>
       </c>
@@ -5026,11 +4986,9 @@
       <c r="CT14" s="50"/>
       <c r="CU14" s="51"/>
     </row>
-    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="70"/>
-      <c r="B15" s="75" t="s">
-        <v>256</v>
-      </c>
+      <c r="B15" s="75"/>
       <c r="C15" s="71" t="s">
         <v>257</v>
       </c>
@@ -5040,9 +4998,7 @@
       <c r="E15" s="74">
         <v>0.7070138888884685</v>
       </c>
-      <c r="F15" s="76" t="s">
-        <v>258</v>
-      </c>
+      <c r="F15" s="76"/>
       <c r="G15" s="73" t="s">
         <v>259</v>
       </c>
@@ -5244,11 +5200,9 @@
       <c r="CT15" s="50"/>
       <c r="CU15" s="51"/>
     </row>
-    <row r="16" spans="1:106" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:106" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="75"/>
-      <c r="B16" s="75" t="s">
-        <v>265</v>
-      </c>
+      <c r="B16" s="75"/>
       <c r="C16" s="76" t="s">
         <v>266</v>
       </c>
@@ -5258,9 +5212,7 @@
       <c r="E16" s="77">
         <v>0.47150462962963502</v>
       </c>
-      <c r="F16" s="76" t="s">
-        <v>267</v>
-      </c>
+      <c r="F16" s="76"/>
       <c r="G16" s="76" t="s">
         <v>268</v>
       </c>
@@ -5439,11 +5391,9 @@
       <c r="CT16" s="79"/>
       <c r="CU16" s="79"/>
     </row>
-    <row r="17" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="80"/>
-      <c r="B17" s="80" t="s">
-        <v>273</v>
-      </c>
+      <c r="B17" s="80"/>
       <c r="C17" s="84" t="s">
         <v>274</v>
       </c>
@@ -5453,9 +5403,7 @@
       <c r="E17" s="86">
         <v>0.69283564814759302</v>
       </c>
-      <c r="F17" s="84" t="s">
-        <v>275</v>
-      </c>
+      <c r="F17" s="84"/>
       <c r="G17" s="84" t="s">
         <v>276</v>
       </c>
@@ -5632,11 +5580,9 @@
       <c r="CT17" s="79"/>
       <c r="CU17" s="79"/>
     </row>
-    <row r="18" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="87"/>
-      <c r="B18" s="117" t="s">
-        <v>281</v>
-      </c>
+      <c r="B18" s="113"/>
       <c r="C18" s="88" t="s">
         <v>282</v>
       </c>
@@ -5646,9 +5592,7 @@
       <c r="E18" s="89">
         <v>0.55278935185197042</v>
       </c>
-      <c r="F18" s="88" t="s">
-        <v>283</v>
-      </c>
+      <c r="F18" s="88"/>
       <c r="G18" s="88" t="s">
         <v>284</v>
       </c>
@@ -5825,11 +5769,9 @@
       <c r="CT18" s="90"/>
       <c r="CU18" s="90"/>
     </row>
-    <row r="19" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="87"/>
-      <c r="B19" s="87" t="s">
-        <v>287</v>
-      </c>
+      <c r="B19" s="87"/>
       <c r="C19" s="94" t="s">
         <v>218</v>
       </c>
@@ -5839,9 +5781,7 @@
       <c r="E19" s="89">
         <v>0.58141203703780775</v>
       </c>
-      <c r="F19" s="88" t="s">
-        <v>288</v>
-      </c>
+      <c r="F19" s="88"/>
       <c r="G19" s="88"/>
       <c r="H19" s="88"/>
       <c r="I19" s="88"/>
@@ -5965,7 +5905,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5974,7 +5914,7 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>289</v>
       </c>
@@ -5991,7 +5931,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>6</v>
       </c>
@@ -6008,7 +5948,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>6</v>
       </c>
@@ -6025,7 +5965,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
@@ -6042,7 +5982,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>6</v>
       </c>
@@ -6059,7 +5999,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -6076,7 +6016,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6093,7 +6033,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6110,7 +6050,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -6127,7 +6067,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6144,7 +6084,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -6161,7 +6101,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -6178,7 +6118,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
@@ -6195,7 +6135,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -6212,7 +6152,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -6229,7 +6169,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
@@ -6246,7 +6186,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -6263,7 +6203,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -6280,7 +6220,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -6297,7 +6237,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>6</v>
       </c>
@@ -6314,7 +6254,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6</v>
       </c>
@@ -6331,7 +6271,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6</v>
       </c>
@@ -6348,7 +6288,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>6</v>
       </c>
@@ -6365,7 +6305,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6382,7 +6322,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>6</v>
       </c>
@@ -6399,7 +6339,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -6416,7 +6356,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -6433,7 +6373,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -6450,7 +6390,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>7</v>
       </c>
@@ -6467,7 +6407,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>7</v>
       </c>
@@ -6484,7 +6424,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>7</v>
       </c>
@@ -6501,7 +6441,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -6518,7 +6458,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>7</v>
       </c>
@@ -6535,7 +6475,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>7</v>
       </c>
@@ -6552,7 +6492,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>7</v>
       </c>
@@ -6569,7 +6509,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>7</v>
       </c>
@@ -6586,7 +6526,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>7</v>
       </c>
@@ -6603,7 +6543,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>7</v>
       </c>
@@ -6620,7 +6560,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6637,7 +6577,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>7</v>
       </c>
@@ -6654,7 +6594,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>7</v>
       </c>
@@ -6671,7 +6611,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>7</v>
       </c>
@@ -6688,7 +6628,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>7</v>
       </c>
@@ -6705,7 +6645,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>7</v>
       </c>
@@ -6722,7 +6662,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>7</v>
       </c>
@@ -6739,7 +6679,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>7</v>
       </c>
@@ -6756,7 +6696,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>7</v>
       </c>
@@ -6773,7 +6713,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>7</v>
       </c>
@@ -6790,7 +6730,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>7</v>
       </c>
@@ -6807,7 +6747,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>7</v>
       </c>
@@ -6824,7 +6764,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>7</v>
       </c>
@@ -6841,7 +6781,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>8</v>
       </c>
@@ -6858,7 +6798,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>8</v>
       </c>
@@ -6875,7 +6815,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>8</v>
       </c>
@@ -6892,7 +6832,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>8</v>
       </c>
@@ -6909,7 +6849,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>8</v>
       </c>
@@ -6926,7 +6866,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>8</v>
       </c>
@@ -6943,7 +6883,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>8</v>
       </c>
@@ -6960,7 +6900,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>8</v>
       </c>
@@ -6977,7 +6917,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>8</v>
       </c>
@@ -6994,7 +6934,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>8</v>
       </c>
@@ -7011,7 +6951,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>8</v>
       </c>
@@ -7028,7 +6968,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>8</v>
       </c>
@@ -7045,7 +6985,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>8</v>
       </c>
@@ -7062,7 +7002,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>8</v>
       </c>
@@ -7079,7 +7019,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>8</v>
       </c>
@@ -7096,7 +7036,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>8</v>
       </c>
@@ -7113,7 +7053,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>8</v>
       </c>
@@ -7130,7 +7070,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -7147,7 +7087,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>8</v>
       </c>
@@ -7164,7 +7104,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>8</v>
       </c>
@@ -7181,7 +7121,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -7198,7 +7138,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7215,7 +7155,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -7232,7 +7172,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8</v>
       </c>
@@ -7249,7 +7189,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8</v>
       </c>
@@ -7266,7 +7206,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9</v>
       </c>
@@ -7283,7 +7223,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9</v>
       </c>
@@ -7300,7 +7240,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>9</v>
       </c>
@@ -7317,7 +7257,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>9</v>
       </c>
@@ -7334,7 +7274,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>9</v>
       </c>
@@ -7351,7 +7291,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -7368,7 +7308,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>9</v>
       </c>
@@ -7385,7 +7325,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>9</v>
       </c>
@@ -7402,7 +7342,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>9</v>
       </c>
@@ -7419,7 +7359,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>9</v>
       </c>
@@ -7436,7 +7376,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>9</v>
       </c>
@@ -7453,7 +7393,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7470,7 +7410,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7487,7 +7427,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7504,7 +7444,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7521,7 +7461,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7538,7 +7478,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7555,7 +7495,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7572,7 +7512,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7589,7 +7529,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7606,7 +7546,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7623,7 +7563,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7640,7 +7580,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7657,7 +7597,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7674,7 +7614,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7691,7 +7631,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10</v>
       </c>
@@ -7708,7 +7648,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10</v>
       </c>
@@ -7725,7 +7665,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10</v>
       </c>
@@ -7742,7 +7682,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10</v>
       </c>
@@ -7759,7 +7699,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>10</v>
       </c>
@@ -7776,7 +7716,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -7793,7 +7733,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>10</v>
       </c>
@@ -7810,7 +7750,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>10</v>
       </c>
@@ -7827,7 +7767,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>10</v>
       </c>
@@ -7844,7 +7784,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>10</v>
       </c>
@@ -7861,7 +7801,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>10</v>
       </c>
@@ -7878,7 +7818,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>10</v>
       </c>
@@ -7895,7 +7835,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>10</v>
       </c>
@@ -7912,7 +7852,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>10</v>
       </c>
@@ -7929,7 +7869,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>10</v>
       </c>
@@ -7946,7 +7886,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>10</v>
       </c>
@@ -7963,7 +7903,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>10</v>
       </c>
@@ -7980,7 +7920,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10</v>
       </c>
@@ -7997,7 +7937,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>10</v>
       </c>
@@ -8014,7 +7954,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>10</v>
       </c>
@@ -8031,7 +7971,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10</v>
       </c>
@@ -8048,7 +7988,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>10</v>
       </c>
@@ -8065,7 +8005,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>10</v>
       </c>
@@ -8082,7 +8022,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>10</v>
       </c>
@@ -8099,7 +8039,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>10</v>
       </c>
@@ -8116,7 +8056,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>11</v>
       </c>
@@ -8133,7 +8073,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>11</v>
       </c>
@@ -8150,7 +8090,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>11</v>
       </c>
@@ -8167,7 +8107,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>11</v>
       </c>
@@ -8184,7 +8124,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>11</v>
       </c>
@@ -8201,7 +8141,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>11</v>
       </c>
@@ -8218,7 +8158,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>11</v>
       </c>
@@ -8235,7 +8175,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>11</v>
       </c>
@@ -8252,7 +8192,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>11</v>
       </c>
@@ -8269,7 +8209,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>11</v>
       </c>
@@ -8286,7 +8226,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>11</v>
       </c>
@@ -8303,7 +8243,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>11</v>
       </c>
@@ -8320,7 +8260,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>11</v>
       </c>
@@ -8337,7 +8277,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>11</v>
       </c>
@@ -8354,7 +8294,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>11</v>
       </c>
@@ -8371,7 +8311,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>11</v>
       </c>
@@ -8388,7 +8328,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>11</v>
       </c>
@@ -8405,7 +8345,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>11</v>
       </c>
@@ -8422,7 +8362,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>11</v>
       </c>
@@ -8439,7 +8379,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>11</v>
       </c>
@@ -8456,7 +8396,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>11</v>
       </c>
@@ -8473,7 +8413,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>11</v>
       </c>
@@ -8490,7 +8430,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>11</v>
       </c>
@@ -8507,7 +8447,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>11</v>
       </c>
@@ -8524,7 +8464,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>11</v>
       </c>
@@ -8541,7 +8481,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>12</v>
       </c>
@@ -8558,7 +8498,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>12</v>
       </c>
@@ -8575,7 +8515,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>12</v>
       </c>
@@ -8592,7 +8532,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>12</v>
       </c>
@@ -8609,7 +8549,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>12</v>
       </c>
@@ -8626,7 +8566,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>12</v>
       </c>
@@ -8643,7 +8583,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>12</v>
       </c>
@@ -8660,7 +8600,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>12</v>
       </c>
@@ -8677,7 +8617,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>12</v>
       </c>
@@ -8694,7 +8634,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>12</v>
       </c>
@@ -8711,7 +8651,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>12</v>
       </c>
@@ -8728,7 +8668,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>12</v>
       </c>
@@ -8745,7 +8685,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>12</v>
       </c>
@@ -8762,7 +8702,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>12</v>
       </c>
@@ -8779,7 +8719,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>12</v>
       </c>
@@ -8796,7 +8736,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>12</v>
       </c>
@@ -8813,7 +8753,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>12</v>
       </c>
@@ -8830,7 +8770,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>12</v>
       </c>
@@ -8847,7 +8787,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>12</v>
       </c>
@@ -8864,7 +8804,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>12</v>
       </c>
@@ -8881,7 +8821,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>12</v>
       </c>
@@ -8898,7 +8838,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>12</v>
       </c>
@@ -8915,7 +8855,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>12</v>
       </c>
@@ -8932,7 +8872,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>12</v>
       </c>
@@ -8949,7 +8889,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>12</v>
       </c>
@@ -8966,7 +8906,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>13</v>
       </c>
@@ -8983,7 +8923,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>13</v>
       </c>
@@ -9000,7 +8940,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>13</v>
       </c>
@@ -9017,7 +8957,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>13</v>
       </c>
@@ -9034,7 +8974,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>13</v>
       </c>
@@ -9051,7 +8991,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>13</v>
       </c>
@@ -9068,7 +9008,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>13</v>
       </c>
@@ -9085,7 +9025,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>13</v>
       </c>
@@ -9102,7 +9042,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>13</v>
       </c>
@@ -9119,7 +9059,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>13</v>
       </c>
@@ -9136,7 +9076,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>13</v>
       </c>
@@ -9153,7 +9093,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>13</v>
       </c>
@@ -9170,7 +9110,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>13</v>
       </c>
@@ -9187,7 +9127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>13</v>
       </c>
@@ -9204,7 +9144,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>13</v>
       </c>
@@ -9221,7 +9161,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>13</v>
       </c>
@@ -9238,7 +9178,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>13</v>
       </c>
@@ -9255,7 +9195,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>13</v>
       </c>
@@ -9272,7 +9212,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>13</v>
       </c>
@@ -9289,7 +9229,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>13</v>
       </c>
@@ -9306,7 +9246,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>13</v>
       </c>
@@ -9323,7 +9263,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>13</v>
       </c>
@@ -9340,7 +9280,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>13</v>
       </c>
@@ -9357,7 +9297,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>13</v>
       </c>
@@ -9374,7 +9314,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>13</v>
       </c>
@@ -9391,7 +9331,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>14</v>
       </c>
@@ -9408,7 +9348,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>14</v>
       </c>
@@ -9425,7 +9365,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>14</v>
       </c>
@@ -9442,7 +9382,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>14</v>
       </c>
@@ -9459,7 +9399,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>14</v>
       </c>
@@ -9476,7 +9416,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14</v>
       </c>
@@ -9493,7 +9433,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>14</v>
       </c>
@@ -9510,7 +9450,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>14</v>
       </c>
@@ -9527,7 +9467,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>14</v>
       </c>
@@ -9544,7 +9484,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>14</v>
       </c>
@@ -9561,7 +9501,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>14</v>
       </c>
@@ -9578,7 +9518,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>14</v>
       </c>
@@ -9595,7 +9535,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>14</v>
       </c>
@@ -9612,7 +9552,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>14</v>
       </c>
@@ -9629,7 +9569,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>14</v>
       </c>
@@ -9646,7 +9586,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>14</v>
       </c>
@@ -9663,7 +9603,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>14</v>
       </c>
@@ -9680,7 +9620,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>14</v>
       </c>
@@ -9697,7 +9637,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>14</v>
       </c>
@@ -9714,7 +9654,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>14</v>
       </c>
@@ -9731,7 +9671,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>14</v>
       </c>
@@ -9748,7 +9688,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>14</v>
       </c>
@@ -9765,7 +9705,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>14</v>
       </c>
@@ -9782,7 +9722,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>14</v>
       </c>
@@ -9799,7 +9739,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>14</v>
       </c>
@@ -9816,7 +9756,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>15</v>
       </c>
@@ -9833,7 +9773,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>15</v>
       </c>
@@ -9850,7 +9790,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>15</v>
       </c>
@@ -9867,7 +9807,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>15</v>
       </c>
@@ -9884,7 +9824,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>15</v>
       </c>
@@ -9901,7 +9841,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>15</v>
       </c>
@@ -9918,7 +9858,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>15</v>
       </c>
@@ -9935,7 +9875,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>15</v>
       </c>
@@ -9952,7 +9892,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>15</v>
       </c>
@@ -9969,7 +9909,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>15</v>
       </c>
@@ -9986,7 +9926,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>15</v>
       </c>
@@ -10003,7 +9943,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>15</v>
       </c>
@@ -10020,7 +9960,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>15</v>
       </c>
@@ -10037,7 +9977,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>15</v>
       </c>
@@ -10054,7 +9994,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>15</v>
       </c>
@@ -10071,7 +10011,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>15</v>
       </c>
@@ -10088,7 +10028,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>15</v>
       </c>
@@ -10105,7 +10045,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>15</v>
       </c>
@@ -10122,7 +10062,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>15</v>
       </c>
@@ -10139,7 +10079,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>15</v>
       </c>
@@ -10156,7 +10096,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>15</v>
       </c>
@@ -10173,7 +10113,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>15</v>
       </c>
@@ -10190,7 +10130,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>15</v>
       </c>
@@ -10207,7 +10147,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>15</v>
       </c>
@@ -10224,7 +10164,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>15</v>
       </c>
@@ -10241,7 +10181,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>16</v>
       </c>
@@ -10258,7 +10198,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>16</v>
       </c>
@@ -10275,7 +10215,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>16</v>
       </c>
@@ -10292,7 +10232,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>16</v>
       </c>
@@ -10309,7 +10249,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>16</v>
       </c>
@@ -10326,7 +10266,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>16</v>
       </c>
@@ -10343,7 +10283,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>16</v>
       </c>
@@ -10360,7 +10300,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>16</v>
       </c>
@@ -10377,7 +10317,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>16</v>
       </c>
@@ -10394,7 +10334,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>16</v>
       </c>
@@ -10411,7 +10351,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>16</v>
       </c>
@@ -10428,7 +10368,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>16</v>
       </c>
@@ -10445,7 +10385,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>16</v>
       </c>
@@ -10462,7 +10402,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>16</v>
       </c>
@@ -10479,7 +10419,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>16</v>
       </c>
@@ -10496,7 +10436,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>16</v>
       </c>
@@ -10513,7 +10453,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>16</v>
       </c>
@@ -10530,7 +10470,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>16</v>
       </c>
@@ -10547,7 +10487,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>16</v>
       </c>
@@ -10564,7 +10504,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>16</v>
       </c>
@@ -10581,7 +10521,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>16</v>
       </c>
@@ -10598,7 +10538,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>16</v>
       </c>
@@ -10615,7 +10555,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>16</v>
       </c>
@@ -10632,7 +10572,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>16</v>
       </c>
@@ -10649,7 +10589,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>16</v>
       </c>
@@ -10666,7 +10606,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10683,7 +10623,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>17</v>
       </c>
@@ -10700,7 +10640,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>17</v>
       </c>
@@ -10717,7 +10657,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>17</v>
       </c>
@@ -10734,7 +10674,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>17</v>
       </c>
@@ -10751,7 +10691,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>17</v>
       </c>
@@ -10768,7 +10708,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>17</v>
       </c>
@@ -10785,7 +10725,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>17</v>
       </c>
@@ -10802,7 +10742,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>17</v>
       </c>
@@ -10819,7 +10759,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>17</v>
       </c>
@@ -10836,7 +10776,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10853,7 +10793,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>17</v>
       </c>
@@ -10870,7 +10810,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>17</v>
       </c>
@@ -10887,7 +10827,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>17</v>
       </c>
@@ -10904,7 +10844,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>17</v>
       </c>
@@ -10921,7 +10861,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>17</v>
       </c>
@@ -10938,7 +10878,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>17</v>
       </c>
@@ -10955,7 +10895,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>17</v>
       </c>
@@ -10972,7 +10912,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>17</v>
       </c>
@@ -10989,7 +10929,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>17</v>
       </c>
@@ -11006,7 +10946,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>17</v>
       </c>
@@ -11023,7 +10963,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>17</v>
       </c>
@@ -11040,7 +10980,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>17</v>
       </c>
@@ -11057,7 +10997,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>17</v>
       </c>
@@ -11074,7 +11014,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>17</v>
       </c>
@@ -11091,7 +11031,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>18</v>
       </c>
@@ -11108,7 +11048,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>18</v>
       </c>
@@ -11125,7 +11065,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>18</v>
       </c>
@@ -11142,7 +11082,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>18</v>
       </c>
@@ -11159,7 +11099,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>18</v>
       </c>
@@ -11176,7 +11116,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>18</v>
       </c>
@@ -11193,7 +11133,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>18</v>
       </c>
@@ -11210,7 +11150,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>18</v>
       </c>
@@ -11227,7 +11167,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>18</v>
       </c>
@@ -11244,7 +11184,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>18</v>
       </c>
@@ -11261,7 +11201,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>18</v>
       </c>
@@ -11278,7 +11218,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>18</v>
       </c>
@@ -11295,7 +11235,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>18</v>
       </c>
@@ -11312,7 +11252,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>18</v>
       </c>
@@ -11329,7 +11269,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>18</v>
       </c>
@@ -11346,7 +11286,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>18</v>
       </c>
@@ -11363,7 +11303,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>18</v>
       </c>
@@ -11380,7 +11320,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>18</v>
       </c>
@@ -11397,7 +11337,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>18</v>
       </c>
@@ -11414,7 +11354,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>18</v>
       </c>
@@ -11431,7 +11371,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>18</v>
       </c>
@@ -11448,7 +11388,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>18</v>
       </c>
@@ -11465,7 +11405,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>18</v>
       </c>
@@ -11482,7 +11422,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>18</v>
       </c>
@@ -11499,7 +11439,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>18</v>
       </c>
@@ -11516,7 +11456,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>19</v>
       </c>
@@ -11533,7 +11473,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>19</v>
       </c>
@@ -11550,7 +11490,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>19</v>
       </c>
@@ -11567,7 +11507,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>19</v>
       </c>
@@ -11584,7 +11524,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>19</v>
       </c>
@@ -11601,7 +11541,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>19</v>
       </c>
@@ -11618,7 +11558,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>19</v>
       </c>
@@ -11635,7 +11575,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>19</v>
       </c>
@@ -11652,7 +11592,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>19</v>
       </c>
@@ -11669,7 +11609,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>19</v>
       </c>
@@ -11686,7 +11626,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>19</v>
       </c>
@@ -11703,7 +11643,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>19</v>
       </c>
@@ -11720,7 +11660,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>19</v>
       </c>
@@ -11737,7 +11677,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>19</v>
       </c>
@@ -11754,7 +11694,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>19</v>
       </c>
@@ -11771,7 +11711,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>19</v>
       </c>
@@ -11788,7 +11728,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>19</v>
       </c>
@@ -11805,7 +11745,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>19</v>
       </c>
@@ -11822,7 +11762,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>19</v>
       </c>
@@ -11839,7 +11779,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>19</v>
       </c>
@@ -11856,7 +11796,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>19</v>
       </c>
@@ -11873,7 +11813,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>19</v>
       </c>
@@ -11890,7 +11830,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>19</v>
       </c>
@@ -11907,7 +11847,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>19</v>
       </c>
@@ -11924,7 +11864,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>19</v>
       </c>

--- a/test_data/Test_Data_Downstream-for pilot.xlsx
+++ b/test_data/Test_Data_Downstream-for pilot.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="22" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CC01C36-C36C-43ED-BB85-10F8BAB08CE9}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="114_{6BDDC0B5-1AE2-43CE-BA9D-EB249FA15F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B037879E-C049-51A3-9105-981E9C4155BB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="31170" yWindow="2595" windowWidth="13830" windowHeight="1170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Data" sheetId="1" r:id="rId1"/>
@@ -2025,18 +2025,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="24" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2054,6 +2042,18 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2394,89 +2394,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DB19"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
-    <col min="6" max="6" width="32.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="35.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="32.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8.1796875" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" customWidth="1"/>
-    <col min="14" max="14" width="21.453125" customWidth="1"/>
-    <col min="15" max="15" width="19.7265625" customWidth="1"/>
-    <col min="16" max="16" width="27.453125" customWidth="1"/>
-    <col min="17" max="17" width="25.1796875" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" customWidth="1"/>
+    <col min="16" max="16" width="27.44140625" customWidth="1"/>
+    <col min="17" max="17" width="25.21875" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="21.7265625" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="31.1796875" customWidth="1"/>
-    <col min="22" max="22" width="16.453125" customWidth="1"/>
-    <col min="23" max="23" width="25.453125" customWidth="1"/>
-    <col min="24" max="24" width="8.453125" customWidth="1"/>
-    <col min="25" max="25" width="15.453125" customWidth="1"/>
-    <col min="26" max="26" width="14.81640625" customWidth="1"/>
-    <col min="27" max="27" width="15.453125" customWidth="1"/>
-    <col min="28" max="28" width="16.81640625" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" customWidth="1"/>
-    <col min="30" max="30" width="24.54296875" customWidth="1"/>
+    <col min="19" max="19" width="21.77734375" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="31.21875" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="25.44140625" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="14.77734375" customWidth="1"/>
+    <col min="27" max="27" width="15.44140625" customWidth="1"/>
+    <col min="28" max="28" width="16.77734375" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" customWidth="1"/>
+    <col min="30" max="30" width="24.5546875" customWidth="1"/>
     <col min="31" max="31" width="24" customWidth="1"/>
-    <col min="32" max="32" width="27.7265625" customWidth="1"/>
-    <col min="33" max="33" width="17.453125" customWidth="1"/>
-    <col min="34" max="34" width="18.26953125" customWidth="1"/>
+    <col min="32" max="32" width="27.77734375" customWidth="1"/>
+    <col min="33" max="33" width="17.44140625" customWidth="1"/>
+    <col min="34" max="34" width="18.21875" customWidth="1"/>
     <col min="35" max="35" width="24" customWidth="1"/>
-    <col min="36" max="36" width="16.26953125" customWidth="1"/>
+    <col min="36" max="36" width="16.21875" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="27.453125" customWidth="1"/>
-    <col min="39" max="39" width="21.453125" customWidth="1"/>
-    <col min="40" max="40" width="15.26953125" customWidth="1"/>
+    <col min="38" max="38" width="27.44140625" customWidth="1"/>
+    <col min="39" max="39" width="21.44140625" customWidth="1"/>
+    <col min="40" max="40" width="15.21875" customWidth="1"/>
     <col min="41" max="41" width="29" customWidth="1"/>
     <col min="42" max="42" width="22" customWidth="1"/>
-    <col min="43" max="43" width="8.1796875" customWidth="1"/>
+    <col min="43" max="43" width="8.21875" customWidth="1"/>
     <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="45" max="45" width="14.453125" customWidth="1"/>
-    <col min="46" max="46" width="23.453125" customWidth="1"/>
-    <col min="47" max="47" width="23.1796875" customWidth="1"/>
-    <col min="48" max="48" width="17.453125" customWidth="1"/>
-    <col min="49" max="49" width="14.1796875" customWidth="1"/>
-    <col min="50" max="50" width="18.7265625" customWidth="1"/>
-    <col min="51" max="51" width="23.453125" customWidth="1"/>
-    <col min="52" max="52" width="24.7265625" customWidth="1"/>
-    <col min="53" max="55" width="12.54296875" customWidth="1"/>
-    <col min="56" max="56" width="25.453125" customWidth="1"/>
-    <col min="57" max="57" width="22.453125" customWidth="1"/>
-    <col min="58" max="58" width="13.453125" customWidth="1"/>
-    <col min="59" max="59" width="15.1796875" customWidth="1"/>
-    <col min="60" max="60" width="13.453125" customWidth="1"/>
-    <col min="61" max="61" width="14.453125" customWidth="1"/>
-    <col min="62" max="62" width="15.453125" customWidth="1"/>
-    <col min="63" max="63" width="17.81640625" customWidth="1"/>
-    <col min="64" max="64" width="12.54296875" customWidth="1"/>
-    <col min="65" max="65" width="27.453125" customWidth="1"/>
-    <col min="66" max="66" width="24.453125" customWidth="1"/>
-    <col min="67" max="73" width="12.54296875" customWidth="1"/>
-    <col min="74" max="74" width="27.453125" customWidth="1"/>
-    <col min="75" max="75" width="24.453125" customWidth="1"/>
-    <col min="76" max="87" width="12.54296875" customWidth="1"/>
-    <col min="88" max="88" width="15.7265625" customWidth="1"/>
-    <col min="89" max="95" width="12.54296875" customWidth="1"/>
-    <col min="96" max="96" width="15.7265625" customWidth="1"/>
-    <col min="97" max="97" width="17.7265625" customWidth="1"/>
-    <col min="98" max="98" width="19.54296875" customWidth="1"/>
+    <col min="45" max="45" width="14.44140625" customWidth="1"/>
+    <col min="46" max="46" width="23.44140625" customWidth="1"/>
+    <col min="47" max="47" width="23.21875" customWidth="1"/>
+    <col min="48" max="48" width="17.44140625" customWidth="1"/>
+    <col min="49" max="49" width="14.21875" customWidth="1"/>
+    <col min="50" max="50" width="18.77734375" customWidth="1"/>
+    <col min="51" max="51" width="23.44140625" customWidth="1"/>
+    <col min="52" max="52" width="24.77734375" customWidth="1"/>
+    <col min="53" max="55" width="12.5546875" customWidth="1"/>
+    <col min="56" max="56" width="25.44140625" customWidth="1"/>
+    <col min="57" max="57" width="22.44140625" customWidth="1"/>
+    <col min="58" max="58" width="13.44140625" customWidth="1"/>
+    <col min="59" max="59" width="15.21875" customWidth="1"/>
+    <col min="60" max="60" width="13.44140625" customWidth="1"/>
+    <col min="61" max="61" width="14.44140625" customWidth="1"/>
+    <col min="62" max="62" width="15.44140625" customWidth="1"/>
+    <col min="63" max="63" width="17.77734375" customWidth="1"/>
+    <col min="64" max="64" width="12.5546875" customWidth="1"/>
+    <col min="65" max="65" width="27.44140625" customWidth="1"/>
+    <col min="66" max="66" width="24.44140625" customWidth="1"/>
+    <col min="67" max="73" width="12.5546875" customWidth="1"/>
+    <col min="74" max="74" width="27.44140625" customWidth="1"/>
+    <col min="75" max="75" width="24.44140625" customWidth="1"/>
+    <col min="76" max="87" width="12.5546875" customWidth="1"/>
+    <col min="88" max="88" width="15.77734375" customWidth="1"/>
+    <col min="89" max="95" width="12.5546875" customWidth="1"/>
+    <col min="96" max="96" width="15.77734375" customWidth="1"/>
+    <col min="97" max="97" width="17.77734375" customWidth="1"/>
+    <col min="98" max="98" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:106" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:106" s="3" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:106" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:106" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2775,29 +2775,29 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="N4" s="111" t="s">
+    <row r="4" spans="1:106" s="7" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="113"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
+      <c r="AE4" s="118"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="119"/>
       <c r="AH4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2870,16 +2870,16 @@
       </c>
       <c r="CT4" s="13"/>
       <c r="CU4" s="13"/>
-      <c r="CW4" s="114" t="s">
+      <c r="CW4" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="CX4" s="114"/>
-      <c r="CY4" s="114"/>
-      <c r="CZ4" s="114"/>
-      <c r="DA4" s="114"/>
-      <c r="DB4" s="114"/>
-    </row>
-    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CX4" s="120"/>
+      <c r="CY4" s="120"/>
+      <c r="CZ4" s="120"/>
+      <c r="DA4" s="120"/>
+      <c r="DB4" s="120"/>
+    </row>
+    <row r="5" spans="1:106" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>7</v>
@@ -3194,9 +3194,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="35"/>
-      <c r="B6" s="115" t="s">
+      <c r="B6" s="111" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="37" t="s">
@@ -3208,7 +3208,7 @@
       <c r="E6" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="118" t="s">
+      <c r="F6" s="114" t="s">
         <v>115</v>
       </c>
       <c r="G6" s="38" t="s">
@@ -3408,9 +3408,9 @@
       <c r="DA6" s="46"/>
       <c r="DB6" s="46"/>
     </row>
-    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35"/>
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="111" t="s">
         <v>150</v>
       </c>
       <c r="C7" s="37" t="s">
@@ -3422,7 +3422,7 @@
       <c r="E7" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="114" t="s">
         <v>153</v>
       </c>
       <c r="G7" s="38" t="s">
@@ -3616,9 +3616,9 @@
       <c r="DA7" s="42"/>
       <c r="DB7" s="42"/>
     </row>
-    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35"/>
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="111" t="s">
         <v>177</v>
       </c>
       <c r="C8" s="52" t="s">
@@ -3630,7 +3630,7 @@
       <c r="E8" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="F8" s="118" t="s">
+      <c r="F8" s="114" t="s">
         <v>180</v>
       </c>
       <c r="G8" s="38" t="s">
@@ -3821,9 +3821,9 @@
       <c r="DA8" s="42"/>
       <c r="DB8" s="42"/>
     </row>
-    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35"/>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="111" t="s">
         <v>198</v>
       </c>
       <c r="C9" s="37" t="s">
@@ -3835,7 +3835,7 @@
       <c r="E9" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="119" t="s">
+      <c r="F9" s="115" t="s">
         <v>201</v>
       </c>
       <c r="G9" s="38" t="s">
@@ -4037,9 +4037,9 @@
       <c r="DA9" s="42"/>
       <c r="DB9" s="42"/>
     </row>
-    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35"/>
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="111" t="s">
         <v>217</v>
       </c>
       <c r="C10" s="54" t="s">
@@ -4051,7 +4051,7 @@
       <c r="E10" s="55">
         <v>0.74733796296277433</v>
       </c>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="116" t="s">
         <v>219</v>
       </c>
       <c r="G10" s="57"/>
@@ -4174,9 +4174,9 @@
       <c r="DA10" s="42"/>
       <c r="DB10" s="42"/>
     </row>
-    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="112" t="s">
         <v>222</v>
       </c>
       <c r="C11" s="67" t="s">
@@ -4386,7 +4386,7 @@
       <c r="CT11" s="50"/>
       <c r="CU11" s="51"/>
     </row>
-    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="70"/>
       <c r="B12" s="75" t="s">
         <v>234</v>
@@ -4600,7 +4600,7 @@
       <c r="CT12" s="50"/>
       <c r="CU12" s="51"/>
     </row>
-    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="70"/>
       <c r="B13" s="75" t="s">
         <v>243</v>
@@ -4814,7 +4814,7 @@
       <c r="CT13" s="50"/>
       <c r="CU13" s="51"/>
     </row>
-    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="70"/>
       <c r="B14" s="75" t="s">
         <v>250</v>
@@ -5026,7 +5026,7 @@
       <c r="CT14" s="50"/>
       <c r="CU14" s="51"/>
     </row>
-    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:106" s="34" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="70"/>
       <c r="B15" s="75" t="s">
         <v>256</v>
@@ -5244,7 +5244,7 @@
       <c r="CT15" s="50"/>
       <c r="CU15" s="51"/>
     </row>
-    <row r="16" spans="1:106" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:106" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="75"/>
       <c r="B16" s="75" t="s">
         <v>265</v>
@@ -5439,7 +5439,7 @@
       <c r="CT16" s="79"/>
       <c r="CU16" s="79"/>
     </row>
-    <row r="17" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="80"/>
       <c r="B17" s="80" t="s">
         <v>273</v>
@@ -5632,9 +5632,9 @@
       <c r="CT17" s="79"/>
       <c r="CU17" s="79"/>
     </row>
-    <row r="18" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="87"/>
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="113" t="s">
         <v>281</v>
       </c>
       <c r="C18" s="88" t="s">
@@ -5825,7 +5825,7 @@
       <c r="CT18" s="90"/>
       <c r="CU18" s="90"/>
     </row>
-    <row r="19" spans="1:99" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:99" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="87"/>
       <c r="B19" s="87" t="s">
         <v>287</v>
@@ -5965,7 +5965,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -5974,7 +5974,7 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>289</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>6</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>6</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>6</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>6</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>6</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>6</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>7</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>7</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>7</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>7</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>7</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>7</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>7</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>7</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>7</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>7</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>7</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>7</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>7</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>7</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>7</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>7</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>7</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>7</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>7</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>7</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>7</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>7</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>8</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>8</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>8</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>8</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>8</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>8</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>8</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>8</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>8</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>8</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>8</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>8</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>8</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>8</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>8</v>
       </c>
@@ -7096,7 +7096,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>8</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>8</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>8</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>8</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>8</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>9</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>9</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>9</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>9</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>9</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>9</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>9</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>9</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>9</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7657,7 +7657,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>10</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>10</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>10</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>10</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>10</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>10</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>10</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>10</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>10</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>10</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>10</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>10</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10</v>
       </c>
@@ -7997,7 +7997,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>10</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>10</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>10</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>10</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>10</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>10</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>11</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>11</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>11</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>11</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>11</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>11</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>11</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>11</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>11</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>11</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>11</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>11</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>11</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>11</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>11</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>11</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>11</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>11</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>11</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>11</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>11</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>11</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>11</v>
       </c>
@@ -8507,7 +8507,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>11</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>11</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>12</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>12</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>12</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>12</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>12</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>12</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>12</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>12</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>12</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>12</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>12</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>12</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>12</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>12</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>12</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>12</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>12</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>12</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>12</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>12</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>12</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>12</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>12</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>12</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>12</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>13</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>13</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>13</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>13</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>13</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>13</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>13</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>13</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>13</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>13</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>13</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>13</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>13</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>13</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>13</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>13</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>13</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>13</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>13</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>13</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>13</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>13</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>13</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>13</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>13</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>14</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>14</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>14</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>14</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>14</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>14</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>14</v>
       </c>
@@ -9527,7 +9527,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>14</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>14</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>14</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>14</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>14</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>14</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>14</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>14</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>14</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>14</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>14</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>14</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>14</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>14</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>14</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>14</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>14</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>15</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>15</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>15</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>15</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>15</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>15</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>15</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>15</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>15</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>15</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>15</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>15</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>15</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>15</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>15</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>15</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>15</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>15</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>15</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>15</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>15</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>15</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>15</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>15</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>15</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>16</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>16</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>16</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>16</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>16</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>16</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>16</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>16</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>16</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>16</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>16</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>16</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>16</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>16</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>16</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>16</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>16</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>16</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>16</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>16</v>
       </c>
@@ -10581,7 +10581,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>16</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>16</v>
       </c>
@@ -10615,7 +10615,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>16</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>16</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>16</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>17</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>17</v>
       </c>
@@ -10717,7 +10717,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>17</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>17</v>
       </c>
@@ -10751,7 +10751,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>17</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>17</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>17</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>17</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>17</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>17</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>17</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>17</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>17</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>17</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>17</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>17</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>17</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>17</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>17</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>17</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>17</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>17</v>
       </c>
@@ -11074,7 +11074,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>17</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>18</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>18</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>18</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>18</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>18</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>18</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>18</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>18</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>18</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>18</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>18</v>
       </c>
@@ -11278,7 +11278,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>18</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>18</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>18</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>18</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>18</v>
       </c>
@@ -11363,7 +11363,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>18</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>18</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>18</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>18</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>18</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>18</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>18</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>18</v>
       </c>
@@ -11499,7 +11499,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>18</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>19</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>19</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>19</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>19</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>19</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>19</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>19</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>19</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>19</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>19</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>19</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>19</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>19</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>19</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>19</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>19</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>19</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>19</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>19</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>19</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>19</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>19</v>
       </c>
@@ -11890,7 +11890,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>19</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>19</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>19</v>
       </c>
